--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1679">
   <si>
     <t>05-050305TM</t>
   </si>
@@ -179,7 +179,7 @@
     <t>05-050302A</t>
   </si>
   <si>
-    <t>7bfed77fd5ad8b4fc68c47294e653478</t>
+    <t>0c865616e57da7ff865bf8e20b4bcf2f</t>
   </si>
   <si>
     <t>02-020005TC</t>
@@ -212,7 +212,7 @@
     <t>915-150018TP</t>
   </si>
   <si>
-    <t>dce7ac10231088c32a5d6a4dd93da4f0</t>
+    <t>62e8009b0bb43fe17664e9f2373a6c8c</t>
   </si>
   <si>
     <t>03-02010301-030102A</t>
@@ -221,7 +221,7 @@
     <t>915-150018TM</t>
   </si>
   <si>
-    <t>e0bffe1fdb5857eab5e3114b0c9c0382</t>
+    <t>39b20a4d3a33d1313cc52833ba6c0bca</t>
   </si>
   <si>
     <t>01-010057A</t>
@@ -278,7 +278,7 @@
     <t>915-150018TC</t>
   </si>
   <si>
-    <t>2e05a144f66028190d34847b3362dde0</t>
+    <t>6a8ff615cdb00a46b4e5c0f541ed124b</t>
   </si>
   <si>
     <t>915-150007TP</t>
@@ -506,6 +506,9 @@
     <t>01-010076TP</t>
   </si>
   <si>
+    <t>b7d78c63edeadaad65afa9377b208b16</t>
+  </si>
+  <si>
     <t>01-010077A</t>
   </si>
   <si>
@@ -530,7 +533,7 @@
     <t>05-050101A</t>
   </si>
   <si>
-    <t>4a3e456e352fa555777ca0bd64d47f10</t>
+    <t>4a75f014e6cf8b2a6884a8454b7d349c</t>
   </si>
   <si>
     <t>04-040021TM</t>
@@ -581,7 +584,7 @@
     <t>05-050102A</t>
   </si>
   <si>
-    <t>84ddc0a1714a5682c52441b3a600e88d</t>
+    <t>30587d204d5fa418df4b30ce24416406</t>
   </si>
   <si>
     <t>03-030035TP</t>
@@ -1475,7 +1478,7 @@
     <t>05-050101TP</t>
   </si>
   <si>
-    <t>6f97afe26a8657a5119d25ad7b8559b0</t>
+    <t>949da19d905f5c0164705cdbf138b039</t>
   </si>
   <si>
     <t>03-030063TC</t>
@@ -1844,7 +1847,7 @@
     <t>915-150013TP</t>
   </si>
   <si>
-    <t>3d453c9ade000e56d3451cb09588c3b3</t>
+    <t>0bc8bdf73950f50bb65c5e87bf7c5d77</t>
   </si>
   <si>
     <t>03-030006TC</t>
@@ -2177,7 +2180,7 @@
     <t>915-150004TP</t>
   </si>
   <si>
-    <t>0495035ecca609cfeb06ce9e8b190008</t>
+    <t>19796459bde6467c01113b81816d466f</t>
   </si>
   <si>
     <t>01-010060TP</t>
@@ -2207,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2378,7 +2381,7 @@
     <t>915-150017TP</t>
   </si>
   <si>
-    <t>ed8c457866145b1fccf8e528d5f248e5</t>
+    <t>2882a2cb40dba8d87f6ef93f3dc9b3b3</t>
   </si>
   <si>
     <t>915-150017TM</t>
@@ -2423,7 +2426,7 @@
     <t>05-050313A</t>
   </si>
   <si>
-    <t>b823ededb00f3f5e595f103281285d1d</t>
+    <t>b5e4fb67b34969403b416ddbb15a1d24</t>
   </si>
   <si>
     <t>902-0204-02040102ATC</t>
@@ -3437,7 +3440,7 @@
     <t>05-050313TP</t>
   </si>
   <si>
-    <t>c6c1e2c119d5ad7edf535dc0da9ba698</t>
+    <t>9f8ae3fc79ca25eb516e02c7d8e9e1ed</t>
   </si>
   <si>
     <t>01-010004A</t>
@@ -3464,7 +3467,7 @@
     <t>05-050313TC</t>
   </si>
   <si>
-    <t>d3725106bca2f2d98ca63e308d586c64</t>
+    <t>25bb50cf2142c3c1efc9273f65308156</t>
   </si>
   <si>
     <t>01-010028A</t>
@@ -4037,7 +4040,7 @@
     <t>05-050102TP</t>
   </si>
   <si>
-    <t>99d7b6e019b6c6918031ae8271d0911e</t>
+    <t>e8973709aee26ae01b8b5a785784a646</t>
   </si>
   <si>
     <t>03-030062TC</t>
@@ -4565,7 +4568,7 @@
     <t>915-150014TP</t>
   </si>
   <si>
-    <t>d14cac23d2626f98c9d87e619d7d7b48</t>
+    <t>ebdec01a6b309e3748d9754a298a2ebb</t>
   </si>
   <si>
     <t>05-0709-070906BTC</t>
@@ -4691,7 +4694,7 @@
     <t>915-150003TP</t>
   </si>
   <si>
-    <t>4e31018713f454334601900c22ae6f95</t>
+    <t>6c8a48c4793f647ae22e6415d1918f72</t>
   </si>
   <si>
     <t>01-080101-010083TC</t>
@@ -5850,12 +5853,12 @@
         <v>163</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B97" t="s">
         <v>1</v>
@@ -5863,39 +5866,39 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B98" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B99" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B100" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B102" t="s">
         <v>1</v>
@@ -5903,23 +5906,23 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B103" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B104" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B105" t="s">
         <v>1</v>
@@ -5927,7 +5930,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B106" t="s">
         <v>1</v>
@@ -5935,7 +5938,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B107" t="s">
         <v>1</v>
@@ -5943,31 +5946,31 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B108" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B109" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B110" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B111" t="s">
         <v>1</v>
@@ -5975,31 +5978,31 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B112" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B113" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B114" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B115" t="s">
         <v>1</v>
@@ -6007,71 +6010,71 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B116" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B117" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B118" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B119" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B120" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B121" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B124" t="s">
         <v>1</v>
@@ -6079,55 +6082,55 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B125" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B126" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B127" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B128" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B129" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B130" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B131" t="s">
         <v>1</v>
@@ -6135,23 +6138,23 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B132" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B134" t="s">
         <v>1</v>
@@ -6159,23 +6162,23 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B137" t="s">
         <v>1</v>
@@ -6183,39 +6186,39 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B142" t="s">
         <v>1</v>
@@ -6223,15 +6226,15 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B143" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B144" t="s">
         <v>1</v>
@@ -6239,55 +6242,55 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B145" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B146" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B147" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B148" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B149" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B150" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B151" t="s">
         <v>1</v>
@@ -6295,15 +6298,15 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B152" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B153" t="s">
         <v>1</v>
@@ -6311,39 +6314,39 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B154" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B155" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B156" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B158" t="s">
         <v>1</v>
@@ -6351,15 +6354,15 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B159" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B160" t="s">
         <v>1</v>
@@ -6367,7 +6370,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B161" t="s">
         <v>1</v>
@@ -6375,7 +6378,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B162" t="s">
         <v>1</v>
@@ -6383,23 +6386,23 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
         <v>1</v>
@@ -6407,15 +6410,15 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B167" t="s">
         <v>1</v>
@@ -6423,7 +6426,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B168" t="s">
         <v>1</v>
@@ -6431,7 +6434,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B169" t="s">
         <v>1</v>
@@ -6439,15 +6442,15 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B171" t="s">
         <v>1</v>
@@ -6455,15 +6458,15 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B172" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B173" t="s">
         <v>1</v>
@@ -6471,15 +6474,15 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B174" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B175" t="s">
         <v>1</v>
@@ -6487,7 +6490,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B176" t="s">
         <v>1</v>
@@ -6495,23 +6498,23 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B177" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
         <v>1</v>
@@ -6519,15 +6522,15 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B180" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B181" t="s">
         <v>1</v>
@@ -6535,63 +6538,63 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B182" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B183" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B184" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B185" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B186" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B187" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B188" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B189" t="s">
         <v>1</v>
@@ -6599,7 +6602,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B190" t="s">
         <v>1</v>
@@ -6607,111 +6610,111 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B191" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B192" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B193" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B194" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B195" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B196" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B197" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B198" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B199" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B200" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B201" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B202" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B203" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B204" t="s">
         <v>75</v>
@@ -6719,63 +6722,63 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B205" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B206" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B207" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B208" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B209" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B210" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B211" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B212" t="s">
         <v>1</v>
@@ -6783,31 +6786,31 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B213" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B214" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B215" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B216" t="s">
         <v>1</v>
@@ -6815,7 +6818,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B217" t="s">
         <v>1</v>
@@ -6823,31 +6826,31 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B218" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B219" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B220" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B221" t="s">
         <v>1</v>
@@ -6855,15 +6858,15 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B222" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B223" t="s">
         <v>1</v>
@@ -6871,7 +6874,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B224" t="s">
         <v>1</v>
@@ -6879,55 +6882,55 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B225" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B226" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B227" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B228" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B229" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B230" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B231" t="s">
         <v>1</v>
@@ -6935,7 +6938,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B232" t="s">
         <v>1</v>
@@ -6943,31 +6946,31 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B233" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B234" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B235" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B236" t="s">
         <v>1</v>
@@ -6975,15 +6978,15 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B237" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B238" t="s">
         <v>1</v>
@@ -6991,23 +6994,23 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B239" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B240" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B241" t="s">
         <v>1</v>
@@ -7015,31 +7018,31 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B242" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B243" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B244" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B245" t="s">
         <v>1</v>
@@ -7047,15 +7050,15 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B246" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B247" t="s">
         <v>1</v>
@@ -7063,31 +7066,31 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B248" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B249" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B250" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B251" t="s">
         <v>1</v>
@@ -7095,7 +7098,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B252" t="s">
         <v>1</v>
@@ -7103,15 +7106,15 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B253" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B254" t="s">
         <v>1</v>
@@ -7119,7 +7122,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B255" t="s">
         <v>1</v>
@@ -7127,39 +7130,39 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B256" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B257" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B258" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B259" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B260" t="s">
         <v>1</v>
@@ -7167,23 +7170,23 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B261" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B262" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B263" t="s">
         <v>1</v>
@@ -7191,23 +7194,23 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B264" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B265" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B266" t="s">
         <v>1</v>
@@ -7215,23 +7218,23 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B267" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B268" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B269" t="s">
         <v>75</v>
@@ -7239,23 +7242,23 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B270" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B271" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B272" t="s">
         <v>1</v>
@@ -7263,15 +7266,15 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B273" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B274" t="s">
         <v>1</v>
@@ -7279,7 +7282,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B275" t="s">
         <v>1</v>
@@ -7287,7 +7290,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B276" t="s">
         <v>75</v>
@@ -7295,7 +7298,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B277" t="s">
         <v>1</v>
@@ -7303,15 +7306,15 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B278" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B279" t="s">
         <v>75</v>
@@ -7319,23 +7322,23 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B280" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B281" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B282" t="s">
         <v>1</v>
@@ -7343,15 +7346,15 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B283" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B284" t="s">
         <v>1</v>
@@ -7359,15 +7362,15 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B285" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B286" t="s">
         <v>1</v>
@@ -7375,103 +7378,103 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B287" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B288" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B289" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B290" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B291" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B292" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B293" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B294" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B295" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B296" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B297" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B298" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B299" t="s">
         <v>1</v>
@@ -7479,55 +7482,55 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B300" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B301" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B302" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B303" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B304" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B305" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B306" t="s">
         <v>1</v>
@@ -7535,23 +7538,23 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B307" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B308" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B309" t="s">
         <v>1</v>
@@ -7559,39 +7562,39 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B310" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B311" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B312" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B313" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B314" t="s">
         <v>1</v>
@@ -7599,23 +7602,23 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B315" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B316" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B317" t="s">
         <v>1</v>
@@ -7623,15 +7626,15 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B318" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B319" t="s">
         <v>1</v>
@@ -7639,7 +7642,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B320" t="s">
         <v>1</v>
@@ -7647,31 +7650,31 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B321" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B322" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B323" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B324" t="s">
         <v>1</v>
@@ -7679,15 +7682,15 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B325" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B326" t="s">
         <v>1</v>
@@ -7695,15 +7698,15 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B327" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B328" t="s">
         <v>1</v>
@@ -7711,23 +7714,23 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B329" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B330" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B331" t="s">
         <v>1</v>
@@ -7735,23 +7738,23 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B332" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B333" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B334" t="s">
         <v>1</v>
@@ -7759,7 +7762,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B335" t="s">
         <v>1</v>
@@ -7767,7 +7770,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B336" t="s">
         <v>1</v>
@@ -7775,47 +7778,47 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B337" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B338" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B339" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B340" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B341" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B342" t="s">
         <v>1</v>
@@ -7823,7 +7826,7 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B343" t="s">
         <v>1</v>
@@ -7831,7 +7834,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B344" t="s">
         <v>1</v>
@@ -7839,7 +7842,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B345" t="s">
         <v>1</v>
@@ -7847,7 +7850,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B346" t="s">
         <v>1</v>
@@ -7855,63 +7858,63 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B347" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B348" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B349" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B350" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B351" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B352" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B353" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B354" t="s">
         <v>1</v>
@@ -7919,7 +7922,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B355" t="s">
         <v>1</v>
@@ -7927,7 +7930,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B356" t="s">
         <v>1</v>
@@ -7935,15 +7938,15 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B357" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B358" t="s">
         <v>1</v>
@@ -7951,239 +7954,239 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B359" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B360" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B361" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B362" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B363" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B364" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B365" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B366" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B367" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B368" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B369" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B370" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B371" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B372" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B373" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B374" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B375" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B376" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B377" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B378" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B379" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B380" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B381" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B382" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B383" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B384" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B385" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B386" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B387" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B388" t="s">
         <v>1</v>
@@ -8191,15 +8194,15 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B389" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B390" t="s">
         <v>1</v>
@@ -8207,15 +8210,15 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B391" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B392" t="s">
         <v>1</v>
@@ -8223,7 +8226,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B393" t="s">
         <v>1</v>
@@ -8231,7 +8234,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B394" t="s">
         <v>1</v>
@@ -8239,7 +8242,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B395" t="s">
         <v>1</v>
@@ -8247,7 +8250,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B396" t="s">
         <v>1</v>
@@ -8255,7 +8258,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B397" t="s">
         <v>1</v>
@@ -8263,7 +8266,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B398" t="s">
         <v>1</v>
@@ -8271,7 +8274,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B399" t="s">
         <v>1</v>
@@ -8279,23 +8282,23 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B400" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B401" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B402" t="s">
         <v>1</v>
@@ -8303,7 +8306,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B403" t="s">
         <v>1</v>
@@ -8311,15 +8314,15 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B404" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B405" t="s">
         <v>1</v>
@@ -8327,7 +8330,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B406" t="s">
         <v>1</v>
@@ -8335,7 +8338,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B407" t="s">
         <v>1</v>
@@ -8343,7 +8346,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B408" t="s">
         <v>1</v>
@@ -8351,47 +8354,47 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B409" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B410" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B411" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B412" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B413" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B414" t="s">
         <v>75</v>
@@ -8399,23 +8402,23 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B415" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B416" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B417" t="s">
         <v>1</v>
@@ -8423,63 +8426,63 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B418" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B419" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B420" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B421" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B422" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B423" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B424" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B425" t="s">
         <v>1</v>
@@ -8487,23 +8490,23 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B426" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B427" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B428" t="s">
         <v>1</v>
@@ -8511,31 +8514,31 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B429" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B430" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B431" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B432" t="s">
         <v>1</v>
@@ -8543,39 +8546,39 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B433" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B434" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B435" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B436" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B437" t="s">
         <v>1</v>
@@ -8583,23 +8586,23 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B438" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B439" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B440" t="s">
         <v>1</v>
@@ -8607,39 +8610,39 @@
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B441" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B442" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B443" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B444" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B445" t="s">
         <v>75</v>
@@ -8647,7 +8650,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B446" t="s">
         <v>1</v>
@@ -8655,31 +8658,31 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B447" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B448" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B449" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B450" t="s">
         <v>1</v>
@@ -8687,7 +8690,7 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B451" t="s">
         <v>1</v>
@@ -8695,7 +8698,7 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B452" t="s">
         <v>1</v>
@@ -8703,7 +8706,7 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B453" t="s">
         <v>1</v>
@@ -8711,7 +8714,7 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B454" t="s">
         <v>1</v>
@@ -8719,7 +8722,7 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B455" t="s">
         <v>1</v>
@@ -8727,71 +8730,71 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B456" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B457" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B458" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B459" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B460" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B461" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B462" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B463" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B464" t="s">
         <v>1</v>
@@ -8799,15 +8802,15 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B465" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B466" t="s">
         <v>75</v>
@@ -8815,7 +8818,7 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B467" t="s">
         <v>75</v>
@@ -8823,23 +8826,23 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B468" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B469" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B470" t="s">
         <v>1</v>
@@ -8847,15 +8850,15 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B471" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B472" t="s">
         <v>1</v>
@@ -8863,7 +8866,7 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B473" t="s">
         <v>1</v>
@@ -8871,7 +8874,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B474" t="s">
         <v>1</v>
@@ -8879,7 +8882,7 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B475" t="s">
         <v>1</v>
@@ -8887,87 +8890,87 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B476" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B477" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B478" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B479" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B480" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B481" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B482" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B483" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B484" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B485" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B486" t="s">
         <v>1</v>
@@ -8975,7 +8978,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B487" t="s">
         <v>1</v>
@@ -8983,15 +8986,15 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B488" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B489" t="s">
         <v>1</v>
@@ -8999,39 +9002,39 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B490" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B491" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B492" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B493" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B494" t="s">
         <v>1</v>
@@ -9039,7 +9042,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B495" t="s">
         <v>75</v>
@@ -9047,31 +9050,31 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B496" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B497" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B498" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B499" t="s">
         <v>75</v>
@@ -9079,159 +9082,159 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B500" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B501" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B502" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B503" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B504" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B505" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B506" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B507" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B508" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B509" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B510" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B511" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B512" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B513" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B514" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B515" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B516" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B517" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B518" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B519" t="s">
         <v>1</v>
@@ -9239,31 +9242,31 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B520" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B521" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B522" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B523" t="s">
         <v>75</v>
@@ -9271,23 +9274,23 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B524" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B525" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B526" t="s">
         <v>1</v>
@@ -9295,23 +9298,23 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B527" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B528" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B529" t="s">
         <v>1</v>
@@ -9319,7 +9322,7 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B530" t="s">
         <v>1</v>
@@ -9327,15 +9330,15 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B531" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B532" t="s">
         <v>1</v>
@@ -9343,63 +9346,63 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B533" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B534" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B535" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B536" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B537" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B538" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B539" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B540" t="s">
         <v>1</v>
@@ -9407,7 +9410,7 @@
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B541" t="s">
         <v>75</v>
@@ -9415,23 +9418,23 @@
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B542" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B543" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B544" t="s">
         <v>1</v>
@@ -9439,31 +9442,31 @@
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B545" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B546" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B547" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B548" t="s">
         <v>1</v>
@@ -9471,15 +9474,15 @@
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B549" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B550" t="s">
         <v>1</v>
@@ -9487,15 +9490,15 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B551" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B552" t="s">
         <v>1</v>
@@ -9503,15 +9506,15 @@
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B553" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B554" t="s">
         <v>1</v>
@@ -9519,7 +9522,7 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B555" t="s">
         <v>1</v>
@@ -9527,39 +9530,39 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B556" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B557" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B558" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B559" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B560" t="s">
         <v>1</v>
@@ -9567,7 +9570,7 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B561" t="s">
         <v>1</v>
@@ -9575,15 +9578,15 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B562" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B563" t="s">
         <v>75</v>
@@ -9591,47 +9594,47 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B564" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B565" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B566" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B567" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B568" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B569" t="s">
         <v>1</v>
@@ -9639,15 +9642,15 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B570" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B571" t="s">
         <v>1</v>
@@ -9655,87 +9658,87 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B572" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B573" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B574" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B575" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B576" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B577" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B578" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B579" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B580" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B581" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B582" t="s">
         <v>1</v>
@@ -9743,263 +9746,263 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B583" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B584" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B585" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B586" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B587" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B588" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B589" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B590" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B591" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B592" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B593" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B594" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B595" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B596" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B597" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B598" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B599" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B600" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B601" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B602" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B603" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B604" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B605" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B606" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B607" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B608" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B609" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B610" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B611" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B612" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B613" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B614" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B615" t="s">
         <v>1</v>
@@ -10007,23 +10010,23 @@
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B616" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B617" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B618" t="s">
         <v>1</v>
@@ -10031,7 +10034,7 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B619" t="s">
         <v>1</v>
@@ -10039,23 +10042,23 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B620" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B621" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B622" t="s">
         <v>1</v>
@@ -10063,7 +10066,7 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B623" t="s">
         <v>1</v>
@@ -10071,55 +10074,55 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B624" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B625" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B626" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B627" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B628" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B629" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B630" t="s">
         <v>1</v>
@@ -10127,7 +10130,7 @@
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B631" t="s">
         <v>1</v>
@@ -10135,7 +10138,7 @@
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B632" t="s">
         <v>1</v>
@@ -10143,15 +10146,15 @@
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B633" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B634" t="s">
         <v>1</v>
@@ -10159,7 +10162,7 @@
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B635" t="s">
         <v>1</v>
@@ -10167,23 +10170,23 @@
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B636" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B637" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B638" t="s">
         <v>1</v>
@@ -10191,23 +10194,23 @@
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B639" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B640" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B641" t="s">
         <v>1</v>
@@ -10215,7 +10218,7 @@
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B642" t="s">
         <v>1</v>
@@ -10223,7 +10226,7 @@
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B643" t="s">
         <v>1</v>
@@ -10231,31 +10234,31 @@
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B644" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B645" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B646" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B647" t="s">
         <v>1</v>
@@ -10263,15 +10266,15 @@
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B648" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B649" t="s">
         <v>1</v>
@@ -10279,7 +10282,7 @@
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B650" t="s">
         <v>1</v>
@@ -10287,15 +10290,15 @@
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B651" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B652" t="s">
         <v>1</v>
@@ -10303,15 +10306,15 @@
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B653" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B654" t="s">
         <v>1</v>
@@ -10319,15 +10322,15 @@
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B655" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B656" t="s">
         <v>1</v>
@@ -10335,15 +10338,15 @@
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B657" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B658" t="s">
         <v>1</v>
@@ -10351,15 +10354,15 @@
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B659" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B660" t="s">
         <v>1</v>
@@ -10367,87 +10370,87 @@
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B661" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B662" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B663" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B664" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B665" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B666" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B667" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B668" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B669" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B670" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B671" t="s">
         <v>1</v>
@@ -10455,7 +10458,7 @@
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B672" t="s">
         <v>1</v>
@@ -10463,23 +10466,23 @@
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B673" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B674" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B675" t="s">
         <v>1</v>
@@ -10487,7 +10490,7 @@
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B676" t="s">
         <v>1</v>
@@ -10495,7 +10498,7 @@
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B677" t="s">
         <v>1</v>
@@ -10503,23 +10506,23 @@
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B678" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B679" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B680" t="s">
         <v>1</v>
@@ -10527,7 +10530,7 @@
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B681" t="s">
         <v>1</v>
@@ -10535,7 +10538,7 @@
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B682" t="s">
         <v>1</v>
@@ -10543,23 +10546,23 @@
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B683" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B684" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B685" t="s">
         <v>1</v>
@@ -10567,23 +10570,23 @@
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B686" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B687" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B688" t="s">
         <v>1</v>
@@ -10591,23 +10594,23 @@
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B689" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B690" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B691" t="s">
         <v>1</v>
@@ -10615,7 +10618,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B692" t="s">
         <v>1</v>
@@ -10623,7 +10626,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B693" t="s">
         <v>1</v>
@@ -10631,15 +10634,15 @@
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B694" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B695" t="s">
         <v>1</v>
@@ -10647,7 +10650,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B696" t="s">
         <v>1</v>
@@ -10655,31 +10658,31 @@
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B697" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B698" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B699" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B700" t="s">
         <v>1</v>
@@ -10687,47 +10690,47 @@
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B701" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B702" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B703" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B704" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B705" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B706" t="s">
         <v>1</v>
@@ -10735,15 +10738,15 @@
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B707" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B708" t="s">
         <v>1</v>
@@ -10751,47 +10754,47 @@
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B709" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B710" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B711" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B712" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B713" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B714" t="s">
         <v>1</v>
@@ -10799,15 +10802,15 @@
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B715" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B716" t="s">
         <v>1</v>
@@ -10815,15 +10818,15 @@
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B717" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B718" t="s">
         <v>1</v>
@@ -10831,47 +10834,47 @@
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B719" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B720" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B721" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B722" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B723" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B724" t="s">
         <v>1</v>
@@ -10879,15 +10882,15 @@
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B725" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B726" t="s">
         <v>1</v>
@@ -10895,7 +10898,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B727" t="s">
         <v>1</v>
@@ -10903,71 +10906,71 @@
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B728" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B729" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B730" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B731" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B732" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B733" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B734" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B735" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B736" t="s">
         <v>1</v>
@@ -10975,39 +10978,39 @@
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B737" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B738" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B739" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B740" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B741" t="s">
         <v>1</v>
@@ -11015,7 +11018,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B742" t="s">
         <v>1</v>
@@ -11023,23 +11026,23 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B743" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B744" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B745" t="s">
         <v>1</v>
@@ -11047,15 +11050,15 @@
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B746" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B747" t="s">
         <v>1</v>
@@ -11063,7 +11066,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B748" t="s">
         <v>1</v>
@@ -11071,15 +11074,15 @@
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B749" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B750" t="s">
         <v>1</v>
@@ -11087,15 +11090,15 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B751" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B752" t="s">
         <v>1</v>
@@ -11103,79 +11106,79 @@
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B753" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B754" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B755" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B756" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B757" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B758" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B759" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B760" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B761" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B762" t="s">
         <v>1</v>
@@ -11183,71 +11186,71 @@
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B763" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B764" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B765" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B766" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B767" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B768" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B769" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B770" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B771" t="s">
         <v>1</v>
@@ -11255,39 +11258,39 @@
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B772" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B773" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B774" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B775" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B776" t="s">
         <v>1</v>
@@ -11295,7 +11298,7 @@
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B777" t="s">
         <v>1</v>
@@ -11303,23 +11306,23 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B778" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B779" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B780" t="s">
         <v>1</v>
@@ -11327,15 +11330,15 @@
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B781" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B782" t="s">
         <v>1</v>
@@ -11343,7 +11346,7 @@
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B783" t="s">
         <v>1</v>
@@ -11351,7 +11354,7 @@
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B784" t="s">
         <v>1</v>
@@ -11359,7 +11362,7 @@
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B785" t="s">
         <v>1</v>
@@ -11367,7 +11370,7 @@
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B786" t="s">
         <v>1</v>
@@ -11375,23 +11378,23 @@
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B787" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B788" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B789" t="s">
         <v>1</v>
@@ -11399,31 +11402,31 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B790" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B791" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B792" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B793" t="s">
         <v>1</v>
@@ -11431,55 +11434,55 @@
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B794" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B795" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B796" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B797" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B798" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B799" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B800" t="s">
         <v>1</v>
@@ -11487,31 +11490,31 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B801" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B802" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B803" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B804" t="s">
         <v>1</v>
@@ -11519,7 +11522,7 @@
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B805" t="s">
         <v>1</v>
@@ -11527,31 +11530,31 @@
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B806" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B807" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B808" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B809" t="s">
         <v>1</v>
@@ -11559,7 +11562,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B810" t="s">
         <v>1</v>
@@ -11567,39 +11570,39 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B811" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B812" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B813" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B814" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B815" t="s">
         <v>1</v>
@@ -11607,7 +11610,7 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B816" t="s">
         <v>1</v>
@@ -11615,7 +11618,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B817" t="s">
         <v>1</v>
@@ -11623,7 +11626,7 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B818" t="s">
         <v>1</v>
@@ -11631,31 +11634,31 @@
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B819" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B820" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B821" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B822" t="s">
         <v>1</v>
@@ -11663,7 +11666,7 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B823" t="s">
         <v>1</v>
@@ -11671,7 +11674,7 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B824" t="s">
         <v>1</v>
@@ -11679,31 +11682,31 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B825" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B826" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B827" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B828" t="s">
         <v>1</v>
@@ -11711,15 +11714,15 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B829" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B830" t="s">
         <v>1</v>
@@ -11727,7 +11730,7 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B831" t="s">
         <v>1</v>
@@ -11735,7 +11738,7 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B832" t="s">
         <v>1</v>
@@ -11743,47 +11746,47 @@
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B833" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B834" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B835" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B836" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B837" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B838" t="s">
         <v>1</v>
@@ -11791,7 +11794,7 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B839" t="s">
         <v>1</v>
@@ -11799,7 +11802,7 @@
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B840" t="s">
         <v>1</v>
@@ -11807,15 +11810,15 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B841" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B842" t="s">
         <v>1</v>
@@ -11823,7 +11826,7 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B843" t="s">
         <v>1</v>
@@ -11831,15 +11834,15 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B844" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B845" t="s">
         <v>1</v>
@@ -11847,23 +11850,23 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B846" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B847" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B848" t="s">
         <v>1</v>
@@ -11871,7 +11874,7 @@
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B849" t="s">
         <v>1</v>
@@ -11879,7 +11882,7 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B850" t="s">
         <v>1</v>
@@ -11887,15 +11890,15 @@
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B851" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B852" t="s">
         <v>1</v>
@@ -11903,7 +11906,7 @@
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B853" t="s">
         <v>1</v>
@@ -11911,7 +11914,7 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B854" t="s">
         <v>1</v>
@@ -11919,7 +11922,7 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B855" t="s">
         <v>1</v>
@@ -11927,47 +11930,47 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B856" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B857" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B858" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B859" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B860" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B861" t="s">
         <v>1</v>
@@ -11975,103 +11978,103 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B862" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B863" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B864" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B865" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B866" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B867" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B868" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B869" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B870" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B871" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B872" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B873" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B874" t="s">
         <v>1</v>
@@ -12079,15 +12082,15 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B875" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B876" t="s">
         <v>1</v>
@@ -12095,15 +12098,15 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B877" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B878" t="s">
         <v>1</v>
@@ -12111,15 +12114,15 @@
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B879" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B880" t="s">
         <v>75</v>
@@ -12127,15 +12130,15 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B881" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B882" t="s">
         <v>1</v>
@@ -12143,39 +12146,39 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B883" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B884" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B885" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B886" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B887" t="s">
         <v>1</v>
@@ -12183,7 +12186,7 @@
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B888" t="s">
         <v>1</v>
@@ -12191,7 +12194,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B889" t="s">
         <v>1</v>
@@ -12199,7 +12202,7 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B890" t="s">
         <v>1</v>
@@ -12207,15 +12210,15 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B891" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B892" t="s">
         <v>1</v>
@@ -12223,15 +12226,15 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B893" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B894" t="s">
         <v>1</v>
@@ -12239,7 +12242,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B895" t="s">
         <v>1</v>
@@ -12247,7 +12250,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B896" t="s">
         <v>1</v>
@@ -12255,7 +12258,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B897" t="s">
         <v>1</v>
@@ -12263,23 +12266,23 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B898" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B899" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B900" t="s">
         <v>1</v>
@@ -12287,7 +12290,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B901" t="s">
         <v>1</v>
@@ -12295,79 +12298,79 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B902" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B903" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B904" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B905" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B906" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B907" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B908" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B909" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B910" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B911" t="s">
         <v>75</v>
@@ -12375,23 +12378,23 @@
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B912" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B913" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B914" t="s">
         <v>1</v>
@@ -12399,199 +12402,199 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B915" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B916" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B917" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B918" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B919" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B920" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B921" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B922" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B923" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B924" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B925" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B926" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B927" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B928" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B929" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B930" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B931" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B932" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B933" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B934" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B935" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B936" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B937" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B938" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B939" t="s">
         <v>1</v>
@@ -12599,47 +12602,47 @@
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B940" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B941" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B942" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B943" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B944" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B945" t="s">
         <v>1</v>
@@ -12647,79 +12650,79 @@
     </row>
     <row r="946">
       <c r="A946" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B946" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B947" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B948" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B949" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B950" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B951" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B952" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B953" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B954" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B955" t="s">
         <v>1</v>
@@ -12727,31 +12730,31 @@
     </row>
     <row r="956">
       <c r="A956" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B956" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B957" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B958" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B959" t="s">
         <v>1</v>
@@ -12759,7 +12762,7 @@
     </row>
     <row r="960">
       <c r="A960" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B960" t="s">
         <v>1</v>
@@ -12767,7 +12770,7 @@
     </row>
     <row r="961">
       <c r="A961" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B961" t="s">
         <v>75</v>
@@ -12775,7 +12778,7 @@
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B962" t="s">
         <v>75</v>
@@ -12783,15 +12786,15 @@
     </row>
     <row r="963">
       <c r="A963" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B963" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B964" t="s">
         <v>1</v>
@@ -12799,15 +12802,15 @@
     </row>
     <row r="965">
       <c r="A965" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B965" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B966" t="s">
         <v>1</v>
@@ -12815,7 +12818,7 @@
     </row>
     <row r="967">
       <c r="A967" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B967" t="s">
         <v>1</v>
@@ -12823,7 +12826,7 @@
     </row>
     <row r="968">
       <c r="A968" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B968" t="s">
         <v>1</v>
@@ -12831,31 +12834,31 @@
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B969" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B970" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B971" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B972" t="s">
         <v>75</v>
@@ -12863,15 +12866,15 @@
     </row>
     <row r="973">
       <c r="A973" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B973" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B974" t="s">
         <v>1</v>
@@ -12879,23 +12882,23 @@
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B975" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B976" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B977" t="s">
         <v>1</v>
@@ -12903,7 +12906,7 @@
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B978" t="s">
         <v>1</v>
@@ -12911,31 +12914,31 @@
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B979" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B980" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B981" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B982" t="s">
         <v>1</v>
@@ -12943,79 +12946,79 @@
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B983" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B984" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B985" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B986" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B987" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B988" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B989" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B990" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B991" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B992" t="s">
         <v>1</v>
@@ -13023,15 +13026,15 @@
     </row>
     <row r="993">
       <c r="A993" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B993" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B994" t="s">
         <v>1</v>
@@ -13039,7 +13042,7 @@
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B995" t="s">
         <v>1</v>
@@ -13047,10 +13050,10 @@
     </row>
     <row r="996">
       <c r="A996" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B996" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
   </sheetData>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -77,7 +77,7 @@
     <t>05-050301A</t>
   </si>
   <si>
-    <t>6b5bef8bc5d42f9d30b95d561587e88f</t>
+    <t>d1207b34dd146200462e7eda16475e81</t>
   </si>
   <si>
     <t>03-030002TP</t>
@@ -827,7 +827,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>1ccd1de32dbe005c6c1543b97ed022a1</t>
+    <t>0b9fdb77c2306ca15ea4882915c5cf03</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -857,7 +857,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>dc9a77fb31c24e9e863f6dda3027d276</t>
+    <t>4f59027b01f2608e46116dcf1e940da8</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>c2ba8bf17373c5f0cff1fce454cec82a</t>
+    <t>708e959fcd99233532b4e728b8ea2a45</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>54b0228258c692d7ac30c1cc315ffe1d</t>
+    <t>fa4da00ea6ea210b37afd666b7934289</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>7fa8cb2d6ddce7331b6da5a3bda30a3d</t>
+    <t>0d31be08e5da513f79cba3aad4e612db</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>b0ca006d6efc4a6a7f3e9e1e6ab99e9f</t>
+    <t>12aa2afe1312739cd170cfbbf6db4bca</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -2831,7 +2831,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>9f4900f2d329a3f8851e5ab2be6b0083</t>
+    <t>b405e7a5ca5f41363a4f948ad66e67e7</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2933,7 +2933,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>b06f4c56633310a66fe340ec26e8c64e</t>
+    <t>77c5e8202b4f1481937ffc3459066017</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -3074,7 +3074,7 @@
     <t>03-030012TM</t>
   </si>
   <si>
-    <t>f2d7d4cbab759cdd14b8052ce5ef9dce</t>
+    <t>a40b31c1cb95200afe4345b7d66118f2</t>
   </si>
   <si>
     <t>01-080101-010089A</t>
@@ -4250,7 +4250,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>685853aadf29d8720ad77666b2bcd08a</t>
+    <t>97bddfc05a36601dd4f26294d424c8d5</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4265,7 +4265,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>c7b676b6fb3551cc5ef82efa3330934d</t>
+    <t>808d4c295a30aa62eac19de0f31ed5b2</t>
   </si>
   <si>
     <t>05-050006TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -65,7 +65,7 @@
     <t>05-050305TC</t>
   </si>
   <si>
-    <t>1df51009c1b5367256f79b4c97a9aee7</t>
+    <t>ed9acce598ab85c41b400614a877078e</t>
   </si>
   <si>
     <t>03-030002TM</t>
@@ -101,7 +101,7 @@
     <t>05-050207TP</t>
   </si>
   <si>
-    <t>09088a9949ad1a8f49e48e974ac83087</t>
+    <t>059e8f1eba321846fc43151850338435</t>
   </si>
   <si>
     <t>915-150012A</t>
@@ -113,7 +113,7 @@
     <t>05-050305TP</t>
   </si>
   <si>
-    <t>53601e0421ef0b80d2334b97bd351763</t>
+    <t>e4680b930d22d7d95a2e1aff9717d877</t>
   </si>
   <si>
     <t>05-0709-070921BTP</t>
@@ -152,7 +152,7 @@
     <t>05-050316TC</t>
   </si>
   <si>
-    <t>27ea83e59e475359c7067824c461be37</t>
+    <t>95bc9b548276ae6f60dc29ef1264f8ed</t>
   </si>
   <si>
     <t>03-030059TP</t>
@@ -206,7 +206,7 @@
     <t>05-050316TP</t>
   </si>
   <si>
-    <t>cf0dc0e7bccb941d33745a261424c664</t>
+    <t>dce0b1f1d6ed8ddf2e03e86f90a23704</t>
   </si>
   <si>
     <t>915-150018TP</t>
@@ -647,7 +647,7 @@
     <t>05-050301TP</t>
   </si>
   <si>
-    <t>25fbfe6bc6a3bd0a2084d71b2d872320</t>
+    <t>b314e5a1fa25c9d6ab436413067e54de</t>
   </si>
   <si>
     <t>05-050301TM</t>
@@ -662,7 +662,7 @@
     <t>05-050301TC</t>
   </si>
   <si>
-    <t>4b993743580714c27f04099bacdaa06f</t>
+    <t>1a3f1505868feb8a19f6cbcdfc804738</t>
   </si>
   <si>
     <t>01-010054TP</t>
@@ -680,7 +680,7 @@
     <t>05-050309A</t>
   </si>
   <si>
-    <t>58f664ec13664584ee1ece5d81b44762</t>
+    <t>8926a7b4d2655f02eaa2160e49ef96ad</t>
   </si>
   <si>
     <t>04-040003TP</t>
@@ -716,7 +716,7 @@
     <t>05-050312TP</t>
   </si>
   <si>
-    <t>fbec840e02f535bdf0b4b1cd69c2a46a</t>
+    <t>e57b169cf0d8d4048e0a76ea4204c296</t>
   </si>
   <si>
     <t>05-0709-070954TC</t>
@@ -731,7 +731,7 @@
     <t>05-050312TC</t>
   </si>
   <si>
-    <t>a435f31ba0bbe2506f40ac6402765640</t>
+    <t>5ad1bafd7c04cb5e92e04db29180a46e</t>
   </si>
   <si>
     <t>03-030055TP</t>
@@ -851,7 +851,7 @@
     <t>05-050203TP</t>
   </si>
   <si>
-    <t>d0df0a98d510e632eb5b028bbf2aba2d</t>
+    <t>2ca64185bfd6830fb10cf73cef34f560</t>
   </si>
   <si>
     <t>05-050007TP</t>
@@ -866,7 +866,7 @@
     <t>05-050308A</t>
   </si>
   <si>
-    <t>2b0269c464b59fe3dd3489ae566592a3</t>
+    <t>5ebc226671fdbd07110f027c3fd35fd4</t>
   </si>
   <si>
     <t>05-050203TM</t>
@@ -899,7 +899,7 @@
     <t>05-050203TC</t>
   </si>
   <si>
-    <t>69e4cd9089eff13849e48dca5d55da53</t>
+    <t>57702b7921554deff2cd45ddaff45c4b</t>
   </si>
   <si>
     <t>01-110304-11030404A</t>
@@ -926,7 +926,7 @@
     <t>05-050303TP</t>
   </si>
   <si>
-    <t>82426963d2aca61c392b118ba5129933</t>
+    <t>9bfd60431b45d499946ababbedf265a1</t>
   </si>
   <si>
     <t>03-030042TM</t>
@@ -953,7 +953,7 @@
     <t>05-050303TC</t>
   </si>
   <si>
-    <t>c861d4fd025db76c7afc46ce10a49f3f</t>
+    <t>4a357f852fdc44460a200c3a02cc839d</t>
   </si>
   <si>
     <t>01-010010TP</t>
@@ -971,7 +971,7 @@
     <t>05-050305A</t>
   </si>
   <si>
-    <t>3b78150ff1fc474be866da618f4a7754</t>
+    <t>e8cf2322e0111a167c83cdbea9f3e3dd</t>
   </si>
   <si>
     <t>04-040001TM</t>
@@ -1013,7 +1013,7 @@
     <t>05-050314TP</t>
   </si>
   <si>
-    <t>0fa317cd20a5b49aad28226bf6df9533</t>
+    <t>38b9da908bdd75aafe2d3c826c744706</t>
   </si>
   <si>
     <t>902-0204-02040102STC</t>
@@ -1055,7 +1055,7 @@
     <t>05-050314TC</t>
   </si>
   <si>
-    <t>bd9f44647569b5e2f4c5ad711528b41a</t>
+    <t>b4022141fd796266c0e0b82f212f99c3</t>
   </si>
   <si>
     <t>902-0204-02040101ATC</t>
@@ -1064,7 +1064,7 @@
     <t>05-050306A</t>
   </si>
   <si>
-    <t>220fbe3e9aaef97d6c55ff34f5c02ce1</t>
+    <t>eccdb284fe64b1be028c8b68764282f5</t>
   </si>
   <si>
     <t>902-0204-02040102STP</t>
@@ -1133,7 +1133,7 @@
     <t>05-050303A</t>
   </si>
   <si>
-    <t>bc91d4b0be812322444314f5443b41bc</t>
+    <t>f77883a5a8ff0fe4b0d11b07edf654ba</t>
   </si>
   <si>
     <t>05-0709-070910TP</t>
@@ -1208,13 +1208,13 @@
     <t>05-050205TP</t>
   </si>
   <si>
-    <t>2e5855dc59a3d101c8e3dae40a359c00</t>
+    <t>57fc0dac869fb3f0d141891a6c9a10c8</t>
   </si>
   <si>
     <t>05-050304A</t>
   </si>
   <si>
-    <t>57ef2d6c399be2220cb6bf4e701a20f6</t>
+    <t>8b43d6eb180c63a16e926b8faf7aee0c</t>
   </si>
   <si>
     <t>05-050009TP</t>
@@ -1238,7 +1238,7 @@
     <t>05-050205TC</t>
   </si>
   <si>
-    <t>c4030331425f6bf729588605a470eb2c</t>
+    <t>1bb755195f22abb90b20e6847658bffb</t>
   </si>
   <si>
     <t>04-040014TM</t>
@@ -1307,7 +1307,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>78e8e5b4d35bc1dd3ceb6a351506c4bc</t>
+    <t>786ced3b59d255ed903db148049874c1</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1466,7 +1466,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>c60c197cb24578b07b6a78579336d15a</t>
+    <t>f68caf7517eec411d056e39f6a6bf8e9</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -1496,7 +1496,7 @@
     <t>05-050201TC</t>
   </si>
   <si>
-    <t>6fb5b1881add52977736c6f8a650d8e7</t>
+    <t>853400072a9a923bb317833eb8e1029d</t>
   </si>
   <si>
     <t>03-030061TP</t>
@@ -1565,7 +1565,7 @@
     <t>05-050310TC</t>
   </si>
   <si>
-    <t>8f8bebfa3bf1f47dff51f2df564f140d</t>
+    <t>0ce4e02808b8b9e5627f74e5a070f157</t>
   </si>
   <si>
     <t>04-040004A</t>
@@ -1613,7 +1613,7 @@
     <t>05-050310TP</t>
   </si>
   <si>
-    <t>d91d562d5a99603c1c4c517bd16bc4d2</t>
+    <t>3d60a2d43a3866ef20089508a1ad4cca</t>
   </si>
   <si>
     <t>03-030072TM</t>
@@ -1748,7 +1748,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>9957746ca62d480b301fca0d3984ec02</t>
+    <t>e2f0a39e1ed7d8ae2482944dfdb5b15e</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -1769,7 +1769,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>eb4717392d96cb5d186e478cf51f188e</t>
+    <t>d9ddd5c3b6ddaab06f18a11561b69053</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -1793,7 +1793,7 @@
     <t>05-050201TP</t>
   </si>
   <si>
-    <t>d5a53b38dbb69a247d63cd2d60e28603</t>
+    <t>99e0624f512a37ca64da29d7ceea58e7</t>
   </si>
   <si>
     <t>05-0709-070902TM</t>
@@ -1901,7 +1901,7 @@
     <t>03-030070TC</t>
   </si>
   <si>
-    <t>884ca1dc8b42bf2cf75c1180c6035b0c</t>
+    <t>8d62e228cacd1180e9dc5effcf95158e</t>
   </si>
   <si>
     <t>05-0709-070906ATP</t>
@@ -1955,7 +1955,7 @@
     <t>03-030070TP</t>
   </si>
   <si>
-    <t>90954109c5d442f2adf8575dd44df35d</t>
+    <t>b144c9348c1ba9f4281b4caf0324bbcf</t>
   </si>
   <si>
     <t>01-080101-010084TC</t>
@@ -2165,7 +2165,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>9e126b63abb9a0b3dd5452a74c4fb13b</t>
+    <t>db02905784f29aa7e098ab09aa487438</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>0841f66eec1f7caf51680bed6f5054c6</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2348,7 +2348,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>102a560568012b479f3fa0a2bfad807a</t>
+    <t>2765c8f1c87dca50e2ff17335bb53c94</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2420,7 +2420,7 @@
     <t>05-050204A</t>
   </si>
   <si>
-    <t>baf84d1cbe510866799112cbfcd7709b</t>
+    <t>6a52edd308d0914ca301e2258cd0169c</t>
   </si>
   <si>
     <t>05-050313A</t>
@@ -2519,7 +2519,7 @@
     <t>05-050205A</t>
   </si>
   <si>
-    <t>6bef42abac4de6cc7407d8d26f62065a</t>
+    <t>7cae69c40117095f8c69f95634c88089</t>
   </si>
   <si>
     <t>04-040011TM</t>
@@ -2531,7 +2531,7 @@
     <t>05-050314A</t>
   </si>
   <si>
-    <t>830064ea44c0d05c93a59723f7118ea2</t>
+    <t>d7c9eb3bb1ebb4a091388333d7bd2a92</t>
   </si>
   <si>
     <t>901-010202-9010102021TP</t>
@@ -2612,7 +2612,7 @@
     <t>05-050208TC</t>
   </si>
   <si>
-    <t>d1484942ef08d715b335040b3a5e7c24</t>
+    <t>fab33c8231a9280e35833755f1a2078d</t>
   </si>
   <si>
     <t>03-030039A</t>
@@ -2657,13 +2657,13 @@
     <t>05-050202A</t>
   </si>
   <si>
-    <t>af1498cfb98edd0fd3304919bc590619</t>
+    <t>4082473e455ea2efcc317070f655c008</t>
   </si>
   <si>
     <t>05-050311A</t>
   </si>
   <si>
-    <t>a72749e8a01d69815f877c9d567e2fd3</t>
+    <t>67ab01d296e75654c21f4739000e956c</t>
   </si>
   <si>
     <t>05-050208TP</t>
@@ -2693,7 +2693,7 @@
     <t>05-050306TP</t>
   </si>
   <si>
-    <t>067ca15bdc2bb75fdda992d4b749a669</t>
+    <t>2cfe0f1373d2ec03ad6aa6b88c28f516</t>
   </si>
   <si>
     <t>905-9050607-905060701TC</t>
@@ -2732,13 +2732,13 @@
     <t>05-050317TC</t>
   </si>
   <si>
-    <t>6c1aa9bb02a7b3c0cdde7e4b3fc07dbf</t>
+    <t>4bd2f562bbbac4f175d158a4b2977ab2</t>
   </si>
   <si>
     <t>05-050312A</t>
   </si>
   <si>
-    <t>e36cfc8d647d2ba777e89889eb5fd238</t>
+    <t>a89528d3176a4dbcfe7c017e954a5ab5</t>
   </si>
   <si>
     <t>05-050009A</t>
@@ -2750,7 +2750,7 @@
     <t>05-050203A</t>
   </si>
   <si>
-    <t>bcb473d3636ec9820ddc03661f7e42a7</t>
+    <t>c56df910e4fed527df2ddd7eb4892484</t>
   </si>
   <si>
     <t>01-080101-010087TM</t>
@@ -2789,7 +2789,7 @@
     <t>05-050317TP</t>
   </si>
   <si>
-    <t>d798c3c15221dcec831d881a939029c2</t>
+    <t>6d93fcf9e0612fa89a7a361894e88df5</t>
   </si>
   <si>
     <t>01-010051TC</t>
@@ -2900,7 +2900,7 @@
     <t>05-050201A</t>
   </si>
   <si>
-    <t>bfc8fc8f5e86b6db53dd5586d2a06e43</t>
+    <t>053e9979a929718be152a7b44a18f23b</t>
   </si>
   <si>
     <t>04-040020TC</t>
@@ -2915,7 +2915,7 @@
     <t>05-050310A</t>
   </si>
   <si>
-    <t>6dc98ce9ec631a34dbe0d8e750d5b178</t>
+    <t>7f53db899963dee22e9ba6497c61010b</t>
   </si>
   <si>
     <t>915-150008TP</t>
@@ -2951,7 +2951,7 @@
     <t>03-030012A</t>
   </si>
   <si>
-    <t>c5c7c649b1403b6bd1a0e26b62810927</t>
+    <t>56c8d45a7d37b859645830d7ec698895</t>
   </si>
   <si>
     <t>03-030045TC</t>
@@ -2990,7 +2990,7 @@
     <t>05-050308TC</t>
   </si>
   <si>
-    <t>f6d27ccd73a65f0bdc5b05a571214f90</t>
+    <t>63ebd04f7f4961c0d42926a65412ba4a</t>
   </si>
   <si>
     <t>02-020002TC</t>
@@ -3008,7 +3008,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>b76fa55681ab244c650ea7ba30d7b660</t>
+    <t>fa298e244c4126c3d7361f58970d83c5</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3026,7 +3026,7 @@
     <t>03-030012TC</t>
   </si>
   <si>
-    <t>642e93137d04f203e5c272c3f7981b54</t>
+    <t>eb90b19323a5859efa320578d58c13a6</t>
   </si>
   <si>
     <t>03-030058TC</t>
@@ -3044,7 +3044,7 @@
     <t>05-050308TP</t>
   </si>
   <si>
-    <t>f19590d68f24b9b672fd3c539aab8343</t>
+    <t>6f945d891b1b07a146ded54fbb93459b</t>
   </si>
   <si>
     <t>03-030035A</t>
@@ -3098,7 +3098,7 @@
     <t>03-030012TP</t>
   </si>
   <si>
-    <t>56b4e83a6888967e55ee50b24f18dba8</t>
+    <t>68cebef0e28dc8122bf6c530043b3209</t>
   </si>
   <si>
     <t>03-030058TM</t>
@@ -3116,7 +3116,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>ba39438bc23efc7a39321ed0bae1a377</t>
+    <t>8f584d73c1d2ae49a61f6dfe4800c4ef</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -3275,7 +3275,7 @@
     <t>05-050204TP</t>
   </si>
   <si>
-    <t>14d050b2269d173538aed8d132a1567b</t>
+    <t>e161a2fa2ee9400f268f365465bde9d9</t>
   </si>
   <si>
     <t>915-150007A</t>
@@ -3329,7 +3329,7 @@
     <t>05-050204TC</t>
   </si>
   <si>
-    <t>a2f2c89d8e61151db8e5d62a41e3d34c</t>
+    <t>61bfb6dfbb9345ec8f1be50c3d1d8590</t>
   </si>
   <si>
     <t>04-040015TM</t>
@@ -3365,7 +3365,7 @@
     <t>05-050302TC</t>
   </si>
   <si>
-    <t>6da39242dc3e342481be3b884dfb17d8</t>
+    <t>8681f7b889429514746ff6849c36e77e</t>
   </si>
   <si>
     <t>01-110304-11030403TP</t>
@@ -3518,7 +3518,7 @@
     <t>05-050317A</t>
   </si>
   <si>
-    <t>79ec90319fcd89f911fb8849489458d2</t>
+    <t>fca18a2901952950103d43ab77236f8c</t>
   </si>
   <si>
     <t>01-010027A</t>
@@ -3584,7 +3584,7 @@
     <t>05-050206TP</t>
   </si>
   <si>
-    <t>5451fc92aae3e5333e1e9e215b99d53d</t>
+    <t>52e22e2e5aa4e0749a78e40333915b33</t>
   </si>
   <si>
     <t>01-010068TM</t>
@@ -3608,7 +3608,7 @@
     <t>05-050206TC</t>
   </si>
   <si>
-    <t>ea6c1a53ffac560a970a1f9ab1584e81</t>
+    <t>2cad2a7bf53ea3238fa8405eecf65ea3</t>
   </si>
   <si>
     <t>04-040013TM</t>
@@ -3692,7 +3692,7 @@
     <t>05-050304TC</t>
   </si>
   <si>
-    <t>e7280d7791813b01dc8a9941481ce44d</t>
+    <t>09c2ea614878074519969e3138174001</t>
   </si>
   <si>
     <t>03-030043TP</t>
@@ -3704,13 +3704,13 @@
     <t>05-050206A</t>
   </si>
   <si>
-    <t>f96b1ebfe6616e0b52a80aaed3ce7e80</t>
+    <t>6be39dc7d3f370598bac8b3e04944505</t>
   </si>
   <si>
     <t>05-050315A</t>
   </si>
   <si>
-    <t>69e752efebe41c5f6e6b78c9585d5f64</t>
+    <t>ea364ee5492aec3427b2f883e19dea73</t>
   </si>
   <si>
     <t>902-0204-02040101STP</t>
@@ -3773,7 +3773,7 @@
     <t>05-050304TP</t>
   </si>
   <si>
-    <t>363a4038010308db052655fb866438e4</t>
+    <t>0c351ffaffde51c6347d401a693f8eee</t>
   </si>
   <si>
     <t>04-040002TP</t>
@@ -3821,7 +3821,7 @@
     <t>05-050315TC</t>
   </si>
   <si>
-    <t>952382d47d10bd78b5a7cebabbc8493e</t>
+    <t>4f3388340ea7f4a2af6d438266c16a79</t>
   </si>
   <si>
     <t>01-010046TM</t>
@@ -3836,7 +3836,7 @@
     <t>05-050316A</t>
   </si>
   <si>
-    <t>00befa18721ee13a08f8b9160e59350c</t>
+    <t>1dfdd5679f7ee319e320d406aa4ca709</t>
   </si>
   <si>
     <t>902-0204-02040101BTC</t>
@@ -3860,7 +3860,7 @@
     <t>05-050207A</t>
   </si>
   <si>
-    <t>c9d8ad33e3779fce70cd4c812e3a58e9</t>
+    <t>d9f4f2892bdd8d80380caf4dcc428307</t>
   </si>
   <si>
     <t>02-020006TM</t>
@@ -3911,7 +3911,7 @@
     <t>05-050315TP</t>
   </si>
   <si>
-    <t>9c12e2aaa7853b75756fbbc3d8715c29</t>
+    <t>44e3088d57e75072827ee3ee130b7943</t>
   </si>
   <si>
     <t>03-030040TP</t>
@@ -3983,7 +3983,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>97f9a506bab813cf629d1c01b94a73cb</t>
+    <t>05089a667705b6ff52f21f0a6990ad9b</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4004,7 +4004,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>1251070858590fb23d481929357c7bbd</t>
+    <t>41bf80ef7c81b0a5661624678ccde1ca</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4109,7 +4109,7 @@
     <t>03-030071A</t>
   </si>
   <si>
-    <t>a55cd841ae22817e9d8e75e6235c48a7</t>
+    <t>bc215835c85ba728793c88004710b458</t>
   </si>
   <si>
     <t>915-150010TP</t>
@@ -4133,7 +4133,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>e8813c180153e8e2f7458d7d4691e535</t>
+    <t>b0c2a18df112b9f277fecaa6a1e00eb7</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4175,7 +4175,7 @@
     <t>03-030070A</t>
   </si>
   <si>
-    <t>13a58843e6c5aa259a24eb42e4c67fbc</t>
+    <t>2ef08e05d9da3935517d358309018e8d</t>
   </si>
   <si>
     <t>03-02010301-030083TM</t>
@@ -4286,7 +4286,7 @@
     <t>05-050202TP</t>
   </si>
   <si>
-    <t>1434c9f69be3cb90e050bb47d6d9121f</t>
+    <t>7f3c93123e6807038cd5a33a137219fe</t>
   </si>
   <si>
     <t>05-0709-070903TM</t>
@@ -4343,7 +4343,7 @@
     <t>05-050311TC</t>
   </si>
   <si>
-    <t>e25302e57621436b50037185e826bdbf</t>
+    <t>9ac516dcbe0b313e4b36eb8426ea47b9</t>
   </si>
   <si>
     <t>04-040014A</t>
@@ -4370,7 +4370,7 @@
     <t>05-050311TP</t>
   </si>
   <si>
-    <t>58589a08c5d5c3408b928146f58a5795</t>
+    <t>1affb1ed2822a12b159e8df078bf0975</t>
   </si>
   <si>
     <t>01-080101-010081TC</t>
@@ -4469,13 +4469,13 @@
     <t>05-050309TC</t>
   </si>
   <si>
-    <t>8f893dcb52b1e47d448c2b51b718df3e</t>
+    <t>6ca08574d86ae3aa9d7e5c47c265b84a</t>
   </si>
   <si>
     <t>05-050002A</t>
   </si>
   <si>
-    <t>58fbeb8b4138f0d93bf09bb62d1abeda</t>
+    <t>42ae2ecbbe95475185886ba7eb9ed1f7</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4505,7 +4505,7 @@
     <t>05-050309TP</t>
   </si>
   <si>
-    <t>4ab28706ee1ae6eb91108014bebc7fe6</t>
+    <t>4674a84d8a29ca83aa949ac49fbfc93a</t>
   </si>
   <si>
     <t>05-050309TM</t>
@@ -4532,7 +4532,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>46c088441dbb7bf6222b524c5aeedd6c</t>
+    <t>6f6df58ed26c3b04d4a1451cd1752a17</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4640,7 +4640,7 @@
     <t>03-030071TC</t>
   </si>
   <si>
-    <t>402455665a127b9c85bbd42f906ecf74</t>
+    <t>4a30d67ce0a5cdc8693422460434cffe</t>
   </si>
   <si>
     <t>915-150014TC</t>
@@ -4688,7 +4688,7 @@
     <t>03-030071TP</t>
   </si>
   <si>
-    <t>ab434232503911719a501da4bb02d3c9</t>
+    <t>1ce9255c51d6bdec0678e73941c7577d</t>
   </si>
   <si>
     <t>915-150003TP</t>
@@ -4736,7 +4736,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>f3f6811874ecdc67316e05785138873c</t>
+    <t>f39c13e6a0c461b855c0c6328d15b4d7</t>
   </si>
   <si>
     <t>01-010006TM</t>
@@ -4871,7 +4871,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>f793cf1af20f3a85061e0db0c3134e3b</t>
+    <t>e64797a2cb3edeb4ee2d3a9ac5c7bd75</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2669,7 +2669,7 @@
     <t>05-050208TP</t>
   </si>
   <si>
-    <t>cbe53266bb0cce4d0fe1a366ae1aa4da</t>
+    <t>6e7a711ccd7d38b00285bd320bf93cfa</t>
   </si>
   <si>
     <t>901-010202-9010102022A</t>
@@ -3338,7 +3338,7 @@
     <t>05-050302TP</t>
   </si>
   <si>
-    <t>76119c28981c4dbf23c59f7a8cfc6fd9</t>
+    <t>197c0b9cfac61b90cfd77d9e3b15133c</t>
   </si>
   <si>
     <t>01-010055TM</t>
@@ -3512,7 +3512,7 @@
     <t>05-050208A</t>
   </si>
   <si>
-    <t>5894348331bb6e1528cc7c651402a1b7</t>
+    <t>85cdec942922fd1be3bcf4d0623befca</t>
   </si>
   <si>
     <t>05-050317A</t>
@@ -4325,7 +4325,7 @@
     <t>05-050202TC</t>
   </si>
   <si>
-    <t>656faa7679774432e51d07f4641ddc9d</t>
+    <t>ec29680cb56f42a64a35dbc3449c2575</t>
   </si>
   <si>
     <t>03-030062TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>0841f66eec1f7caf51680bed6f5054c6</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -1457,7 +1457,7 @@
     <t>05-050003TM</t>
   </si>
   <si>
-    <t>5479388ebbf116e5c648f81165e5b532</t>
+    <t>a996d4ebbf0fd8d2ceecd7b76c1e4798</t>
   </si>
   <si>
     <t>01-010025TM</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -77,7 +77,7 @@
     <t>05-050301A</t>
   </si>
   <si>
-    <t>d1207b34dd146200462e7eda16475e81</t>
+    <t>408047ce987223fba9f85e8d7dda986f</t>
   </si>
   <si>
     <t>03-030002TP</t>
@@ -533,7 +533,7 @@
     <t>05-050101A</t>
   </si>
   <si>
-    <t>4a75f014e6cf8b2a6884a8454b7d349c</t>
+    <t>57287b73631d1dd0760a97d7f3caac2e</t>
   </si>
   <si>
     <t>04-040021TM</t>
@@ -584,7 +584,7 @@
     <t>05-050102A</t>
   </si>
   <si>
-    <t>30587d204d5fa418df4b30ce24416406</t>
+    <t>6de338d5b96f4c93b6ec4bb89b59161e</t>
   </si>
   <si>
     <t>03-030035TP</t>
@@ -827,7 +827,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>0b9fdb77c2306ca15ea4882915c5cf03</t>
+    <t>84f9177b78615335c74de6904e2acd32</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -857,7 +857,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>4f59027b01f2608e46116dcf1e940da8</t>
+    <t>ab0ea17fae2aec0703ccc1e868a613be</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1478,7 +1478,7 @@
     <t>05-050101TP</t>
   </si>
   <si>
-    <t>949da19d905f5c0164705cdbf138b039</t>
+    <t>3e99b032c7ffd9082e7b4646ae3134b8</t>
   </si>
   <si>
     <t>03-030063TC</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>0841f66eec1f7caf51680bed6f5054c6</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2426,7 +2426,7 @@
     <t>05-050313A</t>
   </si>
   <si>
-    <t>b5e4fb67b34969403b416ddbb15a1d24</t>
+    <t>1e9f650233b1837146e626f3c41edea3</t>
   </si>
   <si>
     <t>902-0204-02040102ATC</t>
@@ -2831,7 +2831,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>b405e7a5ca5f41363a4f948ad66e67e7</t>
+    <t>568f02ee5c11b452a06580198ae3fcfd</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2933,7 +2933,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>77c5e8202b4f1481937ffc3459066017</t>
+    <t>df33604063d2187b012a3a687c78f6f7</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -3440,7 +3440,7 @@
     <t>05-050313TP</t>
   </si>
   <si>
-    <t>9f8ae3fc79ca25eb516e02c7d8e9e1ed</t>
+    <t>3c97d05e668859254bf07149cb1a8d06</t>
   </si>
   <si>
     <t>01-010004A</t>
@@ -3467,7 +3467,7 @@
     <t>05-050313TC</t>
   </si>
   <si>
-    <t>25bb50cf2142c3c1efc9273f65308156</t>
+    <t>ed84dfdffacedeec79d20a683308511e</t>
   </si>
   <si>
     <t>01-010028A</t>
@@ -4040,7 +4040,7 @@
     <t>05-050102TP</t>
   </si>
   <si>
-    <t>e8973709aee26ae01b8b5a785784a646</t>
+    <t>90c03a7dd9cf250bec609eba72199372</t>
   </si>
   <si>
     <t>03-030062TC</t>
@@ -4250,7 +4250,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>97bddfc05a36601dd4f26294d424c8d5</t>
+    <t>ad6e173e9e187d4df9db4e9e93687c24</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4265,7 +4265,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>808d4c295a30aa62eac19de0f31ed5b2</t>
+    <t>3a4d48d91fc07d0a8fd7f12c5d10e8e5</t>
   </si>
   <si>
     <t>05-050006TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -179,7 +179,7 @@
     <t>05-050302A</t>
   </si>
   <si>
-    <t>0c865616e57da7ff865bf8e20b4bcf2f</t>
+    <t>a6ed462f4b3da22413d958a0e0aa216f</t>
   </si>
   <si>
     <t>02-020005TC</t>
@@ -647,7 +647,7 @@
     <t>05-050301TP</t>
   </si>
   <si>
-    <t>b314e5a1fa25c9d6ab436413067e54de</t>
+    <t>50799c60fdb747d4279d38bd5b03aeb8</t>
   </si>
   <si>
     <t>05-050301TM</t>
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>708e959fcd99233532b4e728b8ea2a45</t>
+    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>fa4da00ea6ea210b37afd666b7934289</t>
+    <t>fe069915e6896d5ed070ddbadaac6446</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>0d31be08e5da513f79cba3aad4e612db</t>
+    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1748,7 +1748,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>e2f0a39e1ed7d8ae2482944dfdb5b15e</t>
+    <t>b0ac4930ec15dbac39af731b9db4768c</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -1769,7 +1769,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>d9ddd5c3b6ddaab06f18a11561b69053</t>
+    <t>2270685ec7d3a5468017dba19d33c2bd</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -2612,7 +2612,7 @@
     <t>05-050208TC</t>
   </si>
   <si>
-    <t>fab33c8231a9280e35833755f1a2078d</t>
+    <t>4b1b942b40330cd0cc3ceb2b49128d69</t>
   </si>
   <si>
     <t>03-030039A</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>12aa2afe1312739cd170cfbbf6db4bca</t>
+    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -3116,7 +3116,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>8f584d73c1d2ae49a61f6dfe4800c4ef</t>
+    <t>887e5ce461f76ef5d09805b2e0f0c8c3</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -65,7 +65,7 @@
     <t>05-050305TC</t>
   </si>
   <si>
-    <t>ed9acce598ab85c41b400614a877078e</t>
+    <t>bf88958680fd0ad4437263ca6fdb297f</t>
   </si>
   <si>
     <t>03-030002TM</t>
@@ -101,7 +101,7 @@
     <t>05-050207TP</t>
   </si>
   <si>
-    <t>059e8f1eba321846fc43151850338435</t>
+    <t>3f566850f7e1fb5e14efe24cd9262168</t>
   </si>
   <si>
     <t>915-150012A</t>
@@ -113,7 +113,7 @@
     <t>05-050305TP</t>
   </si>
   <si>
-    <t>e4680b930d22d7d95a2e1aff9717d877</t>
+    <t>3be5860e231c20fa27df04eb4ca8cf98</t>
   </si>
   <si>
     <t>05-0709-070921BTP</t>
@@ -152,7 +152,7 @@
     <t>05-050316TC</t>
   </si>
   <si>
-    <t>95bc9b548276ae6f60dc29ef1264f8ed</t>
+    <t>6bf83fd50321eed05183fd05dcc29b85</t>
   </si>
   <si>
     <t>03-030059TP</t>
@@ -206,7 +206,7 @@
     <t>05-050316TP</t>
   </si>
   <si>
-    <t>dce0b1f1d6ed8ddf2e03e86f90a23704</t>
+    <t>bdfa6c8d82452f12b312fe16aed392ed</t>
   </si>
   <si>
     <t>915-150018TP</t>
@@ -680,7 +680,7 @@
     <t>05-050309A</t>
   </si>
   <si>
-    <t>8926a7b4d2655f02eaa2160e49ef96ad</t>
+    <t>dc47d7dcb14346d6d0beb3cbf823be31</t>
   </si>
   <si>
     <t>04-040003TP</t>
@@ -716,7 +716,7 @@
     <t>05-050312TP</t>
   </si>
   <si>
-    <t>e57b169cf0d8d4048e0a76ea4204c296</t>
+    <t>9630a8476f259b238c150ab3f99edf8e</t>
   </si>
   <si>
     <t>05-0709-070954TC</t>
@@ -731,7 +731,7 @@
     <t>05-050312TC</t>
   </si>
   <si>
-    <t>5ad1bafd7c04cb5e92e04db29180a46e</t>
+    <t>ff88d21c9f0b469b698693cda95351e9</t>
   </si>
   <si>
     <t>03-030055TP</t>
@@ -851,7 +851,7 @@
     <t>05-050203TP</t>
   </si>
   <si>
-    <t>2ca64185bfd6830fb10cf73cef34f560</t>
+    <t>d54dc554914eb3eb482791129a9f1b55</t>
   </si>
   <si>
     <t>05-050007TP</t>
@@ -866,7 +866,7 @@
     <t>05-050308A</t>
   </si>
   <si>
-    <t>5ebc226671fdbd07110f027c3fd35fd4</t>
+    <t>cc991a52b705db26dc7a0813407aaf1f</t>
   </si>
   <si>
     <t>05-050203TM</t>
@@ -899,7 +899,7 @@
     <t>05-050203TC</t>
   </si>
   <si>
-    <t>57702b7921554deff2cd45ddaff45c4b</t>
+    <t>460ad78a8776f06c7aa8601798efa385</t>
   </si>
   <si>
     <t>01-110304-11030404A</t>
@@ -926,7 +926,7 @@
     <t>05-050303TP</t>
   </si>
   <si>
-    <t>9bfd60431b45d499946ababbedf265a1</t>
+    <t>1003d58c916678b64c8fb9bc851634d1</t>
   </si>
   <si>
     <t>03-030042TM</t>
@@ -953,7 +953,7 @@
     <t>05-050303TC</t>
   </si>
   <si>
-    <t>4a357f852fdc44460a200c3a02cc839d</t>
+    <t>dacbadc0a71781aab84d5510eb2d5a3a</t>
   </si>
   <si>
     <t>01-010010TP</t>
@@ -971,7 +971,7 @@
     <t>05-050305A</t>
   </si>
   <si>
-    <t>e8cf2322e0111a167c83cdbea9f3e3dd</t>
+    <t>20690ceb1cad475a5b571ca87e928d06</t>
   </si>
   <si>
     <t>04-040001TM</t>
@@ -1013,7 +1013,7 @@
     <t>05-050314TP</t>
   </si>
   <si>
-    <t>38b9da908bdd75aafe2d3c826c744706</t>
+    <t>88af5bf5ace7bc9f41425d4f63be1fa2</t>
   </si>
   <si>
     <t>902-0204-02040102STC</t>
@@ -1055,7 +1055,7 @@
     <t>05-050314TC</t>
   </si>
   <si>
-    <t>b4022141fd796266c0e0b82f212f99c3</t>
+    <t>701ed1d847fae8c7ccd569fc1d79d15f</t>
   </si>
   <si>
     <t>902-0204-02040101ATC</t>
@@ -1064,7 +1064,7 @@
     <t>05-050306A</t>
   </si>
   <si>
-    <t>eccdb284fe64b1be028c8b68764282f5</t>
+    <t>77f66364cc88cbdc1a18e276684ad447</t>
   </si>
   <si>
     <t>902-0204-02040102STP</t>
@@ -1133,7 +1133,7 @@
     <t>05-050303A</t>
   </si>
   <si>
-    <t>f77883a5a8ff0fe4b0d11b07edf654ba</t>
+    <t>149517503b59ddfc3918c862b96b3067</t>
   </si>
   <si>
     <t>05-0709-070910TP</t>
@@ -1208,13 +1208,13 @@
     <t>05-050205TP</t>
   </si>
   <si>
-    <t>57fc0dac869fb3f0d141891a6c9a10c8</t>
+    <t>09dc94ef4f361581164ab3997e67c878</t>
   </si>
   <si>
     <t>05-050304A</t>
   </si>
   <si>
-    <t>8b43d6eb180c63a16e926b8faf7aee0c</t>
+    <t>09420b52977612a4d86a279f940ff25d</t>
   </si>
   <si>
     <t>05-050009TP</t>
@@ -1238,7 +1238,7 @@
     <t>05-050205TC</t>
   </si>
   <si>
-    <t>1bb755195f22abb90b20e6847658bffb</t>
+    <t>add83c8ffd62b5c5fff7be16dae8afaf</t>
   </si>
   <si>
     <t>04-040014TM</t>
@@ -1307,7 +1307,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>786ced3b59d255ed903db148049874c1</t>
+    <t>e0c82a61a67245f79968a744f7b09936</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1466,7 +1466,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>f68caf7517eec411d056e39f6a6bf8e9</t>
+    <t>659242aec416d17e85f02ecbb12330d9</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -1496,7 +1496,7 @@
     <t>05-050201TC</t>
   </si>
   <si>
-    <t>853400072a9a923bb317833eb8e1029d</t>
+    <t>66a9960dc0d88e04f3a96d58130f043c</t>
   </si>
   <si>
     <t>03-030061TP</t>
@@ -1565,7 +1565,7 @@
     <t>05-050310TC</t>
   </si>
   <si>
-    <t>0ce4e02808b8b9e5627f74e5a070f157</t>
+    <t>60115817a4a3be48293379683941555f</t>
   </si>
   <si>
     <t>04-040004A</t>
@@ -1613,7 +1613,7 @@
     <t>05-050310TP</t>
   </si>
   <si>
-    <t>3d60a2d43a3866ef20089508a1ad4cca</t>
+    <t>4fcc2830cebe5ef789159e5ea8813780</t>
   </si>
   <si>
     <t>03-030072TM</t>
@@ -1793,7 +1793,7 @@
     <t>05-050201TP</t>
   </si>
   <si>
-    <t>99e0624f512a37ca64da29d7ceea58e7</t>
+    <t>0f1b7e48d003129c49d1a2059acc209b</t>
   </si>
   <si>
     <t>05-0709-070902TM</t>
@@ -2165,7 +2165,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>db02905784f29aa7e098ab09aa487438</t>
+    <t>2e53c6037ada0a5f4509b5c48de7db82</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2348,7 +2348,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>2765c8f1c87dca50e2ff17335bb53c94</t>
+    <t>cd6d4751cda79df64f498f4b24da5db7</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2420,7 +2420,7 @@
     <t>05-050204A</t>
   </si>
   <si>
-    <t>6a52edd308d0914ca301e2258cd0169c</t>
+    <t>ac412a65c65171b2378eada58b4f3bd5</t>
   </si>
   <si>
     <t>05-050313A</t>
@@ -2519,7 +2519,7 @@
     <t>05-050205A</t>
   </si>
   <si>
-    <t>7cae69c40117095f8c69f95634c88089</t>
+    <t>90ab25c4405ead4ee0afe1b9d14f2107</t>
   </si>
   <si>
     <t>04-040011TM</t>
@@ -2531,7 +2531,7 @@
     <t>05-050314A</t>
   </si>
   <si>
-    <t>d7c9eb3bb1ebb4a091388333d7bd2a92</t>
+    <t>2d6ceb7203356c3b73893edf9cda7000</t>
   </si>
   <si>
     <t>901-010202-9010102021TP</t>
@@ -2663,13 +2663,13 @@
     <t>05-050311A</t>
   </si>
   <si>
-    <t>67ab01d296e75654c21f4739000e956c</t>
+    <t>00659defee040ed572c29c341ea04db5</t>
   </si>
   <si>
     <t>05-050208TP</t>
   </si>
   <si>
-    <t>6e7a711ccd7d38b00285bd320bf93cfa</t>
+    <t>1715ab406c35b7c24e90dcbb31ace64b</t>
   </si>
   <si>
     <t>901-010202-9010102022A</t>
@@ -2693,7 +2693,7 @@
     <t>05-050306TP</t>
   </si>
   <si>
-    <t>2cfe0f1373d2ec03ad6aa6b88c28f516</t>
+    <t>e71bf6219416afaac82fb6bc9f5e2fa3</t>
   </si>
   <si>
     <t>905-9050607-905060701TC</t>
@@ -2732,13 +2732,13 @@
     <t>05-050317TC</t>
   </si>
   <si>
-    <t>4bd2f562bbbac4f175d158a4b2977ab2</t>
+    <t>7067f67b2942213b4d4713364e70ae2e</t>
   </si>
   <si>
     <t>05-050312A</t>
   </si>
   <si>
-    <t>a89528d3176a4dbcfe7c017e954a5ab5</t>
+    <t>a9630c418c3f59d6a1b0b360a841ebf0</t>
   </si>
   <si>
     <t>05-050009A</t>
@@ -2750,7 +2750,7 @@
     <t>05-050203A</t>
   </si>
   <si>
-    <t>c56df910e4fed527df2ddd7eb4892484</t>
+    <t>60ddfdefed4769e4fc5a58fc7044c3e5</t>
   </si>
   <si>
     <t>01-080101-010087TM</t>
@@ -2789,7 +2789,7 @@
     <t>05-050317TP</t>
   </si>
   <si>
-    <t>6d93fcf9e0612fa89a7a361894e88df5</t>
+    <t>229410bf60ee30df3fa138b86e565bc4</t>
   </si>
   <si>
     <t>01-010051TC</t>
@@ -2900,7 +2900,7 @@
     <t>05-050201A</t>
   </si>
   <si>
-    <t>053e9979a929718be152a7b44a18f23b</t>
+    <t>7f4dc12e25c618f37e507de07c1df792</t>
   </si>
   <si>
     <t>04-040020TC</t>
@@ -2915,7 +2915,7 @@
     <t>05-050310A</t>
   </si>
   <si>
-    <t>7f53db899963dee22e9ba6497c61010b</t>
+    <t>41669038dfc6b535dfbec046e1d33aa1</t>
   </si>
   <si>
     <t>915-150008TP</t>
@@ -2990,7 +2990,7 @@
     <t>05-050308TC</t>
   </si>
   <si>
-    <t>63ebd04f7f4961c0d42926a65412ba4a</t>
+    <t>c6b34662dbb3d73f48d62ae6dbde660d</t>
   </si>
   <si>
     <t>02-020002TC</t>
@@ -3008,7 +3008,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>fa298e244c4126c3d7361f58970d83c5</t>
+    <t>134162bc7e138f3db345fa90ad9f1a3d</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3044,7 +3044,7 @@
     <t>05-050308TP</t>
   </si>
   <si>
-    <t>6f945d891b1b07a146ded54fbb93459b</t>
+    <t>e6f48497af448ef49af760d78c76a34e</t>
   </si>
   <si>
     <t>03-030035A</t>
@@ -3275,7 +3275,7 @@
     <t>05-050204TP</t>
   </si>
   <si>
-    <t>e161a2fa2ee9400f268f365465bde9d9</t>
+    <t>f27901d9c6928abaa5448bc98fd3c169</t>
   </si>
   <si>
     <t>915-150007A</t>
@@ -3329,7 +3329,7 @@
     <t>05-050204TC</t>
   </si>
   <si>
-    <t>61bfb6dfbb9345ec8f1be50c3d1d8590</t>
+    <t>29a2a7a244786b74b0f5a6bbb50b99de</t>
   </si>
   <si>
     <t>04-040015TM</t>
@@ -3365,7 +3365,7 @@
     <t>05-050302TC</t>
   </si>
   <si>
-    <t>8681f7b889429514746ff6849c36e77e</t>
+    <t>72c1a8e6f3d566ecac609952c138676c</t>
   </si>
   <si>
     <t>01-110304-11030403TP</t>
@@ -3512,13 +3512,13 @@
     <t>05-050208A</t>
   </si>
   <si>
-    <t>85cdec942922fd1be3bcf4d0623befca</t>
+    <t>4a0a1f70e7364e195cef4517668fda56</t>
   </si>
   <si>
     <t>05-050317A</t>
   </si>
   <si>
-    <t>fca18a2901952950103d43ab77236f8c</t>
+    <t>8698bccf05cce2f5667bf3d4c8455e29</t>
   </si>
   <si>
     <t>01-010027A</t>
@@ -3584,7 +3584,7 @@
     <t>05-050206TP</t>
   </si>
   <si>
-    <t>52e22e2e5aa4e0749a78e40333915b33</t>
+    <t>a6c0778e5c6025b5eca2a3b5364d1036</t>
   </si>
   <si>
     <t>01-010068TM</t>
@@ -3608,7 +3608,7 @@
     <t>05-050206TC</t>
   </si>
   <si>
-    <t>2cad2a7bf53ea3238fa8405eecf65ea3</t>
+    <t>e0fadaae9e7a01f3914884584a6b7517</t>
   </si>
   <si>
     <t>04-040013TM</t>
@@ -3692,7 +3692,7 @@
     <t>05-050304TC</t>
   </si>
   <si>
-    <t>09c2ea614878074519969e3138174001</t>
+    <t>c4fe35ca784828d1893f420a8d6d2832</t>
   </si>
   <si>
     <t>03-030043TP</t>
@@ -3704,13 +3704,13 @@
     <t>05-050206A</t>
   </si>
   <si>
-    <t>6be39dc7d3f370598bac8b3e04944505</t>
+    <t>ef1f7bc09084fe7e760fcd662b2c9eec</t>
   </si>
   <si>
     <t>05-050315A</t>
   </si>
   <si>
-    <t>ea364ee5492aec3427b2f883e19dea73</t>
+    <t>432f2b12e1f6894d2d49d0752077aa1d</t>
   </si>
   <si>
     <t>902-0204-02040101STP</t>
@@ -3773,7 +3773,7 @@
     <t>05-050304TP</t>
   </si>
   <si>
-    <t>0c351ffaffde51c6347d401a693f8eee</t>
+    <t>62150c20d121c8274d6f90ed3903f51d</t>
   </si>
   <si>
     <t>04-040002TP</t>
@@ -3821,7 +3821,7 @@
     <t>05-050315TC</t>
   </si>
   <si>
-    <t>4f3388340ea7f4a2af6d438266c16a79</t>
+    <t>3460c0548689483b7415f521fbf687cb</t>
   </si>
   <si>
     <t>01-010046TM</t>
@@ -3836,7 +3836,7 @@
     <t>05-050316A</t>
   </si>
   <si>
-    <t>1dfdd5679f7ee319e320d406aa4ca709</t>
+    <t>5e4ab72ee31126c82067e63326a6968e</t>
   </si>
   <si>
     <t>902-0204-02040101BTC</t>
@@ -3860,7 +3860,7 @@
     <t>05-050207A</t>
   </si>
   <si>
-    <t>d9f4f2892bdd8d80380caf4dcc428307</t>
+    <t>8cbba115c0d3741f462453bd485fd304</t>
   </si>
   <si>
     <t>02-020006TM</t>
@@ -3911,7 +3911,7 @@
     <t>05-050315TP</t>
   </si>
   <si>
-    <t>44e3088d57e75072827ee3ee130b7943</t>
+    <t>d74eb364d395241e4a88ce4dd643a1b4</t>
   </si>
   <si>
     <t>03-030040TP</t>
@@ -3983,7 +3983,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>05089a667705b6ff52f21f0a6990ad9b</t>
+    <t>e43456585f774ed373438d7ef49f2aa3</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4004,7 +4004,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>41bf80ef7c81b0a5661624678ccde1ca</t>
+    <t>f43b4a6f7cc8bf13c3a92b4b7f8e726d</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4133,7 +4133,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>b0c2a18df112b9f277fecaa6a1e00eb7</t>
+    <t>ea579b3f30efb72eb919c6a56f538c3e</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4325,7 +4325,7 @@
     <t>05-050202TC</t>
   </si>
   <si>
-    <t>ec29680cb56f42a64a35dbc3449c2575</t>
+    <t>58fca060a06c31d35ca37b7b32ae2d13</t>
   </si>
   <si>
     <t>03-030062TP</t>
@@ -4343,7 +4343,7 @@
     <t>05-050311TC</t>
   </si>
   <si>
-    <t>9ac516dcbe0b313e4b36eb8426ea47b9</t>
+    <t>7522cf9fbb024ae1c150b2151111be09</t>
   </si>
   <si>
     <t>04-040014A</t>
@@ -4370,7 +4370,7 @@
     <t>05-050311TP</t>
   </si>
   <si>
-    <t>1affb1ed2822a12b159e8df078bf0975</t>
+    <t>fa838f54022d6a8979ed747fda2cb32f</t>
   </si>
   <si>
     <t>01-080101-010081TC</t>
@@ -4469,13 +4469,13 @@
     <t>05-050309TC</t>
   </si>
   <si>
-    <t>6ca08574d86ae3aa9d7e5c47c265b84a</t>
+    <t>186b1a836d5aa29ca4cd018da9200e46</t>
   </si>
   <si>
     <t>05-050002A</t>
   </si>
   <si>
-    <t>42ae2ecbbe95475185886ba7eb9ed1f7</t>
+    <t>7509b2ca97b6b009aa96ff8bb2d842d5</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4505,7 +4505,7 @@
     <t>05-050309TP</t>
   </si>
   <si>
-    <t>4674a84d8a29ca83aa949ac49fbfc93a</t>
+    <t>1a091c654aec82de978d555c663bab50</t>
   </si>
   <si>
     <t>05-050309TM</t>
@@ -4532,7 +4532,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>6f6df58ed26c3b04d4a1451cd1752a17</t>
+    <t>2a07bf6c6c1eb49dfac0a251abbaf02f</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4736,7 +4736,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>f39c13e6a0c461b855c0c6328d15b4d7</t>
+    <t>ee1b5d5b8ff266973aaea21d50fad9fa</t>
   </si>
   <si>
     <t>01-010006TM</t>
@@ -4871,7 +4871,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>e64797a2cb3edeb4ee2d3a9ac5c7bd75</t>
+    <t>fa45adef370f900924977faca8daa50d</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2657,7 +2657,7 @@
     <t>05-050202A</t>
   </si>
   <si>
-    <t>4082473e455ea2efcc317070f655c008</t>
+    <t>dcedc3bb0496b5514f1f455c2762bfbb</t>
   </si>
   <si>
     <t>05-050311A</t>
@@ -3338,7 +3338,7 @@
     <t>05-050302TP</t>
   </si>
   <si>
-    <t>197c0b9cfac61b90cfd77d9e3b15133c</t>
+    <t>8e139870df3053cfbb1e578385924988</t>
   </si>
   <si>
     <t>01-010055TM</t>
@@ -4286,7 +4286,7 @@
     <t>05-050202TP</t>
   </si>
   <si>
-    <t>7f3c93123e6807038cd5a33a137219fe</t>
+    <t>e54e7c48877447368243eafb48fab8ff</t>
   </si>
   <si>
     <t>05-0709-070903TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -662,7 +662,7 @@
     <t>05-050301TC</t>
   </si>
   <si>
-    <t>1a3f1505868feb8a19f6cbcdfc804738</t>
+    <t>3f3cb0272d91d93b8d9910216dd98b56</t>
   </si>
   <si>
     <t>01-010054TP</t>
@@ -1748,7 +1748,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>b0ac4930ec15dbac39af731b9db4768c</t>
+    <t>0e6c865ef608c20883124ef0380127e2</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>d878f735a89572d2273c1e98708e28dd</t>
+    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -1748,7 +1748,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>0e6c865ef608c20883124ef0380127e2</t>
+    <t>b0ac4930ec15dbac39af731b9db4768c</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>0841f66eec1f7caf51680bed6f5054c6</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -827,7 +827,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>84f9177b78615335c74de6904e2acd32</t>
+    <t>14dc6a7115ed8643d0342c17efbddf27</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -857,7 +857,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>ab0ea17fae2aec0703ccc1e868a613be</t>
+    <t>546191a602cd86ccda80feba3dc550d8</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
+    <t>e485342c765c36244fab6a0d410188bb</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>fe069915e6896d5ed070ddbadaac6446</t>
+    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
+    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1307,7 +1307,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>e0c82a61a67245f79968a744f7b09936</t>
+    <t>accee517f3d37c3718bdd35d130fdb09</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1466,7 +1466,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>659242aec416d17e85f02ecbb12330d9</t>
+    <t>d03a41d30eaa290a2df7d86128170fc8</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
+    <t>397f95ff13cb7f56235d92785ac466a5</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -2831,7 +2831,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>568f02ee5c11b452a06580198ae3fcfd</t>
+    <t>bce246d0f326510acf85215689732b93</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2933,7 +2933,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>df33604063d2187b012a3a687c78f6f7</t>
+    <t>c178e29df4f7707ac5dd97e5dfb43e98</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -3983,7 +3983,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>e43456585f774ed373438d7ef49f2aa3</t>
+    <t>cb9274c9525c17ea68bb2adb72b918b2</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4250,7 +4250,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>ad6e173e9e187d4df9db4e9e93687c24</t>
+    <t>ff983b6dba0a7b6b341e82f792b83e5f</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4265,7 +4265,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>3a4d48d91fc07d0a8fd7f12c5d10e8e5</t>
+    <t>f13308e69a2d1e8b94c4a1516c7a0cc4</t>
   </si>
   <si>
     <t>05-050006TM</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>d878f735a89572d2273c1e98708e28dd</t>
+    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
   </si>
   <si>
     <t>03-030060TP</t>
@@ -4871,7 +4871,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>fa45adef370f900924977faca8daa50d</t>
+    <t>166e7d248577a16ab1474b1ad6135ff9</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -827,7 +827,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>14dc6a7115ed8643d0342c17efbddf27</t>
+    <t>84f9177b78615335c74de6904e2acd32</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -857,7 +857,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>546191a602cd86ccda80feba3dc550d8</t>
+    <t>ab0ea17fae2aec0703ccc1e868a613be</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>e485342c765c36244fab6a0d410188bb</t>
+    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
+    <t>fe069915e6896d5ed070ddbadaac6446</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
+    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1307,7 +1307,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>accee517f3d37c3718bdd35d130fdb09</t>
+    <t>e0c82a61a67245f79968a744f7b09936</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1466,7 +1466,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>d03a41d30eaa290a2df7d86128170fc8</t>
+    <t>659242aec416d17e85f02ecbb12330d9</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -2165,7 +2165,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>2e53c6037ada0a5f4509b5c48de7db82</t>
+    <t>222036ac958a83c91ac7ee20641a3bcd</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>0841f66eec1f7caf51680bed6f5054c6</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2348,7 +2348,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>cd6d4751cda79df64f498f4b24da5db7</t>
+    <t>56b006ec8a69efa8ace08d6c37cc8aab</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>397f95ff13cb7f56235d92785ac466a5</t>
+    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -2831,7 +2831,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>bce246d0f326510acf85215689732b93</t>
+    <t>568f02ee5c11b452a06580198ae3fcfd</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2933,7 +2933,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>c178e29df4f7707ac5dd97e5dfb43e98</t>
+    <t>df33604063d2187b012a3a687c78f6f7</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -3008,7 +3008,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>134162bc7e138f3db345fa90ad9f1a3d</t>
+    <t>ea84c9018e64e1a60956b7b5ea05c98d</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3983,7 +3983,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>cb9274c9525c17ea68bb2adb72b918b2</t>
+    <t>e43456585f774ed373438d7ef49f2aa3</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4004,7 +4004,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>f43b4a6f7cc8bf13c3a92b4b7f8e726d</t>
+    <t>b0d983bda09391468dcc9b39c3bfbd4b</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4133,7 +4133,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>ea579b3f30efb72eb919c6a56f538c3e</t>
+    <t>98a8d5220c099a28a1f4102ef82c39cb</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4250,7 +4250,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>ff983b6dba0a7b6b341e82f792b83e5f</t>
+    <t>ad6e173e9e187d4df9db4e9e93687c24</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4265,7 +4265,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>f13308e69a2d1e8b94c4a1516c7a0cc4</t>
+    <t>3a4d48d91fc07d0a8fd7f12c5d10e8e5</t>
   </si>
   <si>
     <t>05-050006TM</t>
@@ -4475,7 +4475,7 @@
     <t>05-050002A</t>
   </si>
   <si>
-    <t>7509b2ca97b6b009aa96ff8bb2d842d5</t>
+    <t>29e2d68caa84824815942fcbb7de8fcb</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4532,7 +4532,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>2a07bf6c6c1eb49dfac0a251abbaf02f</t>
+    <t>26d18c3464dd106a56836bfa4eab269a</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4736,7 +4736,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>ee1b5d5b8ff266973aaea21d50fad9fa</t>
+    <t>4e0e765b29a9b7c15fa8c3babf7ab96b</t>
   </si>
   <si>
     <t>01-010006TM</t>
@@ -4871,7 +4871,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>166e7d248577a16ab1474b1ad6135ff9</t>
+    <t>fa45adef370f900924977faca8daa50d</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -827,7 +827,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>84f9177b78615335c74de6904e2acd32</t>
+    <t>14dc6a7115ed8643d0342c17efbddf27</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -857,7 +857,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>ab0ea17fae2aec0703ccc1e868a613be</t>
+    <t>546191a602cd86ccda80feba3dc550d8</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
+    <t>e485342c765c36244fab6a0d410188bb</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>fe069915e6896d5ed070ddbadaac6446</t>
+    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
+    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1307,7 +1307,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>e0c82a61a67245f79968a744f7b09936</t>
+    <t>accee517f3d37c3718bdd35d130fdb09</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1466,7 +1466,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>659242aec416d17e85f02ecbb12330d9</t>
+    <t>d03a41d30eaa290a2df7d86128170fc8</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -1769,7 +1769,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>2270685ec7d3a5468017dba19d33c2bd</t>
+    <t>258d3ef813ddad27f7ba8abc6388b27b</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -2165,7 +2165,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>222036ac958a83c91ac7ee20641a3bcd</t>
+    <t>2e53c6037ada0a5f4509b5c48de7db82</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2348,7 +2348,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>56b006ec8a69efa8ace08d6c37cc8aab</t>
+    <t>cd6d4751cda79df64f498f4b24da5db7</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
+    <t>397f95ff13cb7f56235d92785ac466a5</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -2831,7 +2831,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>568f02ee5c11b452a06580198ae3fcfd</t>
+    <t>bce246d0f326510acf85215689732b93</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2933,7 +2933,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>df33604063d2187b012a3a687c78f6f7</t>
+    <t>c178e29df4f7707ac5dd97e5dfb43e98</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -3008,7 +3008,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>ea84c9018e64e1a60956b7b5ea05c98d</t>
+    <t>134162bc7e138f3db345fa90ad9f1a3d</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3116,7 +3116,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>887e5ce461f76ef5d09805b2e0f0c8c3</t>
+    <t>d07887befe6d56766f32d3ba049af99e</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -3983,7 +3983,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>e43456585f774ed373438d7ef49f2aa3</t>
+    <t>cb9274c9525c17ea68bb2adb72b918b2</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4004,7 +4004,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>b0d983bda09391468dcc9b39c3bfbd4b</t>
+    <t>f43b4a6f7cc8bf13c3a92b4b7f8e726d</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4133,7 +4133,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>98a8d5220c099a28a1f4102ef82c39cb</t>
+    <t>ea579b3f30efb72eb919c6a56f538c3e</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4250,7 +4250,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>ad6e173e9e187d4df9db4e9e93687c24</t>
+    <t>ff983b6dba0a7b6b341e82f792b83e5f</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4265,7 +4265,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>3a4d48d91fc07d0a8fd7f12c5d10e8e5</t>
+    <t>f13308e69a2d1e8b94c4a1516c7a0cc4</t>
   </si>
   <si>
     <t>05-050006TM</t>
@@ -4475,7 +4475,7 @@
     <t>05-050002A</t>
   </si>
   <si>
-    <t>29e2d68caa84824815942fcbb7de8fcb</t>
+    <t>7509b2ca97b6b009aa96ff8bb2d842d5</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4532,7 +4532,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>26d18c3464dd106a56836bfa4eab269a</t>
+    <t>2a07bf6c6c1eb49dfac0a251abbaf02f</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4736,7 +4736,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>4e0e765b29a9b7c15fa8c3babf7ab96b</t>
+    <t>ee1b5d5b8ff266973aaea21d50fad9fa</t>
   </si>
   <si>
     <t>01-010006TM</t>
@@ -4871,7 +4871,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>fa45adef370f900924977faca8daa50d</t>
+    <t>166e7d248577a16ab1474b1ad6135ff9</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -827,7 +827,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>14dc6a7115ed8643d0342c17efbddf27</t>
+    <t>84f9177b78615335c74de6904e2acd32</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -857,7 +857,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>546191a602cd86ccda80feba3dc550d8</t>
+    <t>ab0ea17fae2aec0703ccc1e868a613be</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1307,7 +1307,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>accee517f3d37c3718bdd35d130fdb09</t>
+    <t>e0c82a61a67245f79968a744f7b09936</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1466,7 +1466,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>d03a41d30eaa290a2df7d86128170fc8</t>
+    <t>659242aec416d17e85f02ecbb12330d9</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -1769,7 +1769,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>258d3ef813ddad27f7ba8abc6388b27b</t>
+    <t>2270685ec7d3a5468017dba19d33c2bd</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -2831,7 +2831,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>bce246d0f326510acf85215689732b93</t>
+    <t>568f02ee5c11b452a06580198ae3fcfd</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2933,7 +2933,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>c178e29df4f7707ac5dd97e5dfb43e98</t>
+    <t>df33604063d2187b012a3a687c78f6f7</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -3116,7 +3116,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>d07887befe6d56766f32d3ba049af99e</t>
+    <t>887e5ce461f76ef5d09805b2e0f0c8c3</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -3983,7 +3983,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>cb9274c9525c17ea68bb2adb72b918b2</t>
+    <t>e43456585f774ed373438d7ef49f2aa3</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4250,7 +4250,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>ff983b6dba0a7b6b341e82f792b83e5f</t>
+    <t>ad6e173e9e187d4df9db4e9e93687c24</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4265,7 +4265,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>f13308e69a2d1e8b94c4a1516c7a0cc4</t>
+    <t>3a4d48d91fc07d0a8fd7f12c5d10e8e5</t>
   </si>
   <si>
     <t>05-050006TM</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>
@@ -4871,7 +4871,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>166e7d248577a16ab1474b1ad6135ff9</t>
+    <t>fa45adef370f900924977faca8daa50d</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>e485342c765c36244fab6a0d410188bb</t>
+    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
+    <t>fe069915e6896d5ed070ddbadaac6446</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
+    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1307,7 +1307,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>e0c82a61a67245f79968a744f7b09936</t>
+    <t>accee517f3d37c3718bdd35d130fdb09</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1466,7 +1466,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>659242aec416d17e85f02ecbb12330d9</t>
+    <t>d03a41d30eaa290a2df7d86128170fc8</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -2165,7 +2165,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>2e53c6037ada0a5f4509b5c48de7db82</t>
+    <t>222036ac958a83c91ac7ee20641a3bcd</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>0841f66eec1f7caf51680bed6f5054c6</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2348,7 +2348,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>cd6d4751cda79df64f498f4b24da5db7</t>
+    <t>56b006ec8a69efa8ace08d6c37cc8aab</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>397f95ff13cb7f56235d92785ac466a5</t>
+    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -3008,7 +3008,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>134162bc7e138f3db345fa90ad9f1a3d</t>
+    <t>ea84c9018e64e1a60956b7b5ea05c98d</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3983,7 +3983,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>e43456585f774ed373438d7ef49f2aa3</t>
+    <t>cb9274c9525c17ea68bb2adb72b918b2</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4004,7 +4004,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>f43b4a6f7cc8bf13c3a92b4b7f8e726d</t>
+    <t>b0d983bda09391468dcc9b39c3bfbd4b</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4133,7 +4133,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>ea579b3f30efb72eb919c6a56f538c3e</t>
+    <t>98a8d5220c099a28a1f4102ef82c39cb</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4475,7 +4475,7 @@
     <t>05-050002A</t>
   </si>
   <si>
-    <t>7509b2ca97b6b009aa96ff8bb2d842d5</t>
+    <t>29e2d68caa84824815942fcbb7de8fcb</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4532,7 +4532,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>2a07bf6c6c1eb49dfac0a251abbaf02f</t>
+    <t>26d18c3464dd106a56836bfa4eab269a</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>d878f735a89572d2273c1e98708e28dd</t>
+    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
   </si>
   <si>
     <t>03-030060TP</t>
@@ -4736,7 +4736,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>ee1b5d5b8ff266973aaea21d50fad9fa</t>
+    <t>4e0e765b29a9b7c15fa8c3babf7ab96b</t>
   </si>
   <si>
     <t>01-010006TM</t>
@@ -4871,7 +4871,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>fa45adef370f900924977faca8daa50d</t>
+    <t>166e7d248577a16ab1474b1ad6135ff9</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
+    <t>e485342c765c36244fab6a0d410188bb</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>fe069915e6896d5ed070ddbadaac6446</t>
+    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
+    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1307,7 +1307,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>accee517f3d37c3718bdd35d130fdb09</t>
+    <t>e0c82a61a67245f79968a744f7b09936</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1466,7 +1466,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>d03a41d30eaa290a2df7d86128170fc8</t>
+    <t>659242aec416d17e85f02ecbb12330d9</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -1748,7 +1748,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>b0ac4930ec15dbac39af731b9db4768c</t>
+    <t>0e6c865ef608c20883124ef0380127e2</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
+    <t>397f95ff13cb7f56235d92785ac466a5</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -3983,7 +3983,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>cb9274c9525c17ea68bb2adb72b918b2</t>
+    <t>e43456585f774ed373438d7ef49f2aa3</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>
@@ -4871,7 +4871,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>166e7d248577a16ab1474b1ad6135ff9</t>
+    <t>fa45adef370f900924977faca8daa50d</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>e485342c765c36244fab6a0d410188bb</t>
+    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
+    <t>fe069915e6896d5ed070ddbadaac6446</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
+    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1748,7 +1748,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>0e6c865ef608c20883124ef0380127e2</t>
+    <t>b0ac4930ec15dbac39af731b9db4768c</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -2165,7 +2165,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>222036ac958a83c91ac7ee20641a3bcd</t>
+    <t>2e53c6037ada0a5f4509b5c48de7db82</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>0841f66eec1f7caf51680bed6f5054c6</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2348,7 +2348,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>56b006ec8a69efa8ace08d6c37cc8aab</t>
+    <t>cd6d4751cda79df64f498f4b24da5db7</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>397f95ff13cb7f56235d92785ac466a5</t>
+    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -3008,7 +3008,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>ea84c9018e64e1a60956b7b5ea05c98d</t>
+    <t>134162bc7e138f3db345fa90ad9f1a3d</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -4004,7 +4004,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>b0d983bda09391468dcc9b39c3bfbd4b</t>
+    <t>f43b4a6f7cc8bf13c3a92b4b7f8e726d</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4133,7 +4133,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>98a8d5220c099a28a1f4102ef82c39cb</t>
+    <t>ea579b3f30efb72eb919c6a56f538c3e</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4475,7 +4475,7 @@
     <t>05-050002A</t>
   </si>
   <si>
-    <t>29e2d68caa84824815942fcbb7de8fcb</t>
+    <t>7509b2ca97b6b009aa96ff8bb2d842d5</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4532,7 +4532,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>26d18c3464dd106a56836bfa4eab269a</t>
+    <t>2a07bf6c6c1eb49dfac0a251abbaf02f</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4736,7 +4736,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>4e0e765b29a9b7c15fa8c3babf7ab96b</t>
+    <t>ee1b5d5b8ff266973aaea21d50fad9fa</t>
   </si>
   <si>
     <t>01-010006TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -827,7 +827,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>84f9177b78615335c74de6904e2acd32</t>
+    <t>14dc6a7115ed8643d0342c17efbddf27</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -857,7 +857,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>ab0ea17fae2aec0703ccc1e868a613be</t>
+    <t>546191a602cd86ccda80feba3dc550d8</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
+    <t>e485342c765c36244fab6a0d410188bb</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>fe069915e6896d5ed070ddbadaac6446</t>
+    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
+    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1457,7 +1457,7 @@
     <t>05-050003TM</t>
   </si>
   <si>
-    <t>a996d4ebbf0fd8d2ceecd7b76c1e4798</t>
+    <t>26a174eb39b463d9fb80104d5dee9319</t>
   </si>
   <si>
     <t>01-010025TM</t>
@@ -1748,7 +1748,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>b0ac4930ec15dbac39af731b9db4768c</t>
+    <t>0e6c865ef608c20883124ef0380127e2</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -1769,7 +1769,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>2270685ec7d3a5468017dba19d33c2bd</t>
+    <t>258d3ef813ddad27f7ba8abc6388b27b</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -2165,7 +2165,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>2e53c6037ada0a5f4509b5c48de7db82</t>
+    <t>222036ac958a83c91ac7ee20641a3bcd</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2348,7 +2348,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>cd6d4751cda79df64f498f4b24da5db7</t>
+    <t>56b006ec8a69efa8ace08d6c37cc8aab</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
+    <t>397f95ff13cb7f56235d92785ac466a5</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -2831,7 +2831,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>568f02ee5c11b452a06580198ae3fcfd</t>
+    <t>bce246d0f326510acf85215689732b93</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2933,7 +2933,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>df33604063d2187b012a3a687c78f6f7</t>
+    <t>c178e29df4f7707ac5dd97e5dfb43e98</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -3008,7 +3008,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>134162bc7e138f3db345fa90ad9f1a3d</t>
+    <t>ea84c9018e64e1a60956b7b5ea05c98d</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3116,7 +3116,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>887e5ce461f76ef5d09805b2e0f0c8c3</t>
+    <t>d07887befe6d56766f32d3ba049af99e</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -4004,7 +4004,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>f43b4a6f7cc8bf13c3a92b4b7f8e726d</t>
+    <t>b0d983bda09391468dcc9b39c3bfbd4b</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4133,7 +4133,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>ea579b3f30efb72eb919c6a56f538c3e</t>
+    <t>98a8d5220c099a28a1f4102ef82c39cb</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4250,7 +4250,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>ad6e173e9e187d4df9db4e9e93687c24</t>
+    <t>ff983b6dba0a7b6b341e82f792b83e5f</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4265,7 +4265,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>3a4d48d91fc07d0a8fd7f12c5d10e8e5</t>
+    <t>f13308e69a2d1e8b94c4a1516c7a0cc4</t>
   </si>
   <si>
     <t>05-050006TM</t>
@@ -4475,7 +4475,7 @@
     <t>05-050002A</t>
   </si>
   <si>
-    <t>7509b2ca97b6b009aa96ff8bb2d842d5</t>
+    <t>29e2d68caa84824815942fcbb7de8fcb</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4532,7 +4532,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>2a07bf6c6c1eb49dfac0a251abbaf02f</t>
+    <t>26d18c3464dd106a56836bfa4eab269a</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4736,7 +4736,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>ee1b5d5b8ff266973aaea21d50fad9fa</t>
+    <t>4e0e765b29a9b7c15fa8c3babf7ab96b</t>
   </si>
   <si>
     <t>01-010006TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -827,7 +827,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>14dc6a7115ed8643d0342c17efbddf27</t>
+    <t>84f9177b78615335c74de6904e2acd32</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -857,7 +857,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>546191a602cd86ccda80feba3dc550d8</t>
+    <t>ab0ea17fae2aec0703ccc1e868a613be</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>e485342c765c36244fab6a0d410188bb</t>
+    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
+    <t>fe069915e6896d5ed070ddbadaac6446</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
+    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1748,7 +1748,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>0e6c865ef608c20883124ef0380127e2</t>
+    <t>b0ac4930ec15dbac39af731b9db4768c</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -1769,7 +1769,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>258d3ef813ddad27f7ba8abc6388b27b</t>
+    <t>2270685ec7d3a5468017dba19d33c2bd</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>0841f66eec1f7caf51680bed6f5054c6</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>397f95ff13cb7f56235d92785ac466a5</t>
+    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -2831,7 +2831,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>bce246d0f326510acf85215689732b93</t>
+    <t>568f02ee5c11b452a06580198ae3fcfd</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2933,7 +2933,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>c178e29df4f7707ac5dd97e5dfb43e98</t>
+    <t>df33604063d2187b012a3a687c78f6f7</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -3116,7 +3116,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>d07887befe6d56766f32d3ba049af99e</t>
+    <t>887e5ce461f76ef5d09805b2e0f0c8c3</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -4250,7 +4250,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>ff983b6dba0a7b6b341e82f792b83e5f</t>
+    <t>ad6e173e9e187d4df9db4e9e93687c24</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4265,7 +4265,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>f13308e69a2d1e8b94c4a1516c7a0cc4</t>
+    <t>3a4d48d91fc07d0a8fd7f12c5d10e8e5</t>
   </si>
   <si>
     <t>05-050006TM</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>d878f735a89572d2273c1e98708e28dd</t>
+    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -1178,7 +1178,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>6afc8b7b89d7b6de5b1f057617bf949e</t>
+    <t>e485342c765c36244fab6a0d410188bb</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1196,7 +1196,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>fe069915e6896d5ed070ddbadaac6446</t>
+    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>3c21b8271b2dc768c843ffbf8ff5324f</t>
+    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1748,7 +1748,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>b0ac4930ec15dbac39af731b9db4768c</t>
+    <t>0e6c865ef608c20883124ef0380127e2</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2744,7 +2744,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>99021a89849f7c14eb47cfe4d4b3107d</t>
+    <t>397f95ff13cb7f56235d92785ac466a5</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -827,7 +827,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>84f9177b78615335c74de6904e2acd32</t>
+    <t>14dc6a7115ed8643d0342c17efbddf27</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -857,7 +857,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>ab0ea17fae2aec0703ccc1e868a613be</t>
+    <t>546191a602cd86ccda80feba3dc550d8</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -2831,7 +2831,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>568f02ee5c11b452a06580198ae3fcfd</t>
+    <t>bce246d0f326510acf85215689732b93</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2933,7 +2933,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>df33604063d2187b012a3a687c78f6f7</t>
+    <t>c178e29df4f7707ac5dd97e5dfb43e98</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -4250,7 +4250,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>ad6e173e9e187d4df9db4e9e93687c24</t>
+    <t>ff983b6dba0a7b6b341e82f792b83e5f</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4265,7 +4265,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>3a4d48d91fc07d0a8fd7f12c5d10e8e5</t>
+    <t>f13308e69a2d1e8b94c4a1516c7a0cc4</t>
   </si>
   <si>
     <t>05-050006TM</t>
@@ -4556,7 +4556,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>d878f735a89572d2273c1e98708e28dd</t>
+    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -1769,7 +1769,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>2270685ec7d3a5468017dba19d33c2bd</t>
+    <t>258d3ef813ddad27f7ba8abc6388b27b</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -2165,7 +2165,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>222036ac958a83c91ac7ee20641a3bcd</t>
+    <t>2e53c6037ada0a5f4509b5c48de7db82</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2348,7 +2348,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>56b006ec8a69efa8ace08d6c37cc8aab</t>
+    <t>cd6d4751cda79df64f498f4b24da5db7</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -3008,7 +3008,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>ea84c9018e64e1a60956b7b5ea05c98d</t>
+    <t>134162bc7e138f3db345fa90ad9f1a3d</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3116,7 +3116,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>887e5ce461f76ef5d09805b2e0f0c8c3</t>
+    <t>d07887befe6d56766f32d3ba049af99e</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -4004,7 +4004,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>b0d983bda09391468dcc9b39c3bfbd4b</t>
+    <t>f43b4a6f7cc8bf13c3a92b4b7f8e726d</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4133,7 +4133,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>98a8d5220c099a28a1f4102ef82c39cb</t>
+    <t>ea579b3f30efb72eb919c6a56f538c3e</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4475,7 +4475,7 @@
     <t>05-050002A</t>
   </si>
   <si>
-    <t>29e2d68caa84824815942fcbb7de8fcb</t>
+    <t>7509b2ca97b6b009aa96ff8bb2d842d5</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4532,7 +4532,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>26d18c3464dd106a56836bfa4eab269a</t>
+    <t>2a07bf6c6c1eb49dfac0a251abbaf02f</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4736,7 +4736,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>4e0e765b29a9b7c15fa8c3babf7ab96b</t>
+    <t>ee1b5d5b8ff266973aaea21d50fad9fa</t>
   </si>
   <si>
     <t>01-010006TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2210,7 +2210,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1681">
   <si>
     <t>05-050305TM</t>
   </si>
@@ -878,6 +878,9 @@
     <t>04-040021A</t>
   </si>
   <si>
+    <t>256ebcd7c18287ed9edb6e1583c0bb11</t>
+  </si>
+  <si>
     <t>01-010016A</t>
   </si>
   <si>
@@ -4160,6 +4163,9 @@
     <t>04-040017A</t>
   </si>
   <si>
+    <t>020ff562b8d75c8031c023584adeec5d</t>
+  </si>
+  <si>
     <t>01-010002TM</t>
   </si>
   <si>
@@ -4349,7 +4355,7 @@
     <t>04-040014A</t>
   </si>
   <si>
-    <t>1b6ed3b3a92747c4d0e386b2f9f87036</t>
+    <t>3bbeda48cc454f005a899945f7dbc5cd</t>
   </si>
   <si>
     <t>03-02010301-030092A</t>
@@ -6437,20 +6443,20 @@
         <v>287</v>
       </c>
       <c r="B169" t="s">
-        <v>1</v>
+        <v>288</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B171" t="s">
         <v>1</v>
@@ -6458,15 +6464,15 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B173" t="s">
         <v>1</v>
@@ -6474,15 +6480,15 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B174" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
         <v>1</v>
@@ -6490,7 +6496,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
         <v>1</v>
@@ -6498,23 +6504,23 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
         <v>1</v>
@@ -6522,15 +6528,15 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B180" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B181" t="s">
         <v>1</v>
@@ -6538,63 +6544,63 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B182" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B183" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B184" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B185" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B186" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B187" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B188" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B189" t="s">
         <v>1</v>
@@ -6602,7 +6608,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B190" t="s">
         <v>1</v>
@@ -6610,111 +6616,111 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B191" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B192" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B193" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B194" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B195" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B196" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B197" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B198" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B199" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B200" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B201" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B202" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B203" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B204" t="s">
         <v>75</v>
@@ -6722,63 +6728,63 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B205" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B206" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B207" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B208" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B209" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B210" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B211" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B212" t="s">
         <v>1</v>
@@ -6786,31 +6792,31 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B213" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B214" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B215" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B216" t="s">
         <v>1</v>
@@ -6818,7 +6824,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B217" t="s">
         <v>1</v>
@@ -6826,31 +6832,31 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B218" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B219" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B220" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B221" t="s">
         <v>1</v>
@@ -6858,15 +6864,15 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B222" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B223" t="s">
         <v>1</v>
@@ -6874,7 +6880,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B224" t="s">
         <v>1</v>
@@ -6882,55 +6888,55 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B225" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B226" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B227" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B228" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B229" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B230" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B231" t="s">
         <v>1</v>
@@ -6938,7 +6944,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B232" t="s">
         <v>1</v>
@@ -6946,31 +6952,31 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B233" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B234" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B235" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B236" t="s">
         <v>1</v>
@@ -6978,15 +6984,15 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B237" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B238" t="s">
         <v>1</v>
@@ -6994,23 +7000,23 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B239" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B240" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B241" t="s">
         <v>1</v>
@@ -7018,31 +7024,31 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B242" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B243" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B244" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B245" t="s">
         <v>1</v>
@@ -7050,15 +7056,15 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B246" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B247" t="s">
         <v>1</v>
@@ -7066,31 +7072,31 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B248" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B249" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B250" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B251" t="s">
         <v>1</v>
@@ -7098,7 +7104,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B252" t="s">
         <v>1</v>
@@ -7106,15 +7112,15 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B253" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B254" t="s">
         <v>1</v>
@@ -7122,7 +7128,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B255" t="s">
         <v>1</v>
@@ -7130,39 +7136,39 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B256" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B257" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B258" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B259" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B260" t="s">
         <v>1</v>
@@ -7170,23 +7176,23 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B261" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B262" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B263" t="s">
         <v>1</v>
@@ -7194,23 +7200,23 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B264" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B265" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B266" t="s">
         <v>1</v>
@@ -7218,23 +7224,23 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B267" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B268" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B269" t="s">
         <v>75</v>
@@ -7242,23 +7248,23 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B270" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B271" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B272" t="s">
         <v>1</v>
@@ -7266,15 +7272,15 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B273" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B274" t="s">
         <v>1</v>
@@ -7282,7 +7288,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B275" t="s">
         <v>1</v>
@@ -7290,7 +7296,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B276" t="s">
         <v>75</v>
@@ -7298,7 +7304,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B277" t="s">
         <v>1</v>
@@ -7306,15 +7312,15 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B278" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B279" t="s">
         <v>75</v>
@@ -7322,23 +7328,23 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B280" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B281" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B282" t="s">
         <v>1</v>
@@ -7346,15 +7352,15 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B283" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B284" t="s">
         <v>1</v>
@@ -7362,15 +7368,15 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B285" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B286" t="s">
         <v>1</v>
@@ -7378,103 +7384,103 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B287" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B288" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B289" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B290" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B291" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B292" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B293" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B294" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B295" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B296" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B297" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B298" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B299" t="s">
         <v>1</v>
@@ -7482,55 +7488,55 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B300" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B301" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B302" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B303" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B304" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B305" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B306" t="s">
         <v>1</v>
@@ -7538,23 +7544,23 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B307" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B308" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B309" t="s">
         <v>1</v>
@@ -7562,39 +7568,39 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B310" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B311" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B312" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B313" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B314" t="s">
         <v>1</v>
@@ -7602,23 +7608,23 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B315" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B316" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B317" t="s">
         <v>1</v>
@@ -7626,15 +7632,15 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B318" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B319" t="s">
         <v>1</v>
@@ -7642,7 +7648,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B320" t="s">
         <v>1</v>
@@ -7650,31 +7656,31 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B321" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B322" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B323" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B324" t="s">
         <v>1</v>
@@ -7682,15 +7688,15 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B325" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B326" t="s">
         <v>1</v>
@@ -7698,15 +7704,15 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B327" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B328" t="s">
         <v>1</v>
@@ -7714,23 +7720,23 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B329" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B330" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B331" t="s">
         <v>1</v>
@@ -7738,23 +7744,23 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B332" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B333" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B334" t="s">
         <v>1</v>
@@ -7762,7 +7768,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B335" t="s">
         <v>1</v>
@@ -7770,7 +7776,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B336" t="s">
         <v>1</v>
@@ -7778,47 +7784,47 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B337" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B338" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B339" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B340" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B341" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B342" t="s">
         <v>1</v>
@@ -7826,7 +7832,7 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B343" t="s">
         <v>1</v>
@@ -7834,7 +7840,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B344" t="s">
         <v>1</v>
@@ -7842,7 +7848,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B345" t="s">
         <v>1</v>
@@ -7850,7 +7856,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B346" t="s">
         <v>1</v>
@@ -7858,63 +7864,63 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B347" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B348" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B349" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B350" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B351" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B352" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B353" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B354" t="s">
         <v>1</v>
@@ -7922,7 +7928,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B355" t="s">
         <v>1</v>
@@ -7930,7 +7936,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B356" t="s">
         <v>1</v>
@@ -7938,15 +7944,15 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B357" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B358" t="s">
         <v>1</v>
@@ -7954,239 +7960,239 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B359" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B360" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B361" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B362" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B363" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B364" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B365" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B366" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B367" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B368" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B369" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B370" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B371" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B372" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B373" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B374" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B375" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B376" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B377" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B378" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B379" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B380" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B381" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B382" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B383" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B384" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B385" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B386" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B387" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B388" t="s">
         <v>1</v>
@@ -8194,15 +8200,15 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B389" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B390" t="s">
         <v>1</v>
@@ -8210,15 +8216,15 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B391" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B392" t="s">
         <v>1</v>
@@ -8226,7 +8232,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B393" t="s">
         <v>1</v>
@@ -8234,7 +8240,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B394" t="s">
         <v>1</v>
@@ -8242,7 +8248,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B395" t="s">
         <v>1</v>
@@ -8250,7 +8256,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B396" t="s">
         <v>1</v>
@@ -8258,7 +8264,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B397" t="s">
         <v>1</v>
@@ -8266,7 +8272,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B398" t="s">
         <v>1</v>
@@ -8274,7 +8280,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B399" t="s">
         <v>1</v>
@@ -8282,23 +8288,23 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B400" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B401" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B402" t="s">
         <v>1</v>
@@ -8306,7 +8312,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B403" t="s">
         <v>1</v>
@@ -8314,15 +8320,15 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B404" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B405" t="s">
         <v>1</v>
@@ -8330,7 +8336,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B406" t="s">
         <v>1</v>
@@ -8338,7 +8344,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B407" t="s">
         <v>1</v>
@@ -8346,7 +8352,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B408" t="s">
         <v>1</v>
@@ -8354,47 +8360,47 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B409" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B410" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B411" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B412" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B413" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B414" t="s">
         <v>75</v>
@@ -8402,23 +8408,23 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B415" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B416" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B417" t="s">
         <v>1</v>
@@ -8426,63 +8432,63 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B418" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B419" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B420" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B421" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B422" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B423" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B424" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B425" t="s">
         <v>1</v>
@@ -8490,23 +8496,23 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B426" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B427" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B428" t="s">
         <v>1</v>
@@ -8514,31 +8520,31 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B429" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B430" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B431" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B432" t="s">
         <v>1</v>
@@ -8546,39 +8552,39 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B433" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B434" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B435" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B436" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B437" t="s">
         <v>1</v>
@@ -8586,23 +8592,23 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B438" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B439" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B440" t="s">
         <v>1</v>
@@ -8610,39 +8616,39 @@
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B441" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B442" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B443" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B444" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B445" t="s">
         <v>75</v>
@@ -8650,7 +8656,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B446" t="s">
         <v>1</v>
@@ -8658,31 +8664,31 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B447" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B448" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B449" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B450" t="s">
         <v>1</v>
@@ -8690,7 +8696,7 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B451" t="s">
         <v>1</v>
@@ -8698,7 +8704,7 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B452" t="s">
         <v>1</v>
@@ -8706,7 +8712,7 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B453" t="s">
         <v>1</v>
@@ -8714,7 +8720,7 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B454" t="s">
         <v>1</v>
@@ -8722,7 +8728,7 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B455" t="s">
         <v>1</v>
@@ -8730,71 +8736,71 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B456" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B457" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B458" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B459" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B460" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B461" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B462" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B463" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B464" t="s">
         <v>1</v>
@@ -8802,15 +8808,15 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B465" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B466" t="s">
         <v>75</v>
@@ -8818,7 +8824,7 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B467" t="s">
         <v>75</v>
@@ -8826,23 +8832,23 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B468" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B469" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B470" t="s">
         <v>1</v>
@@ -8850,15 +8856,15 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B471" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B472" t="s">
         <v>1</v>
@@ -8866,7 +8872,7 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B473" t="s">
         <v>1</v>
@@ -8874,7 +8880,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B474" t="s">
         <v>1</v>
@@ -8882,7 +8888,7 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B475" t="s">
         <v>1</v>
@@ -8890,87 +8896,87 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B476" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B477" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B478" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B479" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B480" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B481" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B482" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B483" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B484" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B485" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B486" t="s">
         <v>1</v>
@@ -8978,7 +8984,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B487" t="s">
         <v>1</v>
@@ -8986,15 +8992,15 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B488" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B489" t="s">
         <v>1</v>
@@ -9002,39 +9008,39 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B490" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B491" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B492" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B493" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B494" t="s">
         <v>1</v>
@@ -9042,7 +9048,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B495" t="s">
         <v>75</v>
@@ -9050,31 +9056,31 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B496" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B497" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B498" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B499" t="s">
         <v>75</v>
@@ -9082,159 +9088,159 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B500" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B501" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B502" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B503" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B504" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B505" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B506" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B507" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B508" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B509" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B510" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B511" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B512" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B513" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B514" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B515" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B516" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B517" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B518" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B519" t="s">
         <v>1</v>
@@ -9242,31 +9248,31 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B520" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B521" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B522" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B523" t="s">
         <v>75</v>
@@ -9274,23 +9280,23 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B524" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B525" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B526" t="s">
         <v>1</v>
@@ -9298,23 +9304,23 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B527" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B528" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B529" t="s">
         <v>1</v>
@@ -9322,7 +9328,7 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B530" t="s">
         <v>1</v>
@@ -9330,15 +9336,15 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B531" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B532" t="s">
         <v>1</v>
@@ -9346,63 +9352,63 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B533" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B534" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B535" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B536" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B537" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B538" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B539" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B540" t="s">
         <v>1</v>
@@ -9410,7 +9416,7 @@
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B541" t="s">
         <v>75</v>
@@ -9418,23 +9424,23 @@
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B542" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B543" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B544" t="s">
         <v>1</v>
@@ -9442,31 +9448,31 @@
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B545" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B546" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B547" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B548" t="s">
         <v>1</v>
@@ -9474,15 +9480,15 @@
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B549" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B550" t="s">
         <v>1</v>
@@ -9490,15 +9496,15 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B551" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B552" t="s">
         <v>1</v>
@@ -9506,15 +9512,15 @@
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B553" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B554" t="s">
         <v>1</v>
@@ -9522,7 +9528,7 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B555" t="s">
         <v>1</v>
@@ -9530,39 +9536,39 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B556" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B557" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B558" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B559" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B560" t="s">
         <v>1</v>
@@ -9570,7 +9576,7 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B561" t="s">
         <v>1</v>
@@ -9578,15 +9584,15 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B562" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B563" t="s">
         <v>75</v>
@@ -9594,47 +9600,47 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B564" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B565" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B566" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B567" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B568" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B569" t="s">
         <v>1</v>
@@ -9642,15 +9648,15 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B570" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B571" t="s">
         <v>1</v>
@@ -9658,87 +9664,87 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B572" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B573" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B574" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B575" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B576" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B577" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B578" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B579" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B580" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B581" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B582" t="s">
         <v>1</v>
@@ -9746,263 +9752,263 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B583" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B584" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B585" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B586" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B587" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B588" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B589" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B590" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B591" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B592" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B593" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B594" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B595" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B596" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B597" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B598" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B599" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B600" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B601" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B602" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B603" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B604" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B605" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B606" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B607" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B608" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B609" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B610" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B611" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B612" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B613" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B614" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B615" t="s">
         <v>1</v>
@@ -10010,23 +10016,23 @@
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B616" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B617" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B618" t="s">
         <v>1</v>
@@ -10034,7 +10040,7 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B619" t="s">
         <v>1</v>
@@ -10042,23 +10048,23 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B620" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B621" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B622" t="s">
         <v>1</v>
@@ -10066,7 +10072,7 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B623" t="s">
         <v>1</v>
@@ -10074,55 +10080,55 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B624" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B625" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B626" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B627" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B628" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B629" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B630" t="s">
         <v>1</v>
@@ -10130,7 +10136,7 @@
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B631" t="s">
         <v>1</v>
@@ -10138,7 +10144,7 @@
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B632" t="s">
         <v>1</v>
@@ -10146,15 +10152,15 @@
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B633" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B634" t="s">
         <v>1</v>
@@ -10162,7 +10168,7 @@
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B635" t="s">
         <v>1</v>
@@ -10170,23 +10176,23 @@
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B636" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B637" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B638" t="s">
         <v>1</v>
@@ -10194,23 +10200,23 @@
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B639" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B640" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B641" t="s">
         <v>1</v>
@@ -10218,7 +10224,7 @@
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B642" t="s">
         <v>1</v>
@@ -10226,7 +10232,7 @@
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B643" t="s">
         <v>1</v>
@@ -10234,31 +10240,31 @@
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B644" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B645" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B646" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B647" t="s">
         <v>1</v>
@@ -10266,15 +10272,15 @@
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B648" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B649" t="s">
         <v>1</v>
@@ -10282,7 +10288,7 @@
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B650" t="s">
         <v>1</v>
@@ -10290,15 +10296,15 @@
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B651" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B652" t="s">
         <v>1</v>
@@ -10306,15 +10312,15 @@
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B653" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B654" t="s">
         <v>1</v>
@@ -10322,15 +10328,15 @@
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B655" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B656" t="s">
         <v>1</v>
@@ -10338,15 +10344,15 @@
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B657" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B658" t="s">
         <v>1</v>
@@ -10354,15 +10360,15 @@
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B659" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B660" t="s">
         <v>1</v>
@@ -10370,87 +10376,87 @@
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B661" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B662" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B663" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B664" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B665" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B666" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B667" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B668" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B669" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B670" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B671" t="s">
         <v>1</v>
@@ -10458,7 +10464,7 @@
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B672" t="s">
         <v>1</v>
@@ -10466,23 +10472,23 @@
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B673" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B674" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B675" t="s">
         <v>1</v>
@@ -10490,7 +10496,7 @@
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B676" t="s">
         <v>1</v>
@@ -10498,7 +10504,7 @@
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B677" t="s">
         <v>1</v>
@@ -10506,23 +10512,23 @@
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B678" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B679" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B680" t="s">
         <v>1</v>
@@ -10530,7 +10536,7 @@
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B681" t="s">
         <v>1</v>
@@ -10538,7 +10544,7 @@
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B682" t="s">
         <v>1</v>
@@ -10546,23 +10552,23 @@
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B683" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B684" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B685" t="s">
         <v>1</v>
@@ -10570,23 +10576,23 @@
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B686" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B687" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B688" t="s">
         <v>1</v>
@@ -10594,23 +10600,23 @@
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B689" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B690" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B691" t="s">
         <v>1</v>
@@ -10618,7 +10624,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B692" t="s">
         <v>1</v>
@@ -10626,7 +10632,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B693" t="s">
         <v>1</v>
@@ -10634,15 +10640,15 @@
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B694" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B695" t="s">
         <v>1</v>
@@ -10650,7 +10656,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B696" t="s">
         <v>1</v>
@@ -10658,31 +10664,31 @@
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B697" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B698" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B699" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B700" t="s">
         <v>1</v>
@@ -10690,47 +10696,47 @@
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B701" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B702" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B703" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B704" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B705" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B706" t="s">
         <v>1</v>
@@ -10738,15 +10744,15 @@
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B707" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B708" t="s">
         <v>1</v>
@@ -10754,47 +10760,47 @@
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B709" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B710" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B711" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B712" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B713" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B714" t="s">
         <v>1</v>
@@ -10802,15 +10808,15 @@
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B715" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B716" t="s">
         <v>1</v>
@@ -10818,15 +10824,15 @@
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B717" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B718" t="s">
         <v>1</v>
@@ -10834,47 +10840,47 @@
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B719" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B720" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B721" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B722" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B723" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B724" t="s">
         <v>1</v>
@@ -10882,15 +10888,15 @@
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B725" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B726" t="s">
         <v>1</v>
@@ -10898,7 +10904,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B727" t="s">
         <v>1</v>
@@ -10906,71 +10912,71 @@
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B728" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B729" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B730" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B731" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B732" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B733" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B734" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B735" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B736" t="s">
         <v>1</v>
@@ -10978,39 +10984,39 @@
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B737" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B738" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B739" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B740" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B741" t="s">
         <v>1</v>
@@ -11018,7 +11024,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B742" t="s">
         <v>1</v>
@@ -11026,23 +11032,23 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B743" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B744" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B745" t="s">
         <v>1</v>
@@ -11050,15 +11056,15 @@
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B746" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B747" t="s">
         <v>1</v>
@@ -11066,7 +11072,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B748" t="s">
         <v>1</v>
@@ -11074,15 +11080,15 @@
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B749" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B750" t="s">
         <v>1</v>
@@ -11090,15 +11096,15 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B751" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B752" t="s">
         <v>1</v>
@@ -11106,79 +11112,79 @@
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B753" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B754" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B755" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B756" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B757" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B758" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B759" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B760" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B761" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B762" t="s">
         <v>1</v>
@@ -11186,71 +11192,71 @@
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B763" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B764" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B765" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B766" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B767" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B768" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B769" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B770" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B771" t="s">
         <v>1</v>
@@ -11258,39 +11264,39 @@
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B772" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B773" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B774" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B775" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B776" t="s">
         <v>1</v>
@@ -11298,7 +11304,7 @@
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B777" t="s">
         <v>1</v>
@@ -11306,23 +11312,23 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B778" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B779" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B780" t="s">
         <v>1</v>
@@ -11330,15 +11336,15 @@
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B781" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B782" t="s">
         <v>1</v>
@@ -11346,7 +11352,7 @@
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B783" t="s">
         <v>1</v>
@@ -11354,7 +11360,7 @@
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B784" t="s">
         <v>1</v>
@@ -11362,7 +11368,7 @@
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B785" t="s">
         <v>1</v>
@@ -11370,7 +11376,7 @@
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B786" t="s">
         <v>1</v>
@@ -11378,23 +11384,23 @@
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B787" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B788" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B789" t="s">
         <v>1</v>
@@ -11402,31 +11408,31 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B790" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B791" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B792" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B793" t="s">
         <v>1</v>
@@ -11434,55 +11440,55 @@
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B794" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B795" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B796" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B797" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B798" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B799" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B800" t="s">
         <v>1</v>
@@ -11490,31 +11496,31 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B801" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B802" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B803" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B804" t="s">
         <v>1</v>
@@ -11522,7 +11528,7 @@
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B805" t="s">
         <v>1</v>
@@ -11530,31 +11536,31 @@
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B806" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B807" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B808" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B809" t="s">
         <v>1</v>
@@ -11562,7 +11568,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B810" t="s">
         <v>1</v>
@@ -11570,39 +11576,39 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B811" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B812" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B813" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B814" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B815" t="s">
         <v>1</v>
@@ -11610,7 +11616,7 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B816" t="s">
         <v>1</v>
@@ -11618,7 +11624,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B817" t="s">
         <v>1</v>
@@ -11626,39 +11632,39 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B818" t="s">
-        <v>1</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B819" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="B820" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="B821" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="B822" t="s">
         <v>1</v>
@@ -11666,7 +11672,7 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="B823" t="s">
         <v>1</v>
@@ -11674,7 +11680,7 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="B824" t="s">
         <v>1</v>
@@ -11682,31 +11688,31 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="B825" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="B826" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B827" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="B828" t="s">
         <v>1</v>
@@ -11714,15 +11720,15 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B829" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="B830" t="s">
         <v>1</v>
@@ -11730,7 +11736,7 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="B831" t="s">
         <v>1</v>
@@ -11738,7 +11744,7 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B832" t="s">
         <v>1</v>
@@ -11746,47 +11752,47 @@
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="B833" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="B834" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="B835" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="B836" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="B837" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="B838" t="s">
         <v>1</v>
@@ -11794,7 +11800,7 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B839" t="s">
         <v>1</v>
@@ -11802,7 +11808,7 @@
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="B840" t="s">
         <v>1</v>
@@ -11810,15 +11816,15 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="B841" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="B842" t="s">
         <v>1</v>
@@ -11826,7 +11832,7 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="B843" t="s">
         <v>1</v>
@@ -11834,15 +11840,15 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="B844" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="B845" t="s">
         <v>1</v>
@@ -11850,23 +11856,23 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="B846" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="B847" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B848" t="s">
         <v>1</v>
@@ -11874,7 +11880,7 @@
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="B849" t="s">
         <v>1</v>
@@ -11882,7 +11888,7 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="B850" t="s">
         <v>1</v>
@@ -11890,15 +11896,15 @@
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="B851" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="B852" t="s">
         <v>1</v>
@@ -11906,7 +11912,7 @@
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="B853" t="s">
         <v>1</v>
@@ -11914,7 +11920,7 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B854" t="s">
         <v>1</v>
@@ -11922,7 +11928,7 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B855" t="s">
         <v>1</v>
@@ -11930,47 +11936,47 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B856" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="B857" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="B858" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="B859" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B860" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="B861" t="s">
         <v>1</v>
@@ -11978,103 +11984,103 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="B862" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="B863" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B864" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="B865" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="B866" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="B867" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="B868" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="B869" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="B870" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="B871" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="B872" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B873" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B874" t="s">
         <v>1</v>
@@ -12082,15 +12088,15 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="B875" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B876" t="s">
         <v>1</v>
@@ -12098,15 +12104,15 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="B877" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="B878" t="s">
         <v>1</v>
@@ -12114,15 +12120,15 @@
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="B879" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B880" t="s">
         <v>75</v>
@@ -12130,15 +12136,15 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="B881" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B882" t="s">
         <v>1</v>
@@ -12146,39 +12152,39 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="B883" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B884" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="B885" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="B886" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="B887" t="s">
         <v>1</v>
@@ -12186,7 +12192,7 @@
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="B888" t="s">
         <v>1</v>
@@ -12194,7 +12200,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="B889" t="s">
         <v>1</v>
@@ -12202,7 +12208,7 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B890" t="s">
         <v>1</v>
@@ -12210,15 +12216,15 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="B891" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B892" t="s">
         <v>1</v>
@@ -12226,15 +12232,15 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="B893" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B894" t="s">
         <v>1</v>
@@ -12242,7 +12248,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B895" t="s">
         <v>1</v>
@@ -12250,7 +12256,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="B896" t="s">
         <v>1</v>
@@ -12258,7 +12264,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="B897" t="s">
         <v>1</v>
@@ -12266,23 +12272,23 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="B898" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="B899" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="B900" t="s">
         <v>1</v>
@@ -12290,7 +12296,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="B901" t="s">
         <v>1</v>
@@ -12298,79 +12304,79 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="B902" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B903" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B904" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B905" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B906" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B907" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B908" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B909" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="B910" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B911" t="s">
         <v>75</v>
@@ -12378,23 +12384,23 @@
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B912" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B913" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B914" t="s">
         <v>1</v>
@@ -12402,199 +12408,199 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B915" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B916" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="B917" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B918" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="B919" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B920" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="B921" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="B922" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="B923" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B924" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="B925" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B926" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B927" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="B928" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B929" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B930" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B931" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B932" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B933" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B934" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="B935" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="B936" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B937" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="B938" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B939" t="s">
         <v>1</v>
@@ -12602,47 +12608,47 @@
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B940" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B941" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="B942" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="B943" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="B944" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="B945" t="s">
         <v>1</v>
@@ -12650,79 +12656,79 @@
     </row>
     <row r="946">
       <c r="A946" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="B946" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="B947" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="B948" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="B949" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B950" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="B951" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="B952" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="B953" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="B954" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="B955" t="s">
         <v>1</v>
@@ -12730,31 +12736,31 @@
     </row>
     <row r="956">
       <c r="A956" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="B956" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="B957" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="B958" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="B959" t="s">
         <v>1</v>
@@ -12762,7 +12768,7 @@
     </row>
     <row r="960">
       <c r="A960" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="B960" t="s">
         <v>1</v>
@@ -12770,7 +12776,7 @@
     </row>
     <row r="961">
       <c r="A961" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="B961" t="s">
         <v>75</v>
@@ -12778,7 +12784,7 @@
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="B962" t="s">
         <v>75</v>
@@ -12786,15 +12792,15 @@
     </row>
     <row r="963">
       <c r="A963" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="B963" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B964" t="s">
         <v>1</v>
@@ -12802,15 +12808,15 @@
     </row>
     <row r="965">
       <c r="A965" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="B965" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="B966" t="s">
         <v>1</v>
@@ -12818,7 +12824,7 @@
     </row>
     <row r="967">
       <c r="A967" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B967" t="s">
         <v>1</v>
@@ -12826,7 +12832,7 @@
     </row>
     <row r="968">
       <c r="A968" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="B968" t="s">
         <v>1</v>
@@ -12834,31 +12840,31 @@
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="B969" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B970" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="B971" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="B972" t="s">
         <v>75</v>
@@ -12866,15 +12872,15 @@
     </row>
     <row r="973">
       <c r="A973" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="B973" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="B974" t="s">
         <v>1</v>
@@ -12882,23 +12888,23 @@
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="B975" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="B976" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="B977" t="s">
         <v>1</v>
@@ -12906,7 +12912,7 @@
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="B978" t="s">
         <v>1</v>
@@ -12914,31 +12920,31 @@
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="B979" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B980" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="B981" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="B982" t="s">
         <v>1</v>
@@ -12946,79 +12952,79 @@
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="B983" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="B984" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B985" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="B986" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B987" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B988" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="B989" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="B990" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="B991" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="B992" t="s">
         <v>1</v>
@@ -13026,15 +13032,15 @@
     </row>
     <row r="993">
       <c r="A993" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="B993" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="B994" t="s">
         <v>1</v>
@@ -13042,7 +13048,7 @@
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="B995" t="s">
         <v>1</v>
@@ -13050,10 +13056,10 @@
     </row>
     <row r="996">
       <c r="A996" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="B996" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
     </row>
   </sheetData>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2213,7 +2213,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>0841f66eec1f7caf51680bed6f5054c6</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2213,7 +2213,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2213,7 +2213,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1695">
   <si>
     <t>05-050305TM</t>
   </si>
@@ -539,6 +539,9 @@
     <t>04-040021TM</t>
   </si>
   <si>
+    <t>f82bd4a6ab8a9d362f159e5f849a581a</t>
+  </si>
+  <si>
     <t>03-030047A</t>
   </si>
   <si>
@@ -557,6 +560,9 @@
     <t>04-040021TP</t>
   </si>
   <si>
+    <t>a6802efafda307dedca9cd91fac20dbb</t>
+  </si>
+  <si>
     <t>01-010041TC</t>
   </si>
   <si>
@@ -602,6 +608,9 @@
     <t>04-040021TC</t>
   </si>
   <si>
+    <t>96925422ed8dcd6c1e4a3565680a927b</t>
+  </si>
+  <si>
     <t>04-040010TM</t>
   </si>
   <si>
@@ -656,7 +665,7 @@
     <t>04-040014TC</t>
   </si>
   <si>
-    <t>b99c222ca5e4a403aa2cd2aa985c2a97</t>
+    <t>a412ce738c555f504b3c2fc2563a4afe</t>
   </si>
   <si>
     <t>05-050301TC</t>
@@ -875,6 +884,9 @@
     <t>04-040016TC</t>
   </si>
   <si>
+    <t>e6bcb2e1d0134c14259cc37457c02026</t>
+  </si>
+  <si>
     <t>04-040021A</t>
   </si>
   <si>
@@ -890,6 +902,9 @@
     <t>04-040016TP</t>
   </si>
   <si>
+    <t>2e2f7ca96cc502c48c011200d1dbad96</t>
+  </si>
+  <si>
     <t>01-010032TC</t>
   </si>
   <si>
@@ -911,6 +926,9 @@
     <t>04-040016TM</t>
   </si>
   <si>
+    <t>9419ac7b14b927a35392df1206b662a5</t>
+  </si>
+  <si>
     <t>01-010010TM</t>
   </si>
   <si>
@@ -983,6 +1001,9 @@
     <t>04-040020A</t>
   </si>
   <si>
+    <t>5d5609353eeae82b410a70830095b5b7</t>
+  </si>
+  <si>
     <t>05-0709-070906AA</t>
   </si>
   <si>
@@ -1232,7 +1253,7 @@
     <t>04-040014TP</t>
   </si>
   <si>
-    <t>0defa52e30cb2325fa7a2ac126c3721d</t>
+    <t>a6aa62789d57a04a889943c1037ac8a7</t>
   </si>
   <si>
     <t>03-030042TC</t>
@@ -1247,7 +1268,7 @@
     <t>04-040014TM</t>
   </si>
   <si>
-    <t>8248ebf504f034f12a563a9ea82aafed</t>
+    <t>492d3a39d5a70a93cd6c37e584ad93d6</t>
   </si>
   <si>
     <t>03-02010301-030089TM</t>
@@ -2213,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2819,6 +2840,9 @@
     <t>04-040020TM</t>
   </si>
   <si>
+    <t>75bf6026f367a6a3e5c8ad3ab0df4e73</t>
+  </si>
+  <si>
     <t>01-080101-010078TP</t>
   </si>
   <si>
@@ -2828,6 +2852,9 @@
     <t>04-040020TP</t>
   </si>
   <si>
+    <t>18b03c2fe27dd5fc2534ad2f8670a77c</t>
+  </si>
+  <si>
     <t>03-02010301-030090TP</t>
   </si>
   <si>
@@ -2909,6 +2936,9 @@
     <t>04-040020TC</t>
   </si>
   <si>
+    <t>eeae9bdd031c807456d6814fc03e4b4e</t>
+  </si>
+  <si>
     <t>03-030034TP</t>
   </si>
   <si>
@@ -4229,6 +4259,9 @@
     <t>04-040016A</t>
   </si>
   <si>
+    <t>9b174f5ac0336b3d5cc49873592889cb</t>
+  </si>
+  <si>
     <t>03-90205-0205_006TC</t>
   </si>
   <si>
@@ -4310,6 +4343,9 @@
     <t>04-040017TC</t>
   </si>
   <si>
+    <t>eca80c0354834bfc6e5c621a9c3fa38f</t>
+  </si>
+  <si>
     <t>05-0709-070903TP</t>
   </si>
   <si>
@@ -4319,10 +4355,16 @@
     <t>04-040017TM</t>
   </si>
   <si>
+    <t>b2730936be8b224e9d9d3b14e33326ec</t>
+  </si>
+  <si>
     <t>05-050104TM</t>
   </si>
   <si>
     <t>04-040017TP</t>
+  </si>
+  <si>
+    <t>bdc0f7f184c1ebe6336fba506f88d7d2</t>
   </si>
   <si>
     <t>05-050104TP</t>
@@ -5907,28 +5949,28 @@
         <v>174</v>
       </c>
       <c r="B102" t="s">
-        <v>1</v>
+        <v>175</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B103" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B104" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B105" t="s">
         <v>1</v>
@@ -5936,15 +5978,15 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B106" t="s">
-        <v>1</v>
+        <v>182</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B107" t="s">
         <v>1</v>
@@ -5952,31 +5994,31 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B108" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B109" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B110" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B111" t="s">
         <v>1</v>
@@ -5984,103 +6026,103 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B112" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B113" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B114" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B115" t="s">
-        <v>1</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B116" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B117" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B118" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B120" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B121" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B122" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B124" t="s">
         <v>1</v>
@@ -6088,55 +6130,55 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B125" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B127" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B128" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B129" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B130" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B131" t="s">
         <v>1</v>
@@ -6144,23 +6186,23 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B134" t="s">
         <v>1</v>
@@ -6168,23 +6210,23 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B135" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B136" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B137" t="s">
         <v>1</v>
@@ -6192,39 +6234,39 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B140" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B141" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B142" t="s">
         <v>1</v>
@@ -6232,15 +6274,15 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B143" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B144" t="s">
         <v>1</v>
@@ -6248,55 +6290,55 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B145" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B146" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B147" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B148" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B149" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B151" t="s">
         <v>1</v>
@@ -6304,15 +6346,15 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B152" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B153" t="s">
         <v>1</v>
@@ -6320,39 +6362,39 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B154" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B155" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B156" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B157" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B158" t="s">
         <v>1</v>
@@ -6360,15 +6402,15 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B159" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B160" t="s">
         <v>1</v>
@@ -6376,7 +6418,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B161" t="s">
         <v>1</v>
@@ -6384,7 +6426,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B162" t="s">
         <v>1</v>
@@ -6392,23 +6434,23 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B165" t="s">
         <v>1</v>
@@ -6416,15 +6458,15 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B166" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B167" t="s">
         <v>1</v>
@@ -6432,47 +6474,47 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B168" t="s">
-        <v>1</v>
+        <v>290</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B171" t="s">
-        <v>1</v>
+        <v>296</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B172" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B173" t="s">
         <v>1</v>
@@ -6480,15 +6522,15 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B174" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B175" t="s">
         <v>1</v>
@@ -6496,31 +6538,31 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B176" t="s">
-        <v>1</v>
+        <v>304</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B177" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B178" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B179" t="s">
         <v>1</v>
@@ -6528,15 +6570,15 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B180" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B181" t="s">
         <v>1</v>
@@ -6544,63 +6586,63 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B182" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B183" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B184" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B185" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B186" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B187" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B188" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B189" t="s">
         <v>1</v>
@@ -6608,119 +6650,119 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B190" t="s">
-        <v>1</v>
+        <v>329</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B191" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B192" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B193" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B194" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B195" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B196" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B197" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B198" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B199" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B200" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B201" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B202" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B203" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B204" t="s">
         <v>75</v>
@@ -6728,63 +6770,63 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B205" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B206" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B207" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B208" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B209" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B210" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B211" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B212" t="s">
         <v>1</v>
@@ -6792,31 +6834,31 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B213" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B214" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B215" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B216" t="s">
         <v>1</v>
@@ -6824,7 +6866,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B217" t="s">
         <v>1</v>
@@ -6832,31 +6874,31 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B218" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B219" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B220" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B221" t="s">
         <v>1</v>
@@ -6864,15 +6906,15 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B222" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B223" t="s">
         <v>1</v>
@@ -6880,7 +6922,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B224" t="s">
         <v>1</v>
@@ -6888,55 +6930,55 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B225" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B226" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B227" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B228" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B229" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B230" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B231" t="s">
         <v>1</v>
@@ -6944,7 +6986,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B232" t="s">
         <v>1</v>
@@ -6952,31 +6994,31 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B233" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B234" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B235" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B236" t="s">
         <v>1</v>
@@ -6984,15 +7026,15 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B237" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B238" t="s">
         <v>1</v>
@@ -7000,23 +7042,23 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B239" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B240" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B241" t="s">
         <v>1</v>
@@ -7024,31 +7066,31 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B242" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B243" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B244" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B245" t="s">
         <v>1</v>
@@ -7056,15 +7098,15 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B246" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B247" t="s">
         <v>1</v>
@@ -7072,31 +7114,31 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B248" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B249" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B250" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B251" t="s">
         <v>1</v>
@@ -7104,7 +7146,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B252" t="s">
         <v>1</v>
@@ -7112,15 +7154,15 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="B253" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B254" t="s">
         <v>1</v>
@@ -7128,7 +7170,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B255" t="s">
         <v>1</v>
@@ -7136,39 +7178,39 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B256" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B257" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B258" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B259" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B260" t="s">
         <v>1</v>
@@ -7176,23 +7218,23 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B261" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B262" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="B263" t="s">
         <v>1</v>
@@ -7200,23 +7242,23 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B264" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B265" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B266" t="s">
         <v>1</v>
@@ -7224,23 +7266,23 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B267" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B268" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B269" t="s">
         <v>75</v>
@@ -7248,23 +7290,23 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B270" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="B271" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B272" t="s">
         <v>1</v>
@@ -7272,15 +7314,15 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B273" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B274" t="s">
         <v>1</v>
@@ -7288,7 +7330,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B275" t="s">
         <v>1</v>
@@ -7296,7 +7338,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B276" t="s">
         <v>75</v>
@@ -7304,7 +7346,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="B277" t="s">
         <v>1</v>
@@ -7312,15 +7354,15 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B278" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B279" t="s">
         <v>75</v>
@@ -7328,23 +7370,23 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="B280" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B281" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B282" t="s">
         <v>1</v>
@@ -7352,15 +7394,15 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B283" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B284" t="s">
         <v>1</v>
@@ -7368,15 +7410,15 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="B285" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B286" t="s">
         <v>1</v>
@@ -7384,103 +7426,103 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B287" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B288" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="B289" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B290" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B291" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B292" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B293" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B294" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B295" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B296" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B297" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B298" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B299" t="s">
         <v>1</v>
@@ -7488,55 +7530,55 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B300" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="B301" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="B302" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="B303" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B304" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="B305" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="B306" t="s">
         <v>1</v>
@@ -7544,23 +7586,23 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="B307" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="B308" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="B309" t="s">
         <v>1</v>
@@ -7568,39 +7610,39 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="B310" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="B311" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="B312" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B313" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B314" t="s">
         <v>1</v>
@@ -7608,23 +7650,23 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B315" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B316" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B317" t="s">
         <v>1</v>
@@ -7632,15 +7674,15 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B318" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B319" t="s">
         <v>1</v>
@@ -7648,7 +7690,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="B320" t="s">
         <v>1</v>
@@ -7656,31 +7698,31 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B321" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B322" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="B323" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B324" t="s">
         <v>1</v>
@@ -7688,15 +7730,15 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="B325" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="B326" t="s">
         <v>1</v>
@@ -7704,15 +7746,15 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B327" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B328" t="s">
         <v>1</v>
@@ -7720,23 +7762,23 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="B329" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B330" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B331" t="s">
         <v>1</v>
@@ -7744,23 +7786,23 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B332" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B333" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B334" t="s">
         <v>1</v>
@@ -7768,7 +7810,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="B335" t="s">
         <v>1</v>
@@ -7776,7 +7818,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B336" t="s">
         <v>1</v>
@@ -7784,47 +7826,47 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B337" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B338" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="B339" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="B340" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="B341" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B342" t="s">
         <v>1</v>
@@ -7832,7 +7874,7 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B343" t="s">
         <v>1</v>
@@ -7840,7 +7882,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B344" t="s">
         <v>1</v>
@@ -7848,7 +7890,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B345" t="s">
         <v>1</v>
@@ -7856,7 +7898,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="B346" t="s">
         <v>1</v>
@@ -7864,63 +7906,63 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B347" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B348" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B349" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B350" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B351" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B352" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B353" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B354" t="s">
         <v>1</v>
@@ -7928,7 +7970,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="B355" t="s">
         <v>1</v>
@@ -7936,7 +7978,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B356" t="s">
         <v>1</v>
@@ -7944,15 +7986,15 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="B357" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="B358" t="s">
         <v>1</v>
@@ -7960,239 +8002,239 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="B359" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B360" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B361" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B362" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B363" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="B364" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="B365" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B366" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="B367" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="B368" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="B369" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="B370" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="B371" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B372" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="B373" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B374" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B375" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="B376" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="B377" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B378" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="B379" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="B380" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="B381" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="B382" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B383" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="B384" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="B385" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="B386" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="B387" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B388" t="s">
         <v>1</v>
@@ -8200,15 +8242,15 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="B389" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="B390" t="s">
         <v>1</v>
@@ -8216,15 +8258,15 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="B391" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="B392" t="s">
         <v>1</v>
@@ -8232,7 +8274,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="B393" t="s">
         <v>1</v>
@@ -8240,7 +8282,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="B394" t="s">
         <v>1</v>
@@ -8248,7 +8290,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="B395" t="s">
         <v>1</v>
@@ -8256,7 +8298,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="B396" t="s">
         <v>1</v>
@@ -8264,7 +8306,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="B397" t="s">
         <v>1</v>
@@ -8272,7 +8314,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="B398" t="s">
         <v>1</v>
@@ -8280,7 +8322,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B399" t="s">
         <v>1</v>
@@ -8288,23 +8330,23 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="B400" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="B401" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B402" t="s">
         <v>1</v>
@@ -8312,7 +8354,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="B403" t="s">
         <v>1</v>
@@ -8320,15 +8362,15 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="B404" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B405" t="s">
         <v>1</v>
@@ -8336,7 +8378,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="B406" t="s">
         <v>1</v>
@@ -8344,7 +8386,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="B407" t="s">
         <v>1</v>
@@ -8352,7 +8394,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="B408" t="s">
         <v>1</v>
@@ -8360,47 +8402,47 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B409" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="B410" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="B411" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="B412" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B413" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="B414" t="s">
         <v>75</v>
@@ -8408,23 +8450,23 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="B415" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="B416" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="B417" t="s">
         <v>1</v>
@@ -8432,63 +8474,63 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="B418" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="B419" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="B420" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="B421" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="B422" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="B423" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="B424" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="B425" t="s">
         <v>1</v>
@@ -8496,23 +8538,23 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="B426" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="B427" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="B428" t="s">
         <v>1</v>
@@ -8520,31 +8562,31 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B429" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="B430" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="B431" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="B432" t="s">
         <v>1</v>
@@ -8552,39 +8594,39 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="B433" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="B434" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="B435" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="B436" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="B437" t="s">
         <v>1</v>
@@ -8592,23 +8634,23 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="B438" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="B439" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="B440" t="s">
         <v>1</v>
@@ -8616,39 +8658,39 @@
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="B441" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="B442" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="B443" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="B444" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="B445" t="s">
         <v>75</v>
@@ -8656,7 +8698,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="B446" t="s">
         <v>1</v>
@@ -8664,31 +8706,31 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="B447" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="B448" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="B449" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="B450" t="s">
         <v>1</v>
@@ -8696,7 +8738,7 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="B451" t="s">
         <v>1</v>
@@ -8704,7 +8746,7 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="B452" t="s">
         <v>1</v>
@@ -8712,7 +8754,7 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="B453" t="s">
         <v>1</v>
@@ -8720,7 +8762,7 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="B454" t="s">
         <v>1</v>
@@ -8728,7 +8770,7 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B455" t="s">
         <v>1</v>
@@ -8736,71 +8778,71 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B456" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="B457" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="B458" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="B459" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="B460" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="B461" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="B462" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="B463" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="B464" t="s">
         <v>1</v>
@@ -8808,15 +8850,15 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="B465" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="B466" t="s">
         <v>75</v>
@@ -8824,7 +8866,7 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="B467" t="s">
         <v>75</v>
@@ -8832,23 +8874,23 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="B468" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="B469" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="B470" t="s">
         <v>1</v>
@@ -8856,15 +8898,15 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="B471" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="B472" t="s">
         <v>1</v>
@@ -8872,7 +8914,7 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B473" t="s">
         <v>1</v>
@@ -8880,7 +8922,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="B474" t="s">
         <v>1</v>
@@ -8888,7 +8930,7 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="B475" t="s">
         <v>1</v>
@@ -8896,87 +8938,87 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="B476" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="B477" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="B478" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="B479" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="B480" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="B481" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="B482" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B483" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="B484" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="B485" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="B486" t="s">
         <v>1</v>
@@ -8984,7 +9026,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="B487" t="s">
         <v>1</v>
@@ -8992,15 +9034,15 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="B488" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="B489" t="s">
         <v>1</v>
@@ -9008,39 +9050,39 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="B490" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="B491" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="B492" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="B493" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="B494" t="s">
         <v>1</v>
@@ -9048,7 +9090,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="B495" t="s">
         <v>75</v>
@@ -9056,31 +9098,31 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="B496" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="B497" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="B498" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="B499" t="s">
         <v>75</v>
@@ -9088,159 +9130,159 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="B500" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="B501" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="B502" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="B503" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="B504" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="B505" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="B506" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="B507" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="B508" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="B509" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="B510" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="B511" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="B512" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="B513" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="B514" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="B515" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="B516" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="B517" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="B518" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="B519" t="s">
         <v>1</v>
@@ -9248,31 +9290,31 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="B520" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="B521" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="B522" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="B523" t="s">
         <v>75</v>
@@ -9280,23 +9322,23 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="B524" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="B525" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="B526" t="s">
         <v>1</v>
@@ -9304,23 +9346,23 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="B527" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="B528" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="B529" t="s">
         <v>1</v>
@@ -9328,7 +9370,7 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="B530" t="s">
         <v>1</v>
@@ -9336,15 +9378,15 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="B531" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="B532" t="s">
         <v>1</v>
@@ -9352,63 +9394,63 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="B533" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="B534" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="B535" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="B536" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="B537" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="B538" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="B539" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="B540" t="s">
         <v>1</v>
@@ -9416,7 +9458,7 @@
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="B541" t="s">
         <v>75</v>
@@ -9424,23 +9466,23 @@
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="B542" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="B543" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="B544" t="s">
         <v>1</v>
@@ -9448,31 +9490,31 @@
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="B545" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="B546" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="B547" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="B548" t="s">
         <v>1</v>
@@ -9480,15 +9522,15 @@
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="B549" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="B550" t="s">
         <v>1</v>
@@ -9496,39 +9538,39 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="B551" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="B552" t="s">
-        <v>1</v>
+        <v>942</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="B553" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="B554" t="s">
-        <v>1</v>
+        <v>946</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>938</v>
+        <v>947</v>
       </c>
       <c r="B555" t="s">
         <v>1</v>
@@ -9536,39 +9578,39 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="B556" t="s">
-        <v>940</v>
+        <v>949</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>941</v>
+        <v>950</v>
       </c>
       <c r="B557" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>943</v>
+        <v>952</v>
       </c>
       <c r="B558" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="B559" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>947</v>
+        <v>956</v>
       </c>
       <c r="B560" t="s">
         <v>1</v>
@@ -9576,7 +9618,7 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
       <c r="B561" t="s">
         <v>1</v>
@@ -9584,15 +9626,15 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="B562" t="s">
-        <v>950</v>
+        <v>959</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="B563" t="s">
         <v>75</v>
@@ -9600,47 +9642,47 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
       <c r="B564" t="s">
-        <v>953</v>
+        <v>962</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>954</v>
+        <v>963</v>
       </c>
       <c r="B565" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="B566" t="s">
-        <v>957</v>
+        <v>966</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="B567" t="s">
-        <v>959</v>
+        <v>968</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="B568" t="s">
-        <v>960</v>
+        <v>969</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="B569" t="s">
         <v>1</v>
@@ -9648,103 +9690,103 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>962</v>
+        <v>971</v>
       </c>
       <c r="B570" t="s">
-        <v>963</v>
+        <v>972</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>964</v>
+        <v>973</v>
       </c>
       <c r="B571" t="s">
-        <v>1</v>
+        <v>974</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="B572" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="B573" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="B574" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="B575" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="B576" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="B577" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="B578" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="B579" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="B580" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
       <c r="B581" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="B582" t="s">
         <v>1</v>
@@ -9752,263 +9794,263 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="B583" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="B584" t="s">
-        <v>989</v>
+        <v>999</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="B585" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="B586" t="s">
-        <v>993</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="B587" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="B588" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="B589" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="B590" t="s">
-        <v>1001</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
       <c r="B591" t="s">
-        <v>1003</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>1004</v>
+        <v>1014</v>
       </c>
       <c r="B592" t="s">
-        <v>1005</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>1006</v>
+        <v>1016</v>
       </c>
       <c r="B593" t="s">
-        <v>1007</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>1008</v>
+        <v>1018</v>
       </c>
       <c r="B594" t="s">
-        <v>1009</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="B595" t="s">
-        <v>1011</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="B596" t="s">
-        <v>1013</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>1014</v>
+        <v>1024</v>
       </c>
       <c r="B597" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
       <c r="B598" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
       <c r="B599" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="B600" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
       <c r="B601" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
       <c r="B602" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="B603" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
       <c r="B604" t="s">
-        <v>1029</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="B605" t="s">
-        <v>1031</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>1032</v>
+        <v>1042</v>
       </c>
       <c r="B606" t="s">
-        <v>1033</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="B607" t="s">
-        <v>1035</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>1036</v>
+        <v>1046</v>
       </c>
       <c r="B608" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>1038</v>
+        <v>1048</v>
       </c>
       <c r="B609" t="s">
-        <v>1039</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="B610" t="s">
-        <v>1041</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>1042</v>
+        <v>1052</v>
       </c>
       <c r="B611" t="s">
-        <v>1043</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>1044</v>
+        <v>1054</v>
       </c>
       <c r="B612" t="s">
-        <v>1045</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>1046</v>
+        <v>1056</v>
       </c>
       <c r="B613" t="s">
-        <v>1047</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>1048</v>
+        <v>1058</v>
       </c>
       <c r="B614" t="s">
-        <v>1049</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="B615" t="s">
         <v>1</v>
@@ -10016,23 +10058,23 @@
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>1051</v>
+        <v>1061</v>
       </c>
       <c r="B616" t="s">
-        <v>1052</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>1053</v>
+        <v>1063</v>
       </c>
       <c r="B617" t="s">
-        <v>1054</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>1055</v>
+        <v>1065</v>
       </c>
       <c r="B618" t="s">
         <v>1</v>
@@ -10040,7 +10082,7 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B619" t="s">
         <v>1</v>
@@ -10048,23 +10090,23 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>1057</v>
+        <v>1067</v>
       </c>
       <c r="B620" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>1059</v>
+        <v>1069</v>
       </c>
       <c r="B621" t="s">
-        <v>1060</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>1061</v>
+        <v>1071</v>
       </c>
       <c r="B622" t="s">
         <v>1</v>
@@ -10072,7 +10114,7 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>1062</v>
+        <v>1072</v>
       </c>
       <c r="B623" t="s">
         <v>1</v>
@@ -10080,55 +10122,55 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="B624" t="s">
-        <v>1064</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>1065</v>
+        <v>1075</v>
       </c>
       <c r="B625" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
       <c r="B626" t="s">
-        <v>1068</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>1069</v>
+        <v>1079</v>
       </c>
       <c r="B627" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="B628" t="s">
-        <v>1072</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>1073</v>
+        <v>1083</v>
       </c>
       <c r="B629" t="s">
-        <v>1074</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>1075</v>
+        <v>1085</v>
       </c>
       <c r="B630" t="s">
         <v>1</v>
@@ -10136,7 +10178,7 @@
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>1076</v>
+        <v>1086</v>
       </c>
       <c r="B631" t="s">
         <v>1</v>
@@ -10144,7 +10186,7 @@
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>1077</v>
+        <v>1087</v>
       </c>
       <c r="B632" t="s">
         <v>1</v>
@@ -10152,15 +10194,15 @@
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>1078</v>
+        <v>1088</v>
       </c>
       <c r="B633" t="s">
-        <v>1079</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>1080</v>
+        <v>1090</v>
       </c>
       <c r="B634" t="s">
         <v>1</v>
@@ -10168,7 +10210,7 @@
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="B635" t="s">
         <v>1</v>
@@ -10176,23 +10218,23 @@
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>1082</v>
+        <v>1092</v>
       </c>
       <c r="B636" t="s">
-        <v>1083</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="B637" t="s">
-        <v>1085</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="B638" t="s">
         <v>1</v>
@@ -10200,23 +10242,23 @@
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>1087</v>
+        <v>1097</v>
       </c>
       <c r="B639" t="s">
-        <v>1088</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>1089</v>
+        <v>1099</v>
       </c>
       <c r="B640" t="s">
-        <v>1090</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>1091</v>
+        <v>1101</v>
       </c>
       <c r="B641" t="s">
         <v>1</v>
@@ -10224,7 +10266,7 @@
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="B642" t="s">
         <v>1</v>
@@ -10232,7 +10274,7 @@
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="B643" t="s">
         <v>1</v>
@@ -10240,31 +10282,31 @@
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="B644" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="B645" t="s">
-        <v>1097</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>1098</v>
+        <v>1108</v>
       </c>
       <c r="B646" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>1100</v>
+        <v>1110</v>
       </c>
       <c r="B647" t="s">
         <v>1</v>
@@ -10272,15 +10314,15 @@
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>1101</v>
+        <v>1111</v>
       </c>
       <c r="B648" t="s">
-        <v>1102</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>1103</v>
+        <v>1113</v>
       </c>
       <c r="B649" t="s">
         <v>1</v>
@@ -10288,7 +10330,7 @@
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>1104</v>
+        <v>1114</v>
       </c>
       <c r="B650" t="s">
         <v>1</v>
@@ -10296,15 +10338,15 @@
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="B651" t="s">
-        <v>1106</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>1107</v>
+        <v>1117</v>
       </c>
       <c r="B652" t="s">
         <v>1</v>
@@ -10312,15 +10354,15 @@
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>1108</v>
+        <v>1118</v>
       </c>
       <c r="B653" t="s">
-        <v>1109</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="B654" t="s">
         <v>1</v>
@@ -10328,15 +10370,15 @@
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="B655" t="s">
-        <v>1112</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="s">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="B656" t="s">
         <v>1</v>
@@ -10344,15 +10386,15 @@
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>1114</v>
+        <v>1124</v>
       </c>
       <c r="B657" t="s">
-        <v>1115</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="B658" t="s">
         <v>1</v>
@@ -10360,15 +10402,15 @@
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>1117</v>
+        <v>1127</v>
       </c>
       <c r="B659" t="s">
-        <v>1118</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="s">
-        <v>1119</v>
+        <v>1129</v>
       </c>
       <c r="B660" t="s">
         <v>1</v>
@@ -10376,87 +10418,87 @@
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>1120</v>
+        <v>1130</v>
       </c>
       <c r="B661" t="s">
-        <v>1121</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>1122</v>
+        <v>1132</v>
       </c>
       <c r="B662" t="s">
-        <v>1123</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>1124</v>
+        <v>1134</v>
       </c>
       <c r="B663" t="s">
-        <v>1125</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>1126</v>
+        <v>1136</v>
       </c>
       <c r="B664" t="s">
-        <v>1127</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>1128</v>
+        <v>1138</v>
       </c>
       <c r="B665" t="s">
-        <v>1129</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="B666" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>1132</v>
+        <v>1142</v>
       </c>
       <c r="B667" t="s">
-        <v>1133</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>1134</v>
+        <v>1144</v>
       </c>
       <c r="B668" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="B669" t="s">
-        <v>1137</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>1138</v>
+        <v>1148</v>
       </c>
       <c r="B670" t="s">
-        <v>1139</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="B671" t="s">
         <v>1</v>
@@ -10464,7 +10506,7 @@
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>1141</v>
+        <v>1151</v>
       </c>
       <c r="B672" t="s">
         <v>1</v>
@@ -10472,23 +10514,23 @@
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>1142</v>
+        <v>1152</v>
       </c>
       <c r="B673" t="s">
-        <v>1143</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>1144</v>
+        <v>1154</v>
       </c>
       <c r="B674" t="s">
-        <v>1145</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>1146</v>
+        <v>1156</v>
       </c>
       <c r="B675" t="s">
         <v>1</v>
@@ -10496,7 +10538,7 @@
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>1147</v>
+        <v>1157</v>
       </c>
       <c r="B676" t="s">
         <v>1</v>
@@ -10504,7 +10546,7 @@
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>1148</v>
+        <v>1158</v>
       </c>
       <c r="B677" t="s">
         <v>1</v>
@@ -10512,23 +10554,23 @@
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>1149</v>
+        <v>1159</v>
       </c>
       <c r="B678" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>1151</v>
+        <v>1161</v>
       </c>
       <c r="B679" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>1153</v>
+        <v>1163</v>
       </c>
       <c r="B680" t="s">
         <v>1</v>
@@ -10536,7 +10578,7 @@
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>1154</v>
+        <v>1164</v>
       </c>
       <c r="B681" t="s">
         <v>1</v>
@@ -10544,7 +10586,7 @@
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
       <c r="B682" t="s">
         <v>1</v>
@@ -10552,23 +10594,23 @@
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="B683" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="B684" t="s">
-        <v>1159</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>1160</v>
+        <v>1170</v>
       </c>
       <c r="B685" t="s">
         <v>1</v>
@@ -10576,23 +10618,23 @@
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="B686" t="s">
-        <v>1162</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>1163</v>
+        <v>1173</v>
       </c>
       <c r="B687" t="s">
-        <v>1164</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>1165</v>
+        <v>1175</v>
       </c>
       <c r="B688" t="s">
         <v>1</v>
@@ -10600,23 +10642,23 @@
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>1166</v>
+        <v>1176</v>
       </c>
       <c r="B689" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>1168</v>
+        <v>1178</v>
       </c>
       <c r="B690" t="s">
-        <v>1169</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>1170</v>
+        <v>1180</v>
       </c>
       <c r="B691" t="s">
         <v>1</v>
@@ -10624,7 +10666,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>1171</v>
+        <v>1181</v>
       </c>
       <c r="B692" t="s">
         <v>1</v>
@@ -10632,7 +10674,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>1172</v>
+        <v>1182</v>
       </c>
       <c r="B693" t="s">
         <v>1</v>
@@ -10640,15 +10682,15 @@
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="B694" t="s">
-        <v>1174</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="B695" t="s">
         <v>1</v>
@@ -10656,7 +10698,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>1176</v>
+        <v>1186</v>
       </c>
       <c r="B696" t="s">
         <v>1</v>
@@ -10664,31 +10706,31 @@
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="B697" t="s">
-        <v>1178</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>1179</v>
+        <v>1189</v>
       </c>
       <c r="B698" t="s">
-        <v>1180</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>1181</v>
+        <v>1191</v>
       </c>
       <c r="B699" t="s">
-        <v>1182</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1183</v>
+        <v>1193</v>
       </c>
       <c r="B700" t="s">
         <v>1</v>
@@ -10696,47 +10738,47 @@
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1184</v>
+        <v>1194</v>
       </c>
       <c r="B701" t="s">
-        <v>1185</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1186</v>
+        <v>1196</v>
       </c>
       <c r="B702" t="s">
-        <v>1187</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1188</v>
+        <v>1198</v>
       </c>
       <c r="B703" t="s">
-        <v>1189</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="B704" t="s">
-        <v>1191</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1192</v>
+        <v>1202</v>
       </c>
       <c r="B705" t="s">
-        <v>1193</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1194</v>
+        <v>1204</v>
       </c>
       <c r="B706" t="s">
         <v>1</v>
@@ -10744,15 +10786,15 @@
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1195</v>
+        <v>1205</v>
       </c>
       <c r="B707" t="s">
-        <v>1196</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1197</v>
+        <v>1207</v>
       </c>
       <c r="B708" t="s">
         <v>1</v>
@@ -10760,47 +10802,47 @@
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1198</v>
+        <v>1208</v>
       </c>
       <c r="B709" t="s">
-        <v>1199</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1200</v>
+        <v>1210</v>
       </c>
       <c r="B710" t="s">
-        <v>1201</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
       <c r="B711" t="s">
-        <v>1203</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1204</v>
+        <v>1214</v>
       </c>
       <c r="B712" t="s">
-        <v>1205</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1206</v>
+        <v>1216</v>
       </c>
       <c r="B713" t="s">
-        <v>1207</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>1208</v>
+        <v>1218</v>
       </c>
       <c r="B714" t="s">
         <v>1</v>
@@ -10808,15 +10850,15 @@
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>1209</v>
+        <v>1219</v>
       </c>
       <c r="B715" t="s">
-        <v>1210</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>1211</v>
+        <v>1221</v>
       </c>
       <c r="B716" t="s">
         <v>1</v>
@@ -10824,15 +10866,15 @@
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>1212</v>
+        <v>1222</v>
       </c>
       <c r="B717" t="s">
-        <v>1213</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>1214</v>
+        <v>1224</v>
       </c>
       <c r="B718" t="s">
         <v>1</v>
@@ -10840,47 +10882,47 @@
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="B719" t="s">
-        <v>1216</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1217</v>
+        <v>1227</v>
       </c>
       <c r="B720" t="s">
-        <v>1218</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1219</v>
+        <v>1229</v>
       </c>
       <c r="B721" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="B722" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="B723" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="B724" t="s">
         <v>1</v>
@@ -10888,15 +10930,15 @@
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="B725" t="s">
-        <v>1227</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="B726" t="s">
         <v>1</v>
@@ -10904,7 +10946,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>1229</v>
+        <v>1239</v>
       </c>
       <c r="B727" t="s">
         <v>1</v>
@@ -10912,71 +10954,71 @@
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="B728" t="s">
-        <v>1231</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1232</v>
+        <v>1242</v>
       </c>
       <c r="B729" t="s">
-        <v>1233</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>1234</v>
+        <v>1244</v>
       </c>
       <c r="B730" t="s">
-        <v>1235</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1236</v>
+        <v>1246</v>
       </c>
       <c r="B731" t="s">
-        <v>1237</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>1238</v>
+        <v>1248</v>
       </c>
       <c r="B732" t="s">
-        <v>1239</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1240</v>
+        <v>1250</v>
       </c>
       <c r="B733" t="s">
-        <v>1241</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1242</v>
+        <v>1252</v>
       </c>
       <c r="B734" t="s">
-        <v>1243</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="B735" t="s">
-        <v>1245</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>1246</v>
+        <v>1256</v>
       </c>
       <c r="B736" t="s">
         <v>1</v>
@@ -10984,39 +11026,39 @@
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="B737" t="s">
-        <v>1248</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1249</v>
+        <v>1259</v>
       </c>
       <c r="B738" t="s">
-        <v>1250</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="B739" t="s">
-        <v>1252</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1253</v>
+        <v>1263</v>
       </c>
       <c r="B740" t="s">
-        <v>1254</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1255</v>
+        <v>1265</v>
       </c>
       <c r="B741" t="s">
         <v>1</v>
@@ -11024,7 +11066,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1256</v>
+        <v>1266</v>
       </c>
       <c r="B742" t="s">
         <v>1</v>
@@ -11032,23 +11074,23 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
       <c r="B743" t="s">
-        <v>1258</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1259</v>
+        <v>1269</v>
       </c>
       <c r="B744" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1261</v>
+        <v>1271</v>
       </c>
       <c r="B745" t="s">
         <v>1</v>
@@ -11056,15 +11098,15 @@
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1262</v>
+        <v>1272</v>
       </c>
       <c r="B746" t="s">
-        <v>1263</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1264</v>
+        <v>1274</v>
       </c>
       <c r="B747" t="s">
         <v>1</v>
@@ -11072,7 +11114,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1265</v>
+        <v>1275</v>
       </c>
       <c r="B748" t="s">
         <v>1</v>
@@ -11080,15 +11122,15 @@
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="B749" t="s">
-        <v>1267</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="B750" t="s">
         <v>1</v>
@@ -11096,15 +11138,15 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1269</v>
+        <v>1279</v>
       </c>
       <c r="B751" t="s">
-        <v>1270</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="B752" t="s">
         <v>1</v>
@@ -11112,79 +11154,79 @@
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1272</v>
+        <v>1282</v>
       </c>
       <c r="B753" t="s">
-        <v>1273</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
       <c r="B754" t="s">
-        <v>1275</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1276</v>
+        <v>1286</v>
       </c>
       <c r="B755" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1278</v>
+        <v>1288</v>
       </c>
       <c r="B756" t="s">
-        <v>1279</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="B757" t="s">
-        <v>1281</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>1282</v>
+        <v>1292</v>
       </c>
       <c r="B758" t="s">
-        <v>1283</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>1284</v>
+        <v>1294</v>
       </c>
       <c r="B759" t="s">
-        <v>1285</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="B760" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="B761" t="s">
-        <v>1289</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1290</v>
+        <v>1300</v>
       </c>
       <c r="B762" t="s">
         <v>1</v>
@@ -11192,71 +11234,71 @@
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>1291</v>
+        <v>1301</v>
       </c>
       <c r="B763" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>1293</v>
+        <v>1303</v>
       </c>
       <c r="B764" t="s">
-        <v>1294</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>1295</v>
+        <v>1305</v>
       </c>
       <c r="B765" t="s">
-        <v>1296</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>1297</v>
+        <v>1307</v>
       </c>
       <c r="B766" t="s">
-        <v>1298</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>1299</v>
+        <v>1309</v>
       </c>
       <c r="B767" t="s">
-        <v>1300</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>1301</v>
+        <v>1311</v>
       </c>
       <c r="B768" t="s">
-        <v>1302</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>1303</v>
+        <v>1313</v>
       </c>
       <c r="B769" t="s">
-        <v>1304</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>1305</v>
+        <v>1315</v>
       </c>
       <c r="B770" t="s">
-        <v>1306</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>1307</v>
+        <v>1317</v>
       </c>
       <c r="B771" t="s">
         <v>1</v>
@@ -11264,39 +11306,39 @@
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>1308</v>
+        <v>1318</v>
       </c>
       <c r="B772" t="s">
-        <v>1309</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="B773" t="s">
-        <v>1311</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>1312</v>
+        <v>1322</v>
       </c>
       <c r="B774" t="s">
-        <v>1313</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>1314</v>
+        <v>1324</v>
       </c>
       <c r="B775" t="s">
-        <v>1315</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="B776" t="s">
         <v>1</v>
@@ -11304,7 +11346,7 @@
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>1317</v>
+        <v>1327</v>
       </c>
       <c r="B777" t="s">
         <v>1</v>
@@ -11312,23 +11354,23 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="B778" t="s">
-        <v>1319</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>1320</v>
+        <v>1330</v>
       </c>
       <c r="B779" t="s">
-        <v>1321</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>1322</v>
+        <v>1332</v>
       </c>
       <c r="B780" t="s">
         <v>1</v>
@@ -11336,15 +11378,15 @@
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>1323</v>
+        <v>1333</v>
       </c>
       <c r="B781" t="s">
-        <v>1324</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>1325</v>
+        <v>1335</v>
       </c>
       <c r="B782" t="s">
         <v>1</v>
@@ -11352,7 +11394,7 @@
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>1326</v>
+        <v>1336</v>
       </c>
       <c r="B783" t="s">
         <v>1</v>
@@ -11360,7 +11402,7 @@
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>1327</v>
+        <v>1337</v>
       </c>
       <c r="B784" t="s">
         <v>1</v>
@@ -11368,7 +11410,7 @@
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>1328</v>
+        <v>1338</v>
       </c>
       <c r="B785" t="s">
         <v>1</v>
@@ -11376,7 +11418,7 @@
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>1329</v>
+        <v>1339</v>
       </c>
       <c r="B786" t="s">
         <v>1</v>
@@ -11384,23 +11426,23 @@
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>1330</v>
+        <v>1340</v>
       </c>
       <c r="B787" t="s">
-        <v>1331</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>1332</v>
+        <v>1342</v>
       </c>
       <c r="B788" t="s">
-        <v>1333</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>1334</v>
+        <v>1344</v>
       </c>
       <c r="B789" t="s">
         <v>1</v>
@@ -11408,31 +11450,31 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>1335</v>
+        <v>1345</v>
       </c>
       <c r="B790" t="s">
-        <v>1336</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>1337</v>
+        <v>1347</v>
       </c>
       <c r="B791" t="s">
-        <v>1338</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>1339</v>
+        <v>1349</v>
       </c>
       <c r="B792" t="s">
-        <v>1340</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>1341</v>
+        <v>1351</v>
       </c>
       <c r="B793" t="s">
         <v>1</v>
@@ -11440,55 +11482,55 @@
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1342</v>
+        <v>1352</v>
       </c>
       <c r="B794" t="s">
-        <v>1343</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1344</v>
+        <v>1354</v>
       </c>
       <c r="B795" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="B796" t="s">
-        <v>1347</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>1348</v>
+        <v>1358</v>
       </c>
       <c r="B797" t="s">
-        <v>1349</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="B798" t="s">
-        <v>1351</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1352</v>
+        <v>1362</v>
       </c>
       <c r="B799" t="s">
-        <v>1353</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1354</v>
+        <v>1364</v>
       </c>
       <c r="B800" t="s">
         <v>1</v>
@@ -11496,31 +11538,31 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>1355</v>
+        <v>1365</v>
       </c>
       <c r="B801" t="s">
-        <v>1356</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>1357</v>
+        <v>1367</v>
       </c>
       <c r="B802" t="s">
-        <v>1358</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>1359</v>
+        <v>1369</v>
       </c>
       <c r="B803" t="s">
-        <v>1360</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>1361</v>
+        <v>1371</v>
       </c>
       <c r="B804" t="s">
         <v>1</v>
@@ -11528,7 +11570,7 @@
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>1362</v>
+        <v>1372</v>
       </c>
       <c r="B805" t="s">
         <v>1</v>
@@ -11536,31 +11578,31 @@
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>1363</v>
+        <v>1373</v>
       </c>
       <c r="B806" t="s">
-        <v>1364</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>1365</v>
+        <v>1375</v>
       </c>
       <c r="B807" t="s">
-        <v>1366</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>1367</v>
+        <v>1377</v>
       </c>
       <c r="B808" t="s">
-        <v>1368</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>1369</v>
+        <v>1379</v>
       </c>
       <c r="B809" t="s">
         <v>1</v>
@@ -11568,7 +11610,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>1370</v>
+        <v>1380</v>
       </c>
       <c r="B810" t="s">
         <v>1</v>
@@ -11576,39 +11618,39 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1371</v>
+        <v>1381</v>
       </c>
       <c r="B811" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1373</v>
+        <v>1383</v>
       </c>
       <c r="B812" t="s">
-        <v>1374</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="B813" t="s">
-        <v>1376</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="B814" t="s">
-        <v>1378</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1379</v>
+        <v>1389</v>
       </c>
       <c r="B815" t="s">
         <v>1</v>
@@ -11616,7 +11658,7 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="B816" t="s">
         <v>1</v>
@@ -11624,7 +11666,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1381</v>
+        <v>1391</v>
       </c>
       <c r="B817" t="s">
         <v>1</v>
@@ -11632,39 +11674,39 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1382</v>
+        <v>1392</v>
       </c>
       <c r="B818" t="s">
-        <v>1383</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1384</v>
+        <v>1394</v>
       </c>
       <c r="B819" t="s">
-        <v>1385</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1386</v>
+        <v>1396</v>
       </c>
       <c r="B820" t="s">
-        <v>1387</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1388</v>
+        <v>1398</v>
       </c>
       <c r="B821" t="s">
-        <v>1389</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="B822" t="s">
         <v>1</v>
@@ -11672,7 +11714,7 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="B823" t="s">
         <v>1</v>
@@ -11680,7 +11722,7 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1392</v>
+        <v>1402</v>
       </c>
       <c r="B824" t="s">
         <v>1</v>
@@ -11688,31 +11730,31 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1393</v>
+        <v>1403</v>
       </c>
       <c r="B825" t="s">
-        <v>1394</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="B826" t="s">
-        <v>1396</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="B827" t="s">
-        <v>1398</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1399</v>
+        <v>1409</v>
       </c>
       <c r="B828" t="s">
         <v>1</v>
@@ -11720,15 +11762,15 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="B829" t="s">
-        <v>1401</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1402</v>
+        <v>1412</v>
       </c>
       <c r="B830" t="s">
         <v>1</v>
@@ -11736,7 +11778,7 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="B831" t="s">
         <v>1</v>
@@ -11744,55 +11786,55 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1404</v>
+        <v>1414</v>
       </c>
       <c r="B832" t="s">
-        <v>1</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1405</v>
+        <v>1416</v>
       </c>
       <c r="B833" t="s">
-        <v>1406</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1407</v>
+        <v>1418</v>
       </c>
       <c r="B834" t="s">
-        <v>1408</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1409</v>
+        <v>1420</v>
       </c>
       <c r="B835" t="s">
-        <v>1410</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1411</v>
+        <v>1422</v>
       </c>
       <c r="B836" t="s">
-        <v>1412</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1413</v>
+        <v>1424</v>
       </c>
       <c r="B837" t="s">
-        <v>1414</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1415</v>
+        <v>1426</v>
       </c>
       <c r="B838" t="s">
         <v>1</v>
@@ -11800,7 +11842,7 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1416</v>
+        <v>1427</v>
       </c>
       <c r="B839" t="s">
         <v>1</v>
@@ -11808,7 +11850,7 @@
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1417</v>
+        <v>1428</v>
       </c>
       <c r="B840" t="s">
         <v>1</v>
@@ -11816,15 +11858,15 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1418</v>
+        <v>1429</v>
       </c>
       <c r="B841" t="s">
-        <v>1419</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1420</v>
+        <v>1431</v>
       </c>
       <c r="B842" t="s">
         <v>1</v>
@@ -11832,7 +11874,7 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1421</v>
+        <v>1432</v>
       </c>
       <c r="B843" t="s">
         <v>1</v>
@@ -11840,15 +11882,15 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1422</v>
+        <v>1433</v>
       </c>
       <c r="B844" t="s">
-        <v>1423</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1424</v>
+        <v>1435</v>
       </c>
       <c r="B845" t="s">
         <v>1</v>
@@ -11856,23 +11898,23 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1425</v>
+        <v>1436</v>
       </c>
       <c r="B846" t="s">
-        <v>1426</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1427</v>
+        <v>1438</v>
       </c>
       <c r="B847" t="s">
-        <v>1428</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1429</v>
+        <v>1440</v>
       </c>
       <c r="B848" t="s">
         <v>1</v>
@@ -11880,7 +11922,7 @@
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1430</v>
+        <v>1441</v>
       </c>
       <c r="B849" t="s">
         <v>1</v>
@@ -11888,31 +11930,31 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1431</v>
+        <v>1442</v>
       </c>
       <c r="B850" t="s">
-        <v>1</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1432</v>
+        <v>1444</v>
       </c>
       <c r="B851" t="s">
-        <v>1433</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1434</v>
+        <v>1446</v>
       </c>
       <c r="B852" t="s">
-        <v>1</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1435</v>
+        <v>1448</v>
       </c>
       <c r="B853" t="s">
         <v>1</v>
@@ -11920,15 +11962,15 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1436</v>
+        <v>1449</v>
       </c>
       <c r="B854" t="s">
-        <v>1</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1437</v>
+        <v>1451</v>
       </c>
       <c r="B855" t="s">
         <v>1</v>
@@ -11936,47 +11978,47 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1438</v>
+        <v>1452</v>
       </c>
       <c r="B856" t="s">
-        <v>1439</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1440</v>
+        <v>1454</v>
       </c>
       <c r="B857" t="s">
-        <v>1441</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1442</v>
+        <v>1456</v>
       </c>
       <c r="B858" t="s">
-        <v>1443</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1444</v>
+        <v>1458</v>
       </c>
       <c r="B859" t="s">
-        <v>1445</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1446</v>
+        <v>1460</v>
       </c>
       <c r="B860" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1448</v>
+        <v>1462</v>
       </c>
       <c r="B861" t="s">
         <v>1</v>
@@ -11984,103 +12026,103 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1449</v>
+        <v>1463</v>
       </c>
       <c r="B862" t="s">
-        <v>1450</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1451</v>
+        <v>1465</v>
       </c>
       <c r="B863" t="s">
-        <v>1452</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1453</v>
+        <v>1467</v>
       </c>
       <c r="B864" t="s">
-        <v>1454</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1455</v>
+        <v>1469</v>
       </c>
       <c r="B865" t="s">
-        <v>1456</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1457</v>
+        <v>1471</v>
       </c>
       <c r="B866" t="s">
-        <v>1458</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1459</v>
+        <v>1473</v>
       </c>
       <c r="B867" t="s">
-        <v>1460</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1461</v>
+        <v>1475</v>
       </c>
       <c r="B868" t="s">
-        <v>1462</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1463</v>
+        <v>1477</v>
       </c>
       <c r="B869" t="s">
-        <v>1464</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1465</v>
+        <v>1479</v>
       </c>
       <c r="B870" t="s">
-        <v>1466</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1467</v>
+        <v>1481</v>
       </c>
       <c r="B871" t="s">
-        <v>1468</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="B872" t="s">
-        <v>1470</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1471</v>
+        <v>1485</v>
       </c>
       <c r="B873" t="s">
-        <v>1472</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>1473</v>
+        <v>1487</v>
       </c>
       <c r="B874" t="s">
         <v>1</v>
@@ -12088,15 +12130,15 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>1474</v>
+        <v>1488</v>
       </c>
       <c r="B875" t="s">
-        <v>1475</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>1476</v>
+        <v>1490</v>
       </c>
       <c r="B876" t="s">
         <v>1</v>
@@ -12104,15 +12146,15 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1477</v>
+        <v>1491</v>
       </c>
       <c r="B877" t="s">
-        <v>1478</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1479</v>
+        <v>1493</v>
       </c>
       <c r="B878" t="s">
         <v>1</v>
@@ -12120,15 +12162,15 @@
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1480</v>
+        <v>1494</v>
       </c>
       <c r="B879" t="s">
-        <v>1481</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1482</v>
+        <v>1496</v>
       </c>
       <c r="B880" t="s">
         <v>75</v>
@@ -12136,15 +12178,15 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1483</v>
+        <v>1497</v>
       </c>
       <c r="B881" t="s">
-        <v>1484</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1485</v>
+        <v>1499</v>
       </c>
       <c r="B882" t="s">
         <v>1</v>
@@ -12152,39 +12194,39 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1486</v>
+        <v>1500</v>
       </c>
       <c r="B883" t="s">
-        <v>1487</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1488</v>
+        <v>1502</v>
       </c>
       <c r="B884" t="s">
-        <v>1489</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1490</v>
+        <v>1504</v>
       </c>
       <c r="B885" t="s">
-        <v>1491</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1492</v>
+        <v>1506</v>
       </c>
       <c r="B886" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1494</v>
+        <v>1508</v>
       </c>
       <c r="B887" t="s">
         <v>1</v>
@@ -12192,7 +12234,7 @@
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1495</v>
+        <v>1509</v>
       </c>
       <c r="B888" t="s">
         <v>1</v>
@@ -12200,7 +12242,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1496</v>
+        <v>1510</v>
       </c>
       <c r="B889" t="s">
         <v>1</v>
@@ -12208,7 +12250,7 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1497</v>
+        <v>1511</v>
       </c>
       <c r="B890" t="s">
         <v>1</v>
@@ -12216,15 +12258,15 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1498</v>
+        <v>1512</v>
       </c>
       <c r="B891" t="s">
-        <v>1499</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1500</v>
+        <v>1514</v>
       </c>
       <c r="B892" t="s">
         <v>1</v>
@@ -12232,15 +12274,15 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1501</v>
+        <v>1515</v>
       </c>
       <c r="B893" t="s">
-        <v>1502</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="B894" t="s">
         <v>1</v>
@@ -12248,7 +12290,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1504</v>
+        <v>1518</v>
       </c>
       <c r="B895" t="s">
         <v>1</v>
@@ -12256,7 +12298,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1505</v>
+        <v>1519</v>
       </c>
       <c r="B896" t="s">
         <v>1</v>
@@ -12264,7 +12306,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1506</v>
+        <v>1520</v>
       </c>
       <c r="B897" t="s">
         <v>1</v>
@@ -12272,23 +12314,23 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>1507</v>
+        <v>1521</v>
       </c>
       <c r="B898" t="s">
-        <v>1508</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1509</v>
+        <v>1523</v>
       </c>
       <c r="B899" t="s">
-        <v>1510</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1511</v>
+        <v>1525</v>
       </c>
       <c r="B900" t="s">
         <v>1</v>
@@ -12296,7 +12338,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1512</v>
+        <v>1526</v>
       </c>
       <c r="B901" t="s">
         <v>1</v>
@@ -12304,79 +12346,79 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1513</v>
+        <v>1527</v>
       </c>
       <c r="B902" t="s">
-        <v>1514</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1515</v>
+        <v>1529</v>
       </c>
       <c r="B903" t="s">
-        <v>1516</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>1517</v>
+        <v>1531</v>
       </c>
       <c r="B904" t="s">
-        <v>1518</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>1519</v>
+        <v>1533</v>
       </c>
       <c r="B905" t="s">
-        <v>1520</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>1521</v>
+        <v>1535</v>
       </c>
       <c r="B906" t="s">
-        <v>1522</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>1523</v>
+        <v>1537</v>
       </c>
       <c r="B907" t="s">
-        <v>1524</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>1525</v>
+        <v>1539</v>
       </c>
       <c r="B908" t="s">
-        <v>1526</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>1527</v>
+        <v>1541</v>
       </c>
       <c r="B909" t="s">
-        <v>1528</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>1529</v>
+        <v>1543</v>
       </c>
       <c r="B910" t="s">
-        <v>1530</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>1531</v>
+        <v>1545</v>
       </c>
       <c r="B911" t="s">
         <v>75</v>
@@ -12384,23 +12426,23 @@
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>1532</v>
+        <v>1546</v>
       </c>
       <c r="B912" t="s">
-        <v>1533</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>1534</v>
+        <v>1548</v>
       </c>
       <c r="B913" t="s">
-        <v>1535</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>1536</v>
+        <v>1550</v>
       </c>
       <c r="B914" t="s">
         <v>1</v>
@@ -12408,199 +12450,199 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>1537</v>
+        <v>1551</v>
       </c>
       <c r="B915" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="B916" t="s">
-        <v>1540</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="B917" t="s">
-        <v>1542</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>1543</v>
+        <v>1557</v>
       </c>
       <c r="B918" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>1545</v>
+        <v>1559</v>
       </c>
       <c r="B919" t="s">
-        <v>1546</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>1547</v>
+        <v>1561</v>
       </c>
       <c r="B920" t="s">
-        <v>1548</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>1549</v>
+        <v>1563</v>
       </c>
       <c r="B921" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>1551</v>
+        <v>1565</v>
       </c>
       <c r="B922" t="s">
-        <v>1552</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>1553</v>
+        <v>1567</v>
       </c>
       <c r="B923" t="s">
-        <v>1554</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="B924" t="s">
-        <v>1556</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>1557</v>
+        <v>1571</v>
       </c>
       <c r="B925" t="s">
-        <v>1558</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>1559</v>
+        <v>1573</v>
       </c>
       <c r="B926" t="s">
-        <v>1560</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>1561</v>
+        <v>1575</v>
       </c>
       <c r="B927" t="s">
-        <v>1562</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>1563</v>
+        <v>1577</v>
       </c>
       <c r="B928" t="s">
-        <v>1564</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>1565</v>
+        <v>1579</v>
       </c>
       <c r="B929" t="s">
-        <v>1566</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>1567</v>
+        <v>1581</v>
       </c>
       <c r="B930" t="s">
-        <v>1568</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>1569</v>
+        <v>1583</v>
       </c>
       <c r="B931" t="s">
-        <v>1570</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="B932" t="s">
-        <v>1572</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>1573</v>
+        <v>1587</v>
       </c>
       <c r="B933" t="s">
-        <v>1574</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="B934" t="s">
-        <v>1576</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>1577</v>
+        <v>1591</v>
       </c>
       <c r="B935" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>1579</v>
+        <v>1593</v>
       </c>
       <c r="B936" t="s">
-        <v>1580</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>1581</v>
+        <v>1595</v>
       </c>
       <c r="B937" t="s">
-        <v>1582</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>1583</v>
+        <v>1597</v>
       </c>
       <c r="B938" t="s">
-        <v>1584</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="B939" t="s">
         <v>1</v>
@@ -12608,47 +12650,47 @@
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>1586</v>
+        <v>1600</v>
       </c>
       <c r="B940" t="s">
-        <v>1587</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>1588</v>
+        <v>1602</v>
       </c>
       <c r="B941" t="s">
-        <v>1589</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>1590</v>
+        <v>1604</v>
       </c>
       <c r="B942" t="s">
-        <v>1591</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>1592</v>
+        <v>1606</v>
       </c>
       <c r="B943" t="s">
-        <v>1593</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="s">
-        <v>1594</v>
+        <v>1608</v>
       </c>
       <c r="B944" t="s">
-        <v>1595</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="s">
-        <v>1596</v>
+        <v>1610</v>
       </c>
       <c r="B945" t="s">
         <v>1</v>
@@ -12656,79 +12698,79 @@
     </row>
     <row r="946">
       <c r="A946" t="s">
-        <v>1597</v>
+        <v>1611</v>
       </c>
       <c r="B946" t="s">
-        <v>1598</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="s">
-        <v>1599</v>
+        <v>1613</v>
       </c>
       <c r="B947" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="s">
-        <v>1601</v>
+        <v>1615</v>
       </c>
       <c r="B948" t="s">
-        <v>1602</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="s">
-        <v>1603</v>
+        <v>1617</v>
       </c>
       <c r="B949" t="s">
-        <v>1604</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="s">
-        <v>1605</v>
+        <v>1619</v>
       </c>
       <c r="B950" t="s">
-        <v>1606</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="s">
-        <v>1607</v>
+        <v>1621</v>
       </c>
       <c r="B951" t="s">
-        <v>1608</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="s">
-        <v>1609</v>
+        <v>1623</v>
       </c>
       <c r="B952" t="s">
-        <v>1610</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="s">
-        <v>1611</v>
+        <v>1625</v>
       </c>
       <c r="B953" t="s">
-        <v>1612</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="s">
-        <v>1613</v>
+        <v>1627</v>
       </c>
       <c r="B954" t="s">
-        <v>1614</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="B955" t="s">
         <v>1</v>
@@ -12736,31 +12778,31 @@
     </row>
     <row r="956">
       <c r="A956" t="s">
-        <v>1616</v>
+        <v>1630</v>
       </c>
       <c r="B956" t="s">
-        <v>1617</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="s">
-        <v>1618</v>
+        <v>1632</v>
       </c>
       <c r="B957" t="s">
-        <v>1619</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="s">
-        <v>1620</v>
+        <v>1634</v>
       </c>
       <c r="B958" t="s">
-        <v>1621</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="s">
-        <v>1622</v>
+        <v>1636</v>
       </c>
       <c r="B959" t="s">
         <v>1</v>
@@ -12768,7 +12810,7 @@
     </row>
     <row r="960">
       <c r="A960" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="B960" t="s">
         <v>1</v>
@@ -12776,7 +12818,7 @@
     </row>
     <row r="961">
       <c r="A961" t="s">
-        <v>1624</v>
+        <v>1638</v>
       </c>
       <c r="B961" t="s">
         <v>75</v>
@@ -12784,7 +12826,7 @@
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>1625</v>
+        <v>1639</v>
       </c>
       <c r="B962" t="s">
         <v>75</v>
@@ -12792,15 +12834,15 @@
     </row>
     <row r="963">
       <c r="A963" t="s">
-        <v>1626</v>
+        <v>1640</v>
       </c>
       <c r="B963" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="s">
-        <v>1628</v>
+        <v>1642</v>
       </c>
       <c r="B964" t="s">
         <v>1</v>
@@ -12808,15 +12850,15 @@
     </row>
     <row r="965">
       <c r="A965" t="s">
-        <v>1629</v>
+        <v>1643</v>
       </c>
       <c r="B965" t="s">
-        <v>1630</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="s">
-        <v>1631</v>
+        <v>1645</v>
       </c>
       <c r="B966" t="s">
         <v>1</v>
@@ -12824,7 +12866,7 @@
     </row>
     <row r="967">
       <c r="A967" t="s">
-        <v>1632</v>
+        <v>1646</v>
       </c>
       <c r="B967" t="s">
         <v>1</v>
@@ -12832,7 +12874,7 @@
     </row>
     <row r="968">
       <c r="A968" t="s">
-        <v>1633</v>
+        <v>1647</v>
       </c>
       <c r="B968" t="s">
         <v>1</v>
@@ -12840,31 +12882,31 @@
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>1634</v>
+        <v>1648</v>
       </c>
       <c r="B969" t="s">
-        <v>1635</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>1636</v>
+        <v>1650</v>
       </c>
       <c r="B970" t="s">
-        <v>1637</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>1638</v>
+        <v>1652</v>
       </c>
       <c r="B971" t="s">
-        <v>1639</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>1640</v>
+        <v>1654</v>
       </c>
       <c r="B972" t="s">
         <v>75</v>
@@ -12872,15 +12914,15 @@
     </row>
     <row r="973">
       <c r="A973" t="s">
-        <v>1641</v>
+        <v>1655</v>
       </c>
       <c r="B973" t="s">
-        <v>1642</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="s">
-        <v>1643</v>
+        <v>1657</v>
       </c>
       <c r="B974" t="s">
         <v>1</v>
@@ -12888,23 +12930,23 @@
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>1644</v>
+        <v>1658</v>
       </c>
       <c r="B975" t="s">
-        <v>1645</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>1646</v>
+        <v>1660</v>
       </c>
       <c r="B976" t="s">
-        <v>1647</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>1648</v>
+        <v>1662</v>
       </c>
       <c r="B977" t="s">
         <v>1</v>
@@ -12912,7 +12954,7 @@
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>1649</v>
+        <v>1663</v>
       </c>
       <c r="B978" t="s">
         <v>1</v>
@@ -12920,31 +12962,31 @@
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>1650</v>
+        <v>1664</v>
       </c>
       <c r="B979" t="s">
-        <v>1376</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>1651</v>
+        <v>1665</v>
       </c>
       <c r="B980" t="s">
-        <v>1652</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>1653</v>
+        <v>1667</v>
       </c>
       <c r="B981" t="s">
-        <v>1654</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>1655</v>
+        <v>1669</v>
       </c>
       <c r="B982" t="s">
         <v>1</v>
@@ -12952,79 +12994,79 @@
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>1656</v>
+        <v>1670</v>
       </c>
       <c r="B983" t="s">
-        <v>1657</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>1658</v>
+        <v>1672</v>
       </c>
       <c r="B984" t="s">
-        <v>1659</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>1660</v>
+        <v>1674</v>
       </c>
       <c r="B985" t="s">
-        <v>1661</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>1662</v>
+        <v>1676</v>
       </c>
       <c r="B986" t="s">
-        <v>1663</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>1664</v>
+        <v>1678</v>
       </c>
       <c r="B987" t="s">
-        <v>1665</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>1666</v>
+        <v>1680</v>
       </c>
       <c r="B988" t="s">
-        <v>1667</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>1668</v>
+        <v>1682</v>
       </c>
       <c r="B989" t="s">
-        <v>1669</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>1670</v>
+        <v>1684</v>
       </c>
       <c r="B990" t="s">
-        <v>1671</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="s">
-        <v>1672</v>
+        <v>1686</v>
       </c>
       <c r="B991" t="s">
-        <v>1673</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="s">
-        <v>1674</v>
+        <v>1688</v>
       </c>
       <c r="B992" t="s">
         <v>1</v>
@@ -13032,15 +13074,15 @@
     </row>
     <row r="993">
       <c r="A993" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="B993" t="s">
-        <v>1676</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>1677</v>
+        <v>1691</v>
       </c>
       <c r="B994" t="s">
         <v>1</v>
@@ -13048,7 +13090,7 @@
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>1678</v>
+        <v>1692</v>
       </c>
       <c r="B995" t="s">
         <v>1</v>
@@ -13056,10 +13098,10 @@
     </row>
     <row r="996">
       <c r="A996" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="B996" t="s">
-        <v>1680</v>
+        <v>1694</v>
       </c>
     </row>
   </sheetData>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -77,7 +77,7 @@
     <t>05-050301A</t>
   </si>
   <si>
-    <t>408047ce987223fba9f85e8d7dda986f</t>
+    <t>8506888276693576c92158880b2778a0</t>
   </si>
   <si>
     <t>03-030002TP</t>
@@ -533,7 +533,7 @@
     <t>05-050101A</t>
   </si>
   <si>
-    <t>57287b73631d1dd0760a97d7f3caac2e</t>
+    <t>89d8b8363a38e01d7a16c2da40df1f3c</t>
   </si>
   <si>
     <t>04-040021TM</t>
@@ -590,7 +590,7 @@
     <t>05-050102A</t>
   </si>
   <si>
-    <t>6de338d5b96f4c93b6ec4bb89b59161e</t>
+    <t>8cabc50ed25dbd573a6921609a339df7</t>
   </si>
   <si>
     <t>03-030035TP</t>
@@ -656,7 +656,7 @@
     <t>05-050301TP</t>
   </si>
   <si>
-    <t>50799c60fdb747d4279d38bd5b03aeb8</t>
+    <t>099acd20269d8221cd4fdb8b77193168</t>
   </si>
   <si>
     <t>05-050301TM</t>
@@ -836,7 +836,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>14dc6a7115ed8643d0342c17efbddf27</t>
+    <t>50865ddaa756834b155e8a12a9fb6878</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -866,7 +866,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>546191a602cd86ccda80feba3dc550d8</t>
+    <t>76f66f979d0ed127425772edced54f59</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1502,7 +1502,7 @@
     <t>05-050101TP</t>
   </si>
   <si>
-    <t>3e99b032c7ffd9082e7b4646ae3134b8</t>
+    <t>c6fa7b4bcd9efd33c0b46e83f0d3938d</t>
   </si>
   <si>
     <t>03-030063TC</t>
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2450,7 +2450,7 @@
     <t>05-050313A</t>
   </si>
   <si>
-    <t>1e9f650233b1837146e626f3c41edea3</t>
+    <t>a7094538211176a4493642127d720327</t>
   </si>
   <si>
     <t>902-0204-02040102ATC</t>
@@ -2861,7 +2861,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>bce246d0f326510acf85215689732b93</t>
+    <t>ac6440f27d6bdf0632f1ffe1730f4b3b</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2966,7 +2966,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>c178e29df4f7707ac5dd97e5dfb43e98</t>
+    <t>2b690f85f54ad877602f070b51761aa2</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -3473,7 +3473,7 @@
     <t>05-050313TP</t>
   </si>
   <si>
-    <t>3c97d05e668859254bf07149cb1a8d06</t>
+    <t>9fbc1de2835461ce96e0d065fbdc2ccb</t>
   </si>
   <si>
     <t>01-010004A</t>
@@ -3500,7 +3500,7 @@
     <t>05-050313TC</t>
   </si>
   <si>
-    <t>ed84dfdffacedeec79d20a683308511e</t>
+    <t>8b8f45498a8f0607cad6be289853893b</t>
   </si>
   <si>
     <t>01-010028A</t>
@@ -4073,7 +4073,7 @@
     <t>05-050102TP</t>
   </si>
   <si>
-    <t>90c03a7dd9cf250bec609eba72199372</t>
+    <t>042d3fe35e65dcec9484c707fdbd953d</t>
   </si>
   <si>
     <t>03-030062TC</t>
@@ -4289,7 +4289,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>ff983b6dba0a7b6b341e82f792b83e5f</t>
+    <t>7ae182c84642edc5382f561eaa06598d</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4304,7 +4304,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>f13308e69a2d1e8b94c4a1516c7a0cc4</t>
+    <t>976c8f5e0985ab7716283e7852a946df</t>
   </si>
   <si>
     <t>05-050006TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -1202,7 +1202,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>e485342c765c36244fab6a0d410188bb</t>
+    <t>1701cd60c0fd5c809f2a1e98dd85181c</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>f35cd2720c6d6e18ab5e89ca234f5b7e</t>
+    <t>f359acb0bce62ddc8b0b443d3adad72a</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1244,7 +1244,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>588e4b8b4b02f4b3b76a481722da12f3</t>
+    <t>15e2dc221af3fce6b6db0833049ce66f</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1772,7 +1772,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>0e6c865ef608c20883124ef0380127e2</t>
+    <t>16900adb23af8ab043627443199b4fc5</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -1793,7 +1793,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>258d3ef813ddad27f7ba8abc6388b27b</t>
+    <t>b66efb5c6546772060de0ac4cbfd1afa</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -2636,7 +2636,7 @@
     <t>05-050208TC</t>
   </si>
   <si>
-    <t>4b1b942b40330cd0cc3ceb2b49128d69</t>
+    <t>988b94643e2660daa15f9c369f70b789</t>
   </si>
   <si>
     <t>03-030039A</t>
@@ -2768,7 +2768,7 @@
     <t>05-050009A</t>
   </si>
   <si>
-    <t>397f95ff13cb7f56235d92785ac466a5</t>
+    <t>4f87d9f7a205a1dbbe49e3a094de731b</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -3149,7 +3149,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>d07887befe6d56766f32d3ba049af99e</t>
+    <t>5714d0a0107259283cbc6a8b9eeda9e7</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -4604,7 +4604,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -65,7 +65,7 @@
     <t>05-050305TC</t>
   </si>
   <si>
-    <t>bf88958680fd0ad4437263ca6fdb297f</t>
+    <t>af31c33312e9cbdceb91ba1cae619041</t>
   </si>
   <si>
     <t>03-030002TM</t>
@@ -101,7 +101,7 @@
     <t>05-050207TP</t>
   </si>
   <si>
-    <t>3f566850f7e1fb5e14efe24cd9262168</t>
+    <t>dd7be23b0a967f072967c7d89602e78f</t>
   </si>
   <si>
     <t>915-150012A</t>
@@ -113,7 +113,7 @@
     <t>05-050305TP</t>
   </si>
   <si>
-    <t>3be5860e231c20fa27df04eb4ca8cf98</t>
+    <t>825b50c1077bcc44e9142241e49f1cff</t>
   </si>
   <si>
     <t>05-0709-070921BTP</t>
@@ -152,7 +152,7 @@
     <t>05-050316TC</t>
   </si>
   <si>
-    <t>6bf83fd50321eed05183fd05dcc29b85</t>
+    <t>fa8cb3c3b8b756132399d3332953b0bd</t>
   </si>
   <si>
     <t>03-030059TP</t>
@@ -179,7 +179,7 @@
     <t>05-050302A</t>
   </si>
   <si>
-    <t>a6ed462f4b3da22413d958a0e0aa216f</t>
+    <t>e7c2c0aef67605ee2a88d1c598b2683f</t>
   </si>
   <si>
     <t>02-020005TC</t>
@@ -206,7 +206,7 @@
     <t>05-050316TP</t>
   </si>
   <si>
-    <t>bdfa6c8d82452f12b312fe16aed392ed</t>
+    <t>9969a07157b2257f0fd8700132780393</t>
   </si>
   <si>
     <t>915-150018TP</t>
@@ -689,7 +689,7 @@
     <t>05-050309A</t>
   </si>
   <si>
-    <t>dc47d7dcb14346d6d0beb3cbf823be31</t>
+    <t>01a7a415f0359063e9a59e03cafd8e98</t>
   </si>
   <si>
     <t>04-040003TP</t>
@@ -725,7 +725,7 @@
     <t>05-050312TP</t>
   </si>
   <si>
-    <t>9630a8476f259b238c150ab3f99edf8e</t>
+    <t>9480db809a06505fe676dccf85bf1d75</t>
   </si>
   <si>
     <t>05-0709-070954TC</t>
@@ -740,7 +740,7 @@
     <t>05-050312TC</t>
   </si>
   <si>
-    <t>ff88d21c9f0b469b698693cda95351e9</t>
+    <t>0e5cabff8af1d5481b7c3e17d8c96c98</t>
   </si>
   <si>
     <t>03-030055TP</t>
@@ -860,7 +860,7 @@
     <t>05-050203TP</t>
   </si>
   <si>
-    <t>d54dc554914eb3eb482791129a9f1b55</t>
+    <t>12d24d38c646234d7d05cda9ca8b8076</t>
   </si>
   <si>
     <t>05-050007TP</t>
@@ -875,7 +875,7 @@
     <t>05-050308A</t>
   </si>
   <si>
-    <t>cc991a52b705db26dc7a0813407aaf1f</t>
+    <t>5fa90ebdbc289531432d123ecba8a9cd</t>
   </si>
   <si>
     <t>05-050203TM</t>
@@ -917,7 +917,7 @@
     <t>05-050203TC</t>
   </si>
   <si>
-    <t>460ad78a8776f06c7aa8601798efa385</t>
+    <t>26b3c81df830df1b8eab5101e091d8b5</t>
   </si>
   <si>
     <t>01-110304-11030404A</t>
@@ -947,7 +947,7 @@
     <t>05-050303TP</t>
   </si>
   <si>
-    <t>1003d58c916678b64c8fb9bc851634d1</t>
+    <t>56c15d873c55652037efa85c0e61256c</t>
   </si>
   <si>
     <t>03-030042TM</t>
@@ -974,7 +974,7 @@
     <t>05-050303TC</t>
   </si>
   <si>
-    <t>dacbadc0a71781aab84d5510eb2d5a3a</t>
+    <t>2f3b2814347a9ffef04fc451a611e891</t>
   </si>
   <si>
     <t>01-010010TP</t>
@@ -992,7 +992,7 @@
     <t>05-050305A</t>
   </si>
   <si>
-    <t>20690ceb1cad475a5b571ca87e928d06</t>
+    <t>800d717efa91ff5a59b84a895bd97196</t>
   </si>
   <si>
     <t>04-040001TM</t>
@@ -1037,7 +1037,7 @@
     <t>05-050314TP</t>
   </si>
   <si>
-    <t>88af5bf5ace7bc9f41425d4f63be1fa2</t>
+    <t>5c5ae8f115b3f8982c041013f59312e9</t>
   </si>
   <si>
     <t>902-0204-02040102STC</t>
@@ -1079,7 +1079,7 @@
     <t>05-050314TC</t>
   </si>
   <si>
-    <t>701ed1d847fae8c7ccd569fc1d79d15f</t>
+    <t>e5cb158eb7c88f78f46fce5df8aa9b39</t>
   </si>
   <si>
     <t>902-0204-02040101ATC</t>
@@ -1088,7 +1088,7 @@
     <t>05-050306A</t>
   </si>
   <si>
-    <t>77f66364cc88cbdc1a18e276684ad447</t>
+    <t>9bcfbfdd1d28207dd0d0df4d04d0a876</t>
   </si>
   <si>
     <t>902-0204-02040102STP</t>
@@ -1157,7 +1157,7 @@
     <t>05-050303A</t>
   </si>
   <si>
-    <t>149517503b59ddfc3918c862b96b3067</t>
+    <t>f1ac35b69c56c41e4086c6b0275d1479</t>
   </si>
   <si>
     <t>05-0709-070910TP</t>
@@ -1232,13 +1232,13 @@
     <t>05-050205TP</t>
   </si>
   <si>
-    <t>09dc94ef4f361581164ab3997e67c878</t>
+    <t>2537c24366e2e12fd3cb2e61066ec412</t>
   </si>
   <si>
     <t>05-050304A</t>
   </si>
   <si>
-    <t>09420b52977612a4d86a279f940ff25d</t>
+    <t>f5123e7de2b78d32a70a6953346246ce</t>
   </si>
   <si>
     <t>05-050009TP</t>
@@ -1262,7 +1262,7 @@
     <t>05-050205TC</t>
   </si>
   <si>
-    <t>add83c8ffd62b5c5fff7be16dae8afaf</t>
+    <t>b70d5a3413a2be3ab3b58ac3e96bd586</t>
   </si>
   <si>
     <t>04-040014TM</t>
@@ -1331,7 +1331,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>e0c82a61a67245f79968a744f7b09936</t>
+    <t>bd0c190fdc6ad6858e7db26ed0e1a31c</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1490,7 +1490,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>659242aec416d17e85f02ecbb12330d9</t>
+    <t>36c11d492334114e57cd2f6887dc8b58</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -1520,7 +1520,7 @@
     <t>05-050201TC</t>
   </si>
   <si>
-    <t>66a9960dc0d88e04f3a96d58130f043c</t>
+    <t>9f1c93a1b6c164b4b600c0f09e89154f</t>
   </si>
   <si>
     <t>03-030061TP</t>
@@ -1589,7 +1589,7 @@
     <t>05-050310TC</t>
   </si>
   <si>
-    <t>60115817a4a3be48293379683941555f</t>
+    <t>25e887e5583f35372283f28e92d27333</t>
   </si>
   <si>
     <t>04-040004A</t>
@@ -1637,7 +1637,7 @@
     <t>05-050310TP</t>
   </si>
   <si>
-    <t>4fcc2830cebe5ef789159e5ea8813780</t>
+    <t>a36c23993dcd2e15a775968f6ac17b5b</t>
   </si>
   <si>
     <t>03-030072TM</t>
@@ -1817,7 +1817,7 @@
     <t>05-050201TP</t>
   </si>
   <si>
-    <t>0f1b7e48d003129c49d1a2059acc209b</t>
+    <t>29364419b881cb3062a9df4ab7349651</t>
   </si>
   <si>
     <t>05-0709-070902TM</t>
@@ -2189,7 +2189,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>2e53c6037ada0a5f4509b5c48de7db82</t>
+    <t>e1f70a292fb3beb643a4f3e43fe7ee57</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2372,7 +2372,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>cd6d4751cda79df64f498f4b24da5db7</t>
+    <t>868e881d8cfa61e7418a181b49c7601e</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2444,7 +2444,7 @@
     <t>05-050204A</t>
   </si>
   <si>
-    <t>ac412a65c65171b2378eada58b4f3bd5</t>
+    <t>7e11d9dbca5e14a6169d3edcd00a5c32</t>
   </si>
   <si>
     <t>05-050313A</t>
@@ -2543,7 +2543,7 @@
     <t>05-050205A</t>
   </si>
   <si>
-    <t>90ab25c4405ead4ee0afe1b9d14f2107</t>
+    <t>57d4113904f1dc0c137b2728c40d233c</t>
   </si>
   <si>
     <t>04-040011TM</t>
@@ -2555,7 +2555,7 @@
     <t>05-050314A</t>
   </si>
   <si>
-    <t>2d6ceb7203356c3b73893edf9cda7000</t>
+    <t>73feff9b9fc889606338dd4511865eac</t>
   </si>
   <si>
     <t>901-010202-9010102021TP</t>
@@ -2687,7 +2687,7 @@
     <t>05-050311A</t>
   </si>
   <si>
-    <t>00659defee040ed572c29c341ea04db5</t>
+    <t>f79c33d32f08b5ff0aa0bd9fcef6dc2c</t>
   </si>
   <si>
     <t>05-050208TP</t>
@@ -2717,7 +2717,7 @@
     <t>05-050306TP</t>
   </si>
   <si>
-    <t>e71bf6219416afaac82fb6bc9f5e2fa3</t>
+    <t>e6f7e6ed8a816ffab3bd6a1833ee032c</t>
   </si>
   <si>
     <t>905-9050607-905060701TC</t>
@@ -2756,13 +2756,13 @@
     <t>05-050317TC</t>
   </si>
   <si>
-    <t>7067f67b2942213b4d4713364e70ae2e</t>
+    <t>391af302ebda2244cf8770442ea1af07</t>
   </si>
   <si>
     <t>05-050312A</t>
   </si>
   <si>
-    <t>a9630c418c3f59d6a1b0b360a841ebf0</t>
+    <t>3091490aa5b60503358cb85f6a8240cb</t>
   </si>
   <si>
     <t>05-050009A</t>
@@ -2774,7 +2774,7 @@
     <t>05-050203A</t>
   </si>
   <si>
-    <t>60ddfdefed4769e4fc5a58fc7044c3e5</t>
+    <t>3b6268853f1fa8bd68839f0ef7b0f77b</t>
   </si>
   <si>
     <t>01-080101-010087TM</t>
@@ -2813,7 +2813,7 @@
     <t>05-050317TP</t>
   </si>
   <si>
-    <t>229410bf60ee30df3fa138b86e565bc4</t>
+    <t>b490a8599bb44f03e16e699f50a3053b</t>
   </si>
   <si>
     <t>01-010051TC</t>
@@ -2930,7 +2930,7 @@
     <t>05-050201A</t>
   </si>
   <si>
-    <t>7f4dc12e25c618f37e507de07c1df792</t>
+    <t>eb6dfa8ffd370531febde8b59adcfd16</t>
   </si>
   <si>
     <t>04-040020TC</t>
@@ -2948,7 +2948,7 @@
     <t>05-050310A</t>
   </si>
   <si>
-    <t>41669038dfc6b535dfbec046e1d33aa1</t>
+    <t>d4bebbf518230ca2aa990ad2dc7e13ac</t>
   </si>
   <si>
     <t>915-150008TP</t>
@@ -3023,7 +3023,7 @@
     <t>05-050308TC</t>
   </si>
   <si>
-    <t>c6b34662dbb3d73f48d62ae6dbde660d</t>
+    <t>a967e55f38ad4dd7eb150b3d0c03f0e5</t>
   </si>
   <si>
     <t>02-020002TC</t>
@@ -3041,7 +3041,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>134162bc7e138f3db345fa90ad9f1a3d</t>
+    <t>0b9c566e0f5b6d1080d7457b397c03ca</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3077,7 +3077,7 @@
     <t>05-050308TP</t>
   </si>
   <si>
-    <t>e6f48497af448ef49af760d78c76a34e</t>
+    <t>66c801a01056005954e9d18be923ab21</t>
   </si>
   <si>
     <t>03-030035A</t>
@@ -3308,7 +3308,7 @@
     <t>05-050204TP</t>
   </si>
   <si>
-    <t>f27901d9c6928abaa5448bc98fd3c169</t>
+    <t>69506d8e29770012b06f21a3ef06de36</t>
   </si>
   <si>
     <t>915-150007A</t>
@@ -3362,7 +3362,7 @@
     <t>05-050204TC</t>
   </si>
   <si>
-    <t>29a2a7a244786b74b0f5a6bbb50b99de</t>
+    <t>c34def8415f15a56ed6c596d8adda356</t>
   </si>
   <si>
     <t>04-040015TM</t>
@@ -3371,7 +3371,7 @@
     <t>05-050302TP</t>
   </si>
   <si>
-    <t>8e139870df3053cfbb1e578385924988</t>
+    <t>f868f002b4016f6d6646129be2c2a6c1</t>
   </si>
   <si>
     <t>01-010055TM</t>
@@ -3545,13 +3545,13 @@
     <t>05-050208A</t>
   </si>
   <si>
-    <t>4a0a1f70e7364e195cef4517668fda56</t>
+    <t>01659c7eafacf6dee84b8f9830f0152d</t>
   </si>
   <si>
     <t>05-050317A</t>
   </si>
   <si>
-    <t>8698bccf05cce2f5667bf3d4c8455e29</t>
+    <t>005c764de734828fc6bdbbb991f36770</t>
   </si>
   <si>
     <t>01-010027A</t>
@@ -3617,7 +3617,7 @@
     <t>05-050206TP</t>
   </si>
   <si>
-    <t>a6c0778e5c6025b5eca2a3b5364d1036</t>
+    <t>1411adebe1166b57dc7540f57ea16da0</t>
   </si>
   <si>
     <t>01-010068TM</t>
@@ -3641,7 +3641,7 @@
     <t>05-050206TC</t>
   </si>
   <si>
-    <t>e0fadaae9e7a01f3914884584a6b7517</t>
+    <t>49e6e8f9ed06e3212c670b1732af6eb3</t>
   </si>
   <si>
     <t>04-040013TM</t>
@@ -3725,7 +3725,7 @@
     <t>05-050304TC</t>
   </si>
   <si>
-    <t>c4fe35ca784828d1893f420a8d6d2832</t>
+    <t>799fbc74ee8253704912777ac54737ec</t>
   </si>
   <si>
     <t>03-030043TP</t>
@@ -3737,13 +3737,13 @@
     <t>05-050206A</t>
   </si>
   <si>
-    <t>ef1f7bc09084fe7e760fcd662b2c9eec</t>
+    <t>4ba2893dda91c9e205f8b0fa258cb7bd</t>
   </si>
   <si>
     <t>05-050315A</t>
   </si>
   <si>
-    <t>432f2b12e1f6894d2d49d0752077aa1d</t>
+    <t>4398dab51214844ae1f69721217b712f</t>
   </si>
   <si>
     <t>902-0204-02040101STP</t>
@@ -3806,7 +3806,7 @@
     <t>05-050304TP</t>
   </si>
   <si>
-    <t>62150c20d121c8274d6f90ed3903f51d</t>
+    <t>69d13b3f4c7e12d5e837a43427a48a49</t>
   </si>
   <si>
     <t>04-040002TP</t>
@@ -3854,7 +3854,7 @@
     <t>05-050315TC</t>
   </si>
   <si>
-    <t>3460c0548689483b7415f521fbf687cb</t>
+    <t>35f22da182aa74db4d971175e1f7ff5a</t>
   </si>
   <si>
     <t>01-010046TM</t>
@@ -3869,7 +3869,7 @@
     <t>05-050316A</t>
   </si>
   <si>
-    <t>5e4ab72ee31126c82067e63326a6968e</t>
+    <t>e147113dd5b8c706c06b2aadc32bb7ca</t>
   </si>
   <si>
     <t>902-0204-02040101BTC</t>
@@ -3893,7 +3893,7 @@
     <t>05-050207A</t>
   </si>
   <si>
-    <t>8cbba115c0d3741f462453bd485fd304</t>
+    <t>85e573f71f103e1bfc01a51dc4c1008f</t>
   </si>
   <si>
     <t>02-020006TM</t>
@@ -3944,7 +3944,7 @@
     <t>05-050315TP</t>
   </si>
   <si>
-    <t>d74eb364d395241e4a88ce4dd643a1b4</t>
+    <t>ec8bb2e90a05f054616078e7212bfab6</t>
   </si>
   <si>
     <t>03-030040TP</t>
@@ -4016,7 +4016,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>e43456585f774ed373438d7ef49f2aa3</t>
+    <t>5775b0c75e8855e415257f666150defd</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4037,7 +4037,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>f43b4a6f7cc8bf13c3a92b4b7f8e726d</t>
+    <t>03c66e267ded994d8dd5ddacb499fc1a</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4166,7 +4166,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>ea579b3f30efb72eb919c6a56f538c3e</t>
+    <t>0c1b8c3533265996ed8fa48d76099afa</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4373,7 +4373,7 @@
     <t>05-050202TC</t>
   </si>
   <si>
-    <t>58fca060a06c31d35ca37b7b32ae2d13</t>
+    <t>c84e23c3a8123f8e8bd33e3e35b003a0</t>
   </si>
   <si>
     <t>03-030062TP</t>
@@ -4391,7 +4391,7 @@
     <t>05-050311TC</t>
   </si>
   <si>
-    <t>7522cf9fbb024ae1c150b2151111be09</t>
+    <t>6ec8c0785f7b16239d4d000394e0bda0</t>
   </si>
   <si>
     <t>04-040014A</t>
@@ -4418,7 +4418,7 @@
     <t>05-050311TP</t>
   </si>
   <si>
-    <t>fa838f54022d6a8979ed747fda2cb32f</t>
+    <t>59cda5b7f2ce6783165a8ae08efc6d92</t>
   </si>
   <si>
     <t>01-080101-010081TC</t>
@@ -4517,13 +4517,13 @@
     <t>05-050309TC</t>
   </si>
   <si>
-    <t>186b1a836d5aa29ca4cd018da9200e46</t>
+    <t>e4b2856774cbae42b1d120f2d9c0b332</t>
   </si>
   <si>
     <t>05-050002A</t>
   </si>
   <si>
-    <t>7509b2ca97b6b009aa96ff8bb2d842d5</t>
+    <t>7433bb1f821af1563b08782cd69ad453</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4553,7 +4553,7 @@
     <t>05-050309TP</t>
   </si>
   <si>
-    <t>1a091c654aec82de978d555c663bab50</t>
+    <t>ab7e9aa4427c9f9a8cf59a7b8ea39ae3</t>
   </si>
   <si>
     <t>05-050309TM</t>
@@ -4580,7 +4580,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>2a07bf6c6c1eb49dfac0a251abbaf02f</t>
+    <t>9411a4c89dba8c34f087a4e12eb198f5</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4784,7 +4784,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>ee1b5d5b8ff266973aaea21d50fad9fa</t>
+    <t>59aef8db0712138bd6b475a7301a320e</t>
   </si>
   <si>
     <t>01-010006TM</t>
@@ -4919,7 +4919,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>fa45adef370f900924977faca8daa50d</t>
+    <t>6a698cf8d62f24a329f480cae1e2141b</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2681,7 +2681,7 @@
     <t>05-050202A</t>
   </si>
   <si>
-    <t>dcedc3bb0496b5514f1f455c2762bfbb</t>
+    <t>921218d33f5bba627e2f373ae40219c2</t>
   </si>
   <si>
     <t>05-050311A</t>
@@ -2693,7 +2693,7 @@
     <t>05-050208TP</t>
   </si>
   <si>
-    <t>1715ab406c35b7c24e90dcbb31ace64b</t>
+    <t>136907f84a1695f8305181af3522d5f1</t>
   </si>
   <si>
     <t>901-010202-9010102022A</t>
@@ -3398,7 +3398,7 @@
     <t>05-050302TC</t>
   </si>
   <si>
-    <t>72c1a8e6f3d566ecac609952c138676c</t>
+    <t>7e066dfe45567d280d6a3ffbbf63c728</t>
   </si>
   <si>
     <t>01-110304-11030403TP</t>
@@ -4325,7 +4325,7 @@
     <t>05-050202TP</t>
   </si>
   <si>
-    <t>e54e7c48877447368243eafb48fab8ff</t>
+    <t>4ab8df049d5c4d0984ad02982e7e6850</t>
   </si>
   <si>
     <t>05-0709-070903TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>eac6d56063697c4696c84438a0564182</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -671,7 +671,7 @@
     <t>05-050301TC</t>
   </si>
   <si>
-    <t>3f3cb0272d91d93b8d9910216dd98b56</t>
+    <t>9b99ed5dfc22d6e656c41522c8d8880a</t>
   </si>
   <si>
     <t>01-010054TP</t>
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>eac6d56063697c4696c84438a0564182</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -4604,7 +4604,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>d878f735a89572d2273c1e98708e28dd</t>
+    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -4604,7 +4604,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -4604,7 +4604,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>d878f735a89572d2273c1e98708e28dd</t>
+    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -4604,7 +4604,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -77,7 +77,7 @@
     <t>05-050301A</t>
   </si>
   <si>
-    <t>8506888276693576c92158880b2778a0</t>
+    <t>2ae1f19395183ed5b2388788b0763313</t>
   </si>
   <si>
     <t>03-030002TP</t>
@@ -179,7 +179,7 @@
     <t>05-050302A</t>
   </si>
   <si>
-    <t>e7c2c0aef67605ee2a88d1c598b2683f</t>
+    <t>3ab600f8362b7bcfde638b88e63a8edf</t>
   </si>
   <si>
     <t>02-020005TC</t>
@@ -533,7 +533,7 @@
     <t>05-050101A</t>
   </si>
   <si>
-    <t>89d8b8363a38e01d7a16c2da40df1f3c</t>
+    <t>981e561710c6392271f58d6d5de82ad8</t>
   </si>
   <si>
     <t>04-040021TM</t>
@@ -590,7 +590,7 @@
     <t>05-050102A</t>
   </si>
   <si>
-    <t>8cabc50ed25dbd573a6921609a339df7</t>
+    <t>005015f0be3db5f7e4cd377d5bae9a3d</t>
   </si>
   <si>
     <t>03-030035TP</t>
@@ -1502,7 +1502,7 @@
     <t>05-050101TP</t>
   </si>
   <si>
-    <t>c6fa7b4bcd9efd33c0b46e83f0d3938d</t>
+    <t>473e2b694ed3b18268ad2c4e1f834416</t>
   </si>
   <si>
     <t>03-030063TC</t>
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2450,7 +2450,7 @@
     <t>05-050313A</t>
   </si>
   <si>
-    <t>a7094538211176a4493642127d720327</t>
+    <t>ed22506af71d0901f2e012d947ce109b</t>
   </si>
   <si>
     <t>902-0204-02040102ATC</t>
@@ -3371,7 +3371,7 @@
     <t>05-050302TP</t>
   </si>
   <si>
-    <t>f868f002b4016f6d6646129be2c2a6c1</t>
+    <t>83753fff470acdb2d7675839e5d94a25</t>
   </si>
   <si>
     <t>01-010055TM</t>
@@ -3473,7 +3473,7 @@
     <t>05-050313TP</t>
   </si>
   <si>
-    <t>9fbc1de2835461ce96e0d065fbdc2ccb</t>
+    <t>3509aa1997c3bcfb51b1a748dbd724ac</t>
   </si>
   <si>
     <t>01-010004A</t>
@@ -3500,7 +3500,7 @@
     <t>05-050313TC</t>
   </si>
   <si>
-    <t>8b8f45498a8f0607cad6be289853893b</t>
+    <t>e7360a55096f740ab6e9aa80791956d2</t>
   </si>
   <si>
     <t>01-010028A</t>
@@ -4073,7 +4073,7 @@
     <t>05-050102TP</t>
   </si>
   <si>
-    <t>042d3fe35e65dcec9484c707fdbd953d</t>
+    <t>44bb8b5c0ae4d1268d9bac033e211aee</t>
   </si>
   <si>
     <t>03-030062TC</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -836,7 +836,7 @@
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>50865ddaa756834b155e8a12a9fb6878</t>
+    <t>79c6fc1430a3f9e4f6e6c36542af1e17</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -866,7 +866,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>76f66f979d0ed127425772edced54f59</t>
+    <t>92b314f412ebbd43548831cc6d68d234</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2861,7 +2861,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>ac6440f27d6bdf0632f1ffe1730f4b3b</t>
+    <t>259e27a37f0d7f6eb129a5b2bc1816cf</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2966,7 +2966,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>2b690f85f54ad877602f070b51761aa2</t>
+    <t>a5bbea05ff12d3a39e488a47ddf51a4b</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -4289,7 +4289,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>7ae182c84642edc5382f561eaa06598d</t>
+    <t>071ce4cf140698ffa659ba39f35e03c6</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4304,7 +4304,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>976c8f5e0985ab7716283e7852a946df</t>
+    <t>be3e17f9107a367b7bb00230db9b8e17</t>
   </si>
   <si>
     <t>05-050006TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -101,7 +101,7 @@
     <t>05-050207TP</t>
   </si>
   <si>
-    <t>dd7be23b0a967f072967c7d89602e78f</t>
+    <t>6823801810e55ff4c050f38a91e4ee75</t>
   </si>
   <si>
     <t>915-150012A</t>
@@ -152,7 +152,7 @@
     <t>05-050316TC</t>
   </si>
   <si>
-    <t>fa8cb3c3b8b756132399d3332953b0bd</t>
+    <t>3962fd7b709886f150bd31bb3b07ca9e</t>
   </si>
   <si>
     <t>03-030059TP</t>
@@ -206,7 +206,7 @@
     <t>05-050316TP</t>
   </si>
   <si>
-    <t>9969a07157b2257f0fd8700132780393</t>
+    <t>e5cfcd4b711511c2aa6cacf2c915a266</t>
   </si>
   <si>
     <t>915-150018TP</t>
@@ -656,7 +656,7 @@
     <t>05-050301TP</t>
   </si>
   <si>
-    <t>099acd20269d8221cd4fdb8b77193168</t>
+    <t>d7dc2244dcc7fecc58c0c3f61dbc3c9c</t>
   </si>
   <si>
     <t>05-050301TM</t>
@@ -671,7 +671,7 @@
     <t>05-050301TC</t>
   </si>
   <si>
-    <t>9b99ed5dfc22d6e656c41522c8d8880a</t>
+    <t>ffc1acb4f56a9e3a2b0a163ba14a7197</t>
   </si>
   <si>
     <t>01-010054TP</t>
@@ -725,7 +725,7 @@
     <t>05-050312TP</t>
   </si>
   <si>
-    <t>9480db809a06505fe676dccf85bf1d75</t>
+    <t>506c015a866fcfd78105d0dad33e5604</t>
   </si>
   <si>
     <t>05-0709-070954TC</t>
@@ -875,7 +875,7 @@
     <t>05-050308A</t>
   </si>
   <si>
-    <t>5fa90ebdbc289531432d123ecba8a9cd</t>
+    <t>ec4833957306512adf3cd6b652995fbb</t>
   </si>
   <si>
     <t>05-050203TM</t>
@@ -974,7 +974,7 @@
     <t>05-050303TC</t>
   </si>
   <si>
-    <t>2f3b2814347a9ffef04fc451a611e891</t>
+    <t>df06acf56eb967b330d5b4c870ed029f</t>
   </si>
   <si>
     <t>01-010010TP</t>
@@ -1037,7 +1037,7 @@
     <t>05-050314TP</t>
   </si>
   <si>
-    <t>5c5ae8f115b3f8982c041013f59312e9</t>
+    <t>451d116ee64b5aa6bf3d70e50dc98460</t>
   </si>
   <si>
     <t>902-0204-02040102STC</t>
@@ -1079,7 +1079,7 @@
     <t>05-050314TC</t>
   </si>
   <si>
-    <t>e5cb158eb7c88f78f46fce5df8aa9b39</t>
+    <t>7c81ed8327f94681ddb71d7a034dd2ae</t>
   </si>
   <si>
     <t>902-0204-02040101ATC</t>
@@ -1157,7 +1157,7 @@
     <t>05-050303A</t>
   </si>
   <si>
-    <t>f1ac35b69c56c41e4086c6b0275d1479</t>
+    <t>f148727e7d1763d473f4e7d50a0d0537</t>
   </si>
   <si>
     <t>05-0709-070910TP</t>
@@ -1202,7 +1202,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>1701cd60c0fd5c809f2a1e98dd85181c</t>
+    <t>0f0b95fa16b5e960960f40a05e998b7d</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1220,7 +1220,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>f359acb0bce62ddc8b0b443d3adad72a</t>
+    <t>ea9fa2a2d873e401a1d888c0f6376dc2</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1232,7 +1232,7 @@
     <t>05-050205TP</t>
   </si>
   <si>
-    <t>2537c24366e2e12fd3cb2e61066ec412</t>
+    <t>3ae556d2c06d358191ed2723760b46e4</t>
   </si>
   <si>
     <t>05-050304A</t>
@@ -1244,7 +1244,7 @@
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>15e2dc221af3fce6b6db0833049ce66f</t>
+    <t>4b3e211c526bd74d156e50d353f2766a</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1262,7 +1262,7 @@
     <t>05-050205TC</t>
   </si>
   <si>
-    <t>b70d5a3413a2be3ab3b58ac3e96bd586</t>
+    <t>e3be78c7f7ac4ae739d60ebbe7e4cdc0</t>
   </si>
   <si>
     <t>04-040014TM</t>
@@ -1772,7 +1772,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>16900adb23af8ab043627443199b4fc5</t>
+    <t>c501e142b73504eb3b4a45e2f070a253</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -1793,7 +1793,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>b66efb5c6546772060de0ac4cbfd1afa</t>
+    <t>11835b3af42c6721df5009cb6446eec7</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -2543,7 +2543,7 @@
     <t>05-050205A</t>
   </si>
   <si>
-    <t>57d4113904f1dc0c137b2728c40d233c</t>
+    <t>2aad3b51d90da07c415874bee03ca5f1</t>
   </si>
   <si>
     <t>04-040011TM</t>
@@ -2555,7 +2555,7 @@
     <t>05-050314A</t>
   </si>
   <si>
-    <t>73feff9b9fc889606338dd4511865eac</t>
+    <t>875fe72072dbc895784a534a5d3e2e28</t>
   </si>
   <si>
     <t>901-010202-9010102021TP</t>
@@ -2636,7 +2636,7 @@
     <t>05-050208TC</t>
   </si>
   <si>
-    <t>988b94643e2660daa15f9c369f70b789</t>
+    <t>acbe1bd7f6caee304584eab28318db72</t>
   </si>
   <si>
     <t>03-030039A</t>
@@ -2717,7 +2717,7 @@
     <t>05-050306TP</t>
   </si>
   <si>
-    <t>e6f7e6ed8a816ffab3bd6a1833ee032c</t>
+    <t>d187e98f94589cff4479a0c30e4cbae3</t>
   </si>
   <si>
     <t>905-9050607-905060701TC</t>
@@ -2756,19 +2756,19 @@
     <t>05-050317TC</t>
   </si>
   <si>
-    <t>391af302ebda2244cf8770442ea1af07</t>
+    <t>de3989494a8d80f0e897ec548840e892</t>
   </si>
   <si>
     <t>05-050312A</t>
   </si>
   <si>
-    <t>3091490aa5b60503358cb85f6a8240cb</t>
+    <t>85b414f65cb310bc02d3b5a8d2e6aafa</t>
   </si>
   <si>
     <t>05-050009A</t>
   </si>
   <si>
-    <t>4f87d9f7a205a1dbbe49e3a094de731b</t>
+    <t>2ddf8a6cbdefcc7ff12aea3e3911f860</t>
   </si>
   <si>
     <t>05-050203A</t>
@@ -2813,7 +2813,7 @@
     <t>05-050317TP</t>
   </si>
   <si>
-    <t>b490a8599bb44f03e16e699f50a3053b</t>
+    <t>db8b3e160875855515bd36f32b37d052</t>
   </si>
   <si>
     <t>01-010051TC</t>
@@ -3149,7 +3149,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>5714d0a0107259283cbc6a8b9eeda9e7</t>
+    <t>7c10915904a1cd481a667b799bde08c7</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -3398,7 +3398,7 @@
     <t>05-050302TC</t>
   </si>
   <si>
-    <t>7e066dfe45567d280d6a3ffbbf63c728</t>
+    <t>8221a623c2222a4c1107cf2575720ec5</t>
   </si>
   <si>
     <t>01-110304-11030403TP</t>
@@ -3551,7 +3551,7 @@
     <t>05-050317A</t>
   </si>
   <si>
-    <t>005c764de734828fc6bdbbb991f36770</t>
+    <t>1120433771da77469c9c1baa4818b120</t>
   </si>
   <si>
     <t>01-010027A</t>
@@ -3743,7 +3743,7 @@
     <t>05-050315A</t>
   </si>
   <si>
-    <t>4398dab51214844ae1f69721217b712f</t>
+    <t>9f197d1576d87a37f72bad3a0091e36e</t>
   </si>
   <si>
     <t>902-0204-02040101STP</t>
@@ -3854,7 +3854,7 @@
     <t>05-050315TC</t>
   </si>
   <si>
-    <t>35f22da182aa74db4d971175e1f7ff5a</t>
+    <t>18b5b6b7843e3a0c6b5e24f7bb284379</t>
   </si>
   <si>
     <t>01-010046TM</t>
@@ -3869,7 +3869,7 @@
     <t>05-050316A</t>
   </si>
   <si>
-    <t>e147113dd5b8c706c06b2aadc32bb7ca</t>
+    <t>04737aab45fd06f3fd0b30259466fa71</t>
   </si>
   <si>
     <t>902-0204-02040101BTC</t>
@@ -3893,7 +3893,7 @@
     <t>05-050207A</t>
   </si>
   <si>
-    <t>85e573f71f103e1bfc01a51dc4c1008f</t>
+    <t>e9fb843323e7e79fdc96daf231e22da8</t>
   </si>
   <si>
     <t>02-020006TM</t>
@@ -3944,7 +3944,7 @@
     <t>05-050315TP</t>
   </si>
   <si>
-    <t>ec8bb2e90a05f054616078e7212bfab6</t>
+    <t>2000fef9b593309d512616c5c0518c00</t>
   </si>
   <si>
     <t>03-030040TP</t>
@@ -4517,7 +4517,7 @@
     <t>05-050309TC</t>
   </si>
   <si>
-    <t>e4b2856774cbae42b1d120f2d9c0b332</t>
+    <t>3bbb92af73a72d21d7d114abb9b296f8</t>
   </si>
   <si>
     <t>05-050002A</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -65,7 +65,7 @@
     <t>05-050305TC</t>
   </si>
   <si>
-    <t>af31c33312e9cbdceb91ba1cae619041</t>
+    <t>a86f172abe92d0af60bb4038d98e03cc</t>
   </si>
   <si>
     <t>03-030002TM</t>
@@ -113,7 +113,7 @@
     <t>05-050305TP</t>
   </si>
   <si>
-    <t>825b50c1077bcc44e9142241e49f1cff</t>
+    <t>742299c11e8c8c59bb7b5f603c1a2e6a</t>
   </si>
   <si>
     <t>05-0709-070921BTP</t>
@@ -689,7 +689,7 @@
     <t>05-050309A</t>
   </si>
   <si>
-    <t>01a7a415f0359063e9a59e03cafd8e98</t>
+    <t>db7c7e498b94191bfcd16c6c448b1bfe</t>
   </si>
   <si>
     <t>04-040003TP</t>
@@ -740,7 +740,7 @@
     <t>05-050312TC</t>
   </si>
   <si>
-    <t>0e5cabff8af1d5481b7c3e17d8c96c98</t>
+    <t>4bc214ce4cd72bd503d49b28e9677a7d</t>
   </si>
   <si>
     <t>03-030055TP</t>
@@ -860,7 +860,7 @@
     <t>05-050203TP</t>
   </si>
   <si>
-    <t>12d24d38c646234d7d05cda9ca8b8076</t>
+    <t>6f475003b91ee3cb78018a7d7aa84e9e</t>
   </si>
   <si>
     <t>05-050007TP</t>
@@ -917,7 +917,7 @@
     <t>05-050203TC</t>
   </si>
   <si>
-    <t>26b3c81df830df1b8eab5101e091d8b5</t>
+    <t>6fbc15156804e5c603f7f7383995e795</t>
   </si>
   <si>
     <t>01-110304-11030404A</t>
@@ -947,7 +947,7 @@
     <t>05-050303TP</t>
   </si>
   <si>
-    <t>56c15d873c55652037efa85c0e61256c</t>
+    <t>3baf8294f342ef57a23dda7f24b84723</t>
   </si>
   <si>
     <t>03-030042TM</t>
@@ -992,7 +992,7 @@
     <t>05-050305A</t>
   </si>
   <si>
-    <t>800d717efa91ff5a59b84a895bd97196</t>
+    <t>61fc802ceecea34bcfdce0bb4d73e14a</t>
   </si>
   <si>
     <t>04-040001TM</t>
@@ -1088,7 +1088,7 @@
     <t>05-050306A</t>
   </si>
   <si>
-    <t>9bcfbfdd1d28207dd0d0df4d04d0a876</t>
+    <t>55ee5d6fedc9f640bc37338056a6d408</t>
   </si>
   <si>
     <t>902-0204-02040102STP</t>
@@ -1238,7 +1238,7 @@
     <t>05-050304A</t>
   </si>
   <si>
-    <t>f5123e7de2b78d32a70a6953346246ce</t>
+    <t>cbf8650ebfbd315aa407fe5d6cdc6125</t>
   </si>
   <si>
     <t>05-050009TP</t>
@@ -1331,7 +1331,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>bd0c190fdc6ad6858e7db26ed0e1a31c</t>
+    <t>17b8ca1165f6afe47a21d97f4370e838</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1490,7 +1490,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>36c11d492334114e57cd2f6887dc8b58</t>
+    <t>4213e11a1866120908a41b7a6ecab2f4</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -1520,7 +1520,7 @@
     <t>05-050201TC</t>
   </si>
   <si>
-    <t>9f1c93a1b6c164b4b600c0f09e89154f</t>
+    <t>054b87ac6fadadd77b8661668567f1f0</t>
   </si>
   <si>
     <t>03-030061TP</t>
@@ -1589,7 +1589,7 @@
     <t>05-050310TC</t>
   </si>
   <si>
-    <t>25e887e5583f35372283f28e92d27333</t>
+    <t>617afa5dc0b30aa909f7923714c33519</t>
   </si>
   <si>
     <t>04-040004A</t>
@@ -1637,7 +1637,7 @@
     <t>05-050310TP</t>
   </si>
   <si>
-    <t>a36c23993dcd2e15a775968f6ac17b5b</t>
+    <t>5f246cc1a85f7556167eab5089df9d7e</t>
   </si>
   <si>
     <t>03-030072TM</t>
@@ -1817,7 +1817,7 @@
     <t>05-050201TP</t>
   </si>
   <si>
-    <t>29364419b881cb3062a9df4ab7349651</t>
+    <t>ef09ea01ea7b15344d6373f9dc7dd6e4</t>
   </si>
   <si>
     <t>05-0709-070902TM</t>
@@ -2189,7 +2189,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>e1f70a292fb3beb643a4f3e43fe7ee57</t>
+    <t>7ba966fe073162d183913402b06c2788</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2372,7 +2372,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>868e881d8cfa61e7418a181b49c7601e</t>
+    <t>f5a87edab6b688b0022e06744f79f6ae</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2444,7 +2444,7 @@
     <t>05-050204A</t>
   </si>
   <si>
-    <t>7e11d9dbca5e14a6169d3edcd00a5c32</t>
+    <t>470fe079d9166ba4ca5b84ea164d6910</t>
   </si>
   <si>
     <t>05-050313A</t>
@@ -2687,13 +2687,13 @@
     <t>05-050311A</t>
   </si>
   <si>
-    <t>f79c33d32f08b5ff0aa0bd9fcef6dc2c</t>
+    <t>64725d32d6cbf89c19fdb2b51d148b2d</t>
   </si>
   <si>
     <t>05-050208TP</t>
   </si>
   <si>
-    <t>136907f84a1695f8305181af3522d5f1</t>
+    <t>4eedab6b746da735ee74177a709f6dbe</t>
   </si>
   <si>
     <t>901-010202-9010102022A</t>
@@ -2774,7 +2774,7 @@
     <t>05-050203A</t>
   </si>
   <si>
-    <t>3b6268853f1fa8bd68839f0ef7b0f77b</t>
+    <t>812e573b5585b1c6c53c90b7bdc481d5</t>
   </si>
   <si>
     <t>01-080101-010087TM</t>
@@ -2930,7 +2930,7 @@
     <t>05-050201A</t>
   </si>
   <si>
-    <t>eb6dfa8ffd370531febde8b59adcfd16</t>
+    <t>ce7ffbd88adb00583fb4e8593eff66d7</t>
   </si>
   <si>
     <t>04-040020TC</t>
@@ -2948,7 +2948,7 @@
     <t>05-050310A</t>
   </si>
   <si>
-    <t>d4bebbf518230ca2aa990ad2dc7e13ac</t>
+    <t>13f34be79aabcc1359e23da555501037</t>
   </si>
   <si>
     <t>915-150008TP</t>
@@ -3023,7 +3023,7 @@
     <t>05-050308TC</t>
   </si>
   <si>
-    <t>a967e55f38ad4dd7eb150b3d0c03f0e5</t>
+    <t>f8b18eafb45143d6543fd78519b50745</t>
   </si>
   <si>
     <t>02-020002TC</t>
@@ -3041,7 +3041,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>0b9c566e0f5b6d1080d7457b397c03ca</t>
+    <t>16c70f51260e8c5c0939474556b261f3</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3077,7 +3077,7 @@
     <t>05-050308TP</t>
   </si>
   <si>
-    <t>66c801a01056005954e9d18be923ab21</t>
+    <t>fe25c468e050060b993e21d48d781d5c</t>
   </si>
   <si>
     <t>03-030035A</t>
@@ -3308,7 +3308,7 @@
     <t>05-050204TP</t>
   </si>
   <si>
-    <t>69506d8e29770012b06f21a3ef06de36</t>
+    <t>2e5cc65730065762e8d4798d35dbe0ce</t>
   </si>
   <si>
     <t>915-150007A</t>
@@ -3362,7 +3362,7 @@
     <t>05-050204TC</t>
   </si>
   <si>
-    <t>c34def8415f15a56ed6c596d8adda356</t>
+    <t>6543d552b980d758663d9fdf72dbd8e2</t>
   </si>
   <si>
     <t>04-040015TM</t>
@@ -3545,7 +3545,7 @@
     <t>05-050208A</t>
   </si>
   <si>
-    <t>01659c7eafacf6dee84b8f9830f0152d</t>
+    <t>32af589514444a64350b4c5fbc8493d6</t>
   </si>
   <si>
     <t>05-050317A</t>
@@ -3617,7 +3617,7 @@
     <t>05-050206TP</t>
   </si>
   <si>
-    <t>1411adebe1166b57dc7540f57ea16da0</t>
+    <t>6d044d451d14db10e2c453db8aa92744</t>
   </si>
   <si>
     <t>01-010068TM</t>
@@ -3641,7 +3641,7 @@
     <t>05-050206TC</t>
   </si>
   <si>
-    <t>49e6e8f9ed06e3212c670b1732af6eb3</t>
+    <t>14a771ce45abc6edbfcd34d40012eac5</t>
   </si>
   <si>
     <t>04-040013TM</t>
@@ -3725,7 +3725,7 @@
     <t>05-050304TC</t>
   </si>
   <si>
-    <t>799fbc74ee8253704912777ac54737ec</t>
+    <t>c6ad7d5b48a7d6eed7c323ac6b15f70a</t>
   </si>
   <si>
     <t>03-030043TP</t>
@@ -3737,7 +3737,7 @@
     <t>05-050206A</t>
   </si>
   <si>
-    <t>4ba2893dda91c9e205f8b0fa258cb7bd</t>
+    <t>0916ccc9bf552a3cd0790ce6e8c6866e</t>
   </si>
   <si>
     <t>05-050315A</t>
@@ -3806,7 +3806,7 @@
     <t>05-050304TP</t>
   </si>
   <si>
-    <t>69d13b3f4c7e12d5e837a43427a48a49</t>
+    <t>315430436be5f0cd7880be6c439ef769</t>
   </si>
   <si>
     <t>04-040002TP</t>
@@ -4016,7 +4016,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>5775b0c75e8855e415257f666150defd</t>
+    <t>ee83d77ea509e0749a780583f558a49d</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4037,7 +4037,7 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>03c66e267ded994d8dd5ddacb499fc1a</t>
+    <t>7761ed1e94332377519ba1879fb3b0e6</t>
   </si>
   <si>
     <t>03-030072A</t>
@@ -4166,7 +4166,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>0c1b8c3533265996ed8fa48d76099afa</t>
+    <t>d0c92177875d9b21edc2cdad9dc20843</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4373,7 +4373,7 @@
     <t>05-050202TC</t>
   </si>
   <si>
-    <t>c84e23c3a8123f8e8bd33e3e35b003a0</t>
+    <t>f51180a9ac2797328f08d09b056ea6be</t>
   </si>
   <si>
     <t>03-030062TP</t>
@@ -4391,7 +4391,7 @@
     <t>05-050311TC</t>
   </si>
   <si>
-    <t>6ec8c0785f7b16239d4d000394e0bda0</t>
+    <t>5ed77c6ae06fb8ef2acdd1d2547f74d8</t>
   </si>
   <si>
     <t>04-040014A</t>
@@ -4418,7 +4418,7 @@
     <t>05-050311TP</t>
   </si>
   <si>
-    <t>59cda5b7f2ce6783165a8ae08efc6d92</t>
+    <t>79745fa3e156d88d9fe3840de4c7cbc4</t>
   </si>
   <si>
     <t>01-080101-010081TC</t>
@@ -4523,7 +4523,7 @@
     <t>05-050002A</t>
   </si>
   <si>
-    <t>7433bb1f821af1563b08782cd69ad453</t>
+    <t>9358ae6f70c031b6ae2680958026ad73</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4553,7 +4553,7 @@
     <t>05-050309TP</t>
   </si>
   <si>
-    <t>ab7e9aa4427c9f9a8cf59a7b8ea39ae3</t>
+    <t>253716e49b083d7a2c7422ea39a44c5d</t>
   </si>
   <si>
     <t>05-050309TM</t>
@@ -4580,7 +4580,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>9411a4c89dba8c34f087a4e12eb198f5</t>
+    <t>343fcaf6e9e6a1ad265752fa513dc6bf</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4604,7 +4604,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>
@@ -4784,7 +4784,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>59aef8db0712138bd6b475a7301a320e</t>
+    <t>0386ac6b6a8521d246cae9e8aaa264c4</t>
   </si>
   <si>
     <t>01-010006TM</t>
@@ -4919,7 +4919,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>6a698cf8d62f24a329f480cae1e2141b</t>
+    <t>2509c347b18298d5dd28d09dd89d9bb8</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2681,7 +2681,7 @@
     <t>05-050202A</t>
   </si>
   <si>
-    <t>921218d33f5bba627e2f373ae40219c2</t>
+    <t>0469b64bb08b560959c1a4b120224755</t>
   </si>
   <si>
     <t>05-050311A</t>
@@ -4325,7 +4325,7 @@
     <t>05-050202TP</t>
   </si>
   <si>
-    <t>4ab8df049d5c4d0984ad02982e7e6850</t>
+    <t>a32272aa3859c328aa744788c8f65243</t>
   </si>
   <si>
     <t>05-0709-070903TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -4604,7 +4604,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
+    <t>d878f735a89572d2273c1e98708e28dd</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -4604,7 +4604,7 @@
     <t>03-030032A</t>
   </si>
   <si>
-    <t>d878f735a89572d2273c1e98708e28dd</t>
+    <t>c9c849f03081bb7a17b5eba5feebb7ea</t>
   </si>
   <si>
     <t>03-030060TP</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -1472,7 +1472,7 @@
     <t>01-080101-010112TM</t>
   </si>
   <si>
-    <t>8c6e2b75376b8490b816902250befb49</t>
+    <t>0e4158b3be5756e9866cace2776c8db4</t>
   </si>
   <si>
     <t>01-010025TP</t>
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1696">
   <si>
     <t>05-050305TM</t>
   </si>
@@ -29,13 +29,13 @@
     <t>01-010050TP</t>
   </si>
   <si>
-    <t>af91f3692b5c2a074c3f4fbe008ebd6f</t>
+    <t>821d617ccb748bee004129e886366b23</t>
   </si>
   <si>
     <t>01-010035A</t>
   </si>
   <si>
-    <t>4a97e7dfbcdd2b1a8476f0dd150a01ef</t>
+    <t>41719c71caba7b1e33163ba72bfe84aa</t>
   </si>
   <si>
     <t>03-030029A</t>
@@ -107,7 +107,7 @@
     <t>915-150012A</t>
   </si>
   <si>
-    <t>09d75f98149a07c4a0583ae9ca10de4d</t>
+    <t>4b44cb446163485ebb0b311da4abdcc6</t>
   </si>
   <si>
     <t>05-050305TP</t>
@@ -119,7 +119,7 @@
     <t>05-0709-070921BTP</t>
   </si>
   <si>
-    <t>4c6f84b27dcccd77f694c10531a70268</t>
+    <t>05b9491f51ef494cb7e34dadbef1270e</t>
   </si>
   <si>
     <t>01-010010A</t>
@@ -173,7 +173,7 @@
     <t>01-010050TC</t>
   </si>
   <si>
-    <t>f701fc6735e33393ae9dfc09dc1f862b</t>
+    <t>0b806737ac696a894d996b6499d5d1a8</t>
   </si>
   <si>
     <t>05-050302A</t>
@@ -188,19 +188,19 @@
     <t>05-0709-070921BTC</t>
   </si>
   <si>
-    <t>5fd184f870d2af27239c7755601859fa</t>
+    <t>5852ad166ec6983e1f7c2f03b75d3bd2</t>
   </si>
   <si>
     <t>03-030004A</t>
   </si>
   <si>
-    <t>6d62a0557ea936e302361742a90bbf2d</t>
+    <t>4f28fb248e974767ac37a0dceefd7331</t>
   </si>
   <si>
     <t>915-150011A</t>
   </si>
   <si>
-    <t>378ab1f948c4e84c7e2344d013d62a55</t>
+    <t>53fe8e276ff06c3fd44492c69d21f244</t>
   </si>
   <si>
     <t>05-050316TP</t>
@@ -212,7 +212,7 @@
     <t>915-150018TP</t>
   </si>
   <si>
-    <t>62e8009b0bb43fe17664e9f2373a6c8c</t>
+    <t>0993f7a58024c6a48ac3ce721114a5c8</t>
   </si>
   <si>
     <t>03-02010301-030102A</t>
@@ -221,7 +221,7 @@
     <t>915-150018TM</t>
   </si>
   <si>
-    <t>39b20a4d3a33d1313cc52833ba6c0bca</t>
+    <t>b45ce4eb58b920538ebcc1d43fc0184b</t>
   </si>
   <si>
     <t>01-010057A</t>
@@ -248,7 +248,7 @@
     <t>05-0709-070908TC</t>
   </si>
   <si>
-    <t>9908c29b7fab4cef9c80ff46dcf03af6</t>
+    <t>5400dab8b05a98ab638b37351beb6afa</t>
   </si>
   <si>
     <t>05-050105A</t>
@@ -278,19 +278,19 @@
     <t>915-150018TC</t>
   </si>
   <si>
-    <t>6a8ff615cdb00a46b4e5c0f541ed124b</t>
+    <t>a56d0a49802668923272ffd81f20ec30</t>
   </si>
   <si>
     <t>915-150007TP</t>
   </si>
   <si>
-    <t>7d576524d3c4fc8fef7b58eb5f8f284d</t>
+    <t>61fbcac4a0e40b79503dbfe09a088dbc</t>
   </si>
   <si>
     <t>01-010063TP</t>
   </si>
   <si>
-    <t>b3f7614824357fe5c8b54b6288c09e92</t>
+    <t>e7f908c55a61b9f4c5f7a987985fd925</t>
   </si>
   <si>
     <t>01-010032A</t>
@@ -302,7 +302,7 @@
     <t>915-150007TM</t>
   </si>
   <si>
-    <t>b367758740bae7360eac1bc8e5e38bc2</t>
+    <t>6c894387e4343caaa722bdb22cc24fb6</t>
   </si>
   <si>
     <t>01-010063TM</t>
@@ -338,7 +338,7 @@
     <t>05-0709-070908TM</t>
   </si>
   <si>
-    <t>67b7c9f494638cfa165a2cb3d182fc27</t>
+    <t>0f2b5a283bbd0fa2e6f4d204e75a45fb</t>
   </si>
   <si>
     <t>03-030026A</t>
@@ -353,7 +353,7 @@
     <t>05-0709-070908TP</t>
   </si>
   <si>
-    <t>4e05305223e360a8e38718a184190ecd</t>
+    <t>c66752fff0d24cd595df16cead8321f4</t>
   </si>
   <si>
     <t>03-030002A</t>
@@ -368,7 +368,7 @@
     <t>915-150007TC</t>
   </si>
   <si>
-    <t>0159658a61ec1e54769b3e111cd5e338</t>
+    <t>49747575b2941f2d7b203570ce685586</t>
   </si>
   <si>
     <t>04-040012TP</t>
@@ -392,7 +392,7 @@
     <t>905-9050607-905060702TM</t>
   </si>
   <si>
-    <t>b0bfef82cb938c7b37b82ac03dd92e02</t>
+    <t>de587608272e7642fea45dc6a4eec7b4</t>
   </si>
   <si>
     <t>01-010055A</t>
@@ -419,7 +419,7 @@
     <t>905-9050607-905060702TP</t>
   </si>
   <si>
-    <t>9d1d568df4a0a88312f112aaa595d6c1</t>
+    <t>3ff638c668f8683b3239757c18b1bd75</t>
   </si>
   <si>
     <t>03-030025A</t>
@@ -431,7 +431,7 @@
     <t>03-030001A</t>
   </si>
   <si>
-    <t>e9080851709b95373d75ab3d52b1eed3</t>
+    <t>508c4b7f803246bcf6e5c5169d743a75</t>
   </si>
   <si>
     <t>05-050307TP</t>
@@ -446,7 +446,7 @@
     <t>905-9050607-905060702TC</t>
   </si>
   <si>
-    <t>bc13665eac829680b6a0efac910209a9</t>
+    <t>3e37fab3289964e163748ae1ae0dc5eb</t>
   </si>
   <si>
     <t>01-010030A</t>
@@ -533,7 +533,7 @@
     <t>05-050101A</t>
   </si>
   <si>
-    <t>981e561710c6392271f58d6d5de82ad8</t>
+    <t>a6a4ad04bd595317b0079bb650a01d78</t>
   </si>
   <si>
     <t>04-040021TM</t>
@@ -575,7 +575,7 @@
     <t>915-150009TM</t>
   </si>
   <si>
-    <t>c90124b7b564c8fd04454539d0804182</t>
+    <t>1a44f6d0f05186195bc181a560434d4d</t>
   </si>
   <si>
     <t>01-010065TM</t>
@@ -590,7 +590,7 @@
     <t>05-050102A</t>
   </si>
   <si>
-    <t>005015f0be3db5f7e4cd377d5bae9a3d</t>
+    <t>0fec58aacd6a62d325a1710fbf7dc0cf</t>
   </si>
   <si>
     <t>03-030035TP</t>
@@ -602,7 +602,7 @@
     <t>915-150009TP</t>
   </si>
   <si>
-    <t>8c9538fa6d11f86766a4e3d63d121b0e</t>
+    <t>d2e7587229c3885463b891d3614cc054</t>
   </si>
   <si>
     <t>04-040021TC</t>
@@ -632,7 +632,7 @@
     <t>915-150009TC</t>
   </si>
   <si>
-    <t>c44933a8687ca715bd1e53da6d63de28</t>
+    <t>99142123935409b93c41af5ec368f9b2</t>
   </si>
   <si>
     <t>04-040010TP</t>
@@ -665,7 +665,7 @@
     <t>04-040014TC</t>
   </si>
   <si>
-    <t>a412ce738c555f504b3c2fc2563a4afe</t>
+    <t>87a5e69893d7f7e018944f9895caf1d9</t>
   </si>
   <si>
     <t>05-050301TC</t>
@@ -695,7 +695,7 @@
     <t>04-040003TP</t>
   </si>
   <si>
-    <t>9e948857ded2a8589cde9e2d0d74f7f7</t>
+    <t>65691ef982935fd3b44ba3dd108cd83f</t>
   </si>
   <si>
     <t>01-010019A</t>
@@ -710,7 +710,7 @@
     <t>04-040003TM</t>
   </si>
   <si>
-    <t>cd96b58e7ba840c9698dfaad67319aad</t>
+    <t>8faa25e5191430c9e9919d991f82646a</t>
   </si>
   <si>
     <t>01-110304-11030403A</t>
@@ -719,7 +719,7 @@
     <t>01-010043TM</t>
   </si>
   <si>
-    <t>b0a11a3971ce3c114ec540c1c518bf4f</t>
+    <t>7880cb33e90d0f0bb0dad5532b72c6d6</t>
   </si>
   <si>
     <t>05-050312TP</t>
@@ -734,7 +734,7 @@
     <t>04-040003TC</t>
   </si>
   <si>
-    <t>11cbe408a34939d2f06c53505a4dfbb8</t>
+    <t>73ad8a2aeacf9e3eeff989980e0e8450</t>
   </si>
   <si>
     <t>05-050312TC</t>
@@ -830,13 +830,13 @@
     <t>01-010043TC</t>
   </si>
   <si>
-    <t>e7b56bcf0d89e5e16dceb6f97a42f1f9</t>
+    <t>4eabe142441c98a110c9ee12d712cfe6</t>
   </si>
   <si>
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>79c6fc1430a3f9e4f6e6c36542af1e17</t>
+    <t>b65a056e377dd16eedcda4f04a751251</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -866,7 +866,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>92b314f412ebbd43548831cc6d68d234</t>
+    <t>26775f8fb4f7818f49d5dc49b38a3129</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1007,7 +1007,7 @@
     <t>05-0709-070906AA</t>
   </si>
   <si>
-    <t>ec1698ab8e6353b5c9c7fcc6b4c8e660</t>
+    <t>1d10f1f6af396db708ccf4ee098150ca</t>
   </si>
   <si>
     <t>01-010067TC</t>
@@ -1061,13 +1061,13 @@
     <t>05-0709-070910TC</t>
   </si>
   <si>
-    <t>b7d2fb4e6114387d8b68a8ec6efef78b</t>
+    <t>8ef4cd605a3cf46667f8182712494327</t>
   </si>
   <si>
     <t>05-0709-070910TM</t>
   </si>
   <si>
-    <t>c7b13c896d79f110af279a23b4fc0266</t>
+    <t>8d7e340b825b66d5861497c1e780ddc2</t>
   </si>
   <si>
     <t>01-010045TP</t>
@@ -1100,7 +1100,7 @@
     <t>05-0709-070906BA</t>
   </si>
   <si>
-    <t>8eb157a8fa1bbe10c34f8a5bf203d4b3</t>
+    <t>90d8ac6682832f94ac5098dfcf75478f</t>
   </si>
   <si>
     <t>01-010056TC</t>
@@ -1163,7 +1163,7 @@
     <t>05-0709-070910TP</t>
   </si>
   <si>
-    <t>bb9ffa8ad25621f081e6aa7a6eb95859</t>
+    <t>3e431fb07fb0f6c9694ec63ca9dc0768</t>
   </si>
   <si>
     <t>01-010045TC</t>
@@ -1214,7 +1214,7 @@
     <t>03-030006A</t>
   </si>
   <si>
-    <t>8db38e28a1f46406c8d92bc388bb0885</t>
+    <t>2449228716b6538cd66d5bc8c14cf808</t>
   </si>
   <si>
     <t>05-050009TM</t>
@@ -1253,7 +1253,7 @@
     <t>04-040014TP</t>
   </si>
   <si>
-    <t>a6aa62789d57a04a889943c1037ac8a7</t>
+    <t>0defa52e30cb2325fa7a2ac126c3721d</t>
   </si>
   <si>
     <t>03-030042TC</t>
@@ -1268,7 +1268,7 @@
     <t>04-040014TM</t>
   </si>
   <si>
-    <t>492d3a39d5a70a93cd6c37e584ad93d6</t>
+    <t>fca3f688af13cc97c5e08c9d3cdb5ec4</t>
   </si>
   <si>
     <t>03-02010301-030089TM</t>
@@ -1298,7 +1298,7 @@
     <t>01-080101-010091TM</t>
   </si>
   <si>
-    <t>19fc0070b6cb6aaf7ebcf6b8d1e992db</t>
+    <t>3485dcb96c4cad67ffca40b22f7a021a</t>
   </si>
   <si>
     <t>01-010058TM</t>
@@ -1400,7 +1400,7 @@
     <t>01-080101-010091TC</t>
   </si>
   <si>
-    <t>4eb30eab2e23b782208c6a5b2be44559</t>
+    <t>6954b707057466638bc105dedcc0ae2b</t>
   </si>
   <si>
     <t>03-030041TP</t>
@@ -1502,7 +1502,7 @@
     <t>05-050101TP</t>
   </si>
   <si>
-    <t>473e2b694ed3b18268ad2c4e1f834416</t>
+    <t>70a8a24919664930809e813e115083b9</t>
   </si>
   <si>
     <t>03-030063TC</t>
@@ -1544,7 +1544,7 @@
     <t>915-150011TP</t>
   </si>
   <si>
-    <t>0c26fd91b9125946602969e60614ecb8</t>
+    <t>e854ca8a23b47c0d6e9010f4816e8974</t>
   </si>
   <si>
     <t>01-010014TP</t>
@@ -1571,7 +1571,7 @@
     <t>905-9050607-905060701A</t>
   </si>
   <si>
-    <t>b2a61c1c546004cbbd4486f2e85dab05</t>
+    <t>7e910355cac59aae9cdb5abe67f245c8</t>
   </si>
   <si>
     <t>01-080101-010093TM</t>
@@ -1604,7 +1604,7 @@
     <t>915-150011TC</t>
   </si>
   <si>
-    <t>856b6031b20a0979bfaf8d26d1b23bbe</t>
+    <t>08fee30ea443d574b66bedbbb56d1561</t>
   </si>
   <si>
     <t>03-030008TP</t>
@@ -1619,7 +1619,7 @@
     <t>915-150011TM</t>
   </si>
   <si>
-    <t>903bb20630a8ace4e47ca2fd1a725f41</t>
+    <t>6f20c78dbc6676815780eb9ecb83d509</t>
   </si>
   <si>
     <t>03-030072TP</t>
@@ -1652,7 +1652,7 @@
     <t>01-010049TP</t>
   </si>
   <si>
-    <t>bd28a05aac77a0bd798d2871eedfbe58</t>
+    <t>bfb7a011b20a35d6c9a0d8ffa3efe1ac</t>
   </si>
   <si>
     <t>01-010003TP</t>
@@ -1673,7 +1673,7 @@
     <t>01-010049TM</t>
   </si>
   <si>
-    <t>8154777e2c8ce05773d7088ed02de109</t>
+    <t>e956c7a7df01a3d09562f57bb09129a4</t>
   </si>
   <si>
     <t>01-080101-010082TM</t>
@@ -1685,7 +1685,7 @@
     <t>04-040003A</t>
   </si>
   <si>
-    <t>d743159f8dd21ff896b707521e0082c6</t>
+    <t>7741b7ed09595472064d877c3a04e492</t>
   </si>
   <si>
     <t>03-02010301-030081A</t>
@@ -1712,7 +1712,7 @@
     <t>05-0709-070902TC</t>
   </si>
   <si>
-    <t>b40b1af66372a7b4200f93a3b9a705ab</t>
+    <t>78141aa3ad407c25ee10a705a2793344</t>
   </si>
   <si>
     <t>03-02010301-030097TC</t>
@@ -1727,7 +1727,7 @@
     <t>03-02010301-030097TM</t>
   </si>
   <si>
-    <t>5311dc722c4fc5a1ee66cca5a4ad5f46</t>
+    <t>2634a1798d1a3c6dfbcfd59bb211ad92</t>
   </si>
   <si>
     <t>03-030050TC</t>
@@ -1799,7 +1799,7 @@
     <t>905-9050607-905060702A</t>
   </si>
   <si>
-    <t>e1021bea513ab0537bc4df13105d9737</t>
+    <t>2b7ace009c184cf0272a47b51bbb0c02</t>
   </si>
   <si>
     <t>03-030061TC</t>
@@ -1811,7 +1811,7 @@
     <t>05-0709-070902TP</t>
   </si>
   <si>
-    <t>852dd907a8027478a4daf60cf9088c2c</t>
+    <t>a321218770d54c1ead7b42d941944f6d</t>
   </si>
   <si>
     <t>05-050201TP</t>
@@ -1823,13 +1823,13 @@
     <t>05-0709-070902TM</t>
   </si>
   <si>
-    <t>2db18754cfde08b840d87e01bd99babb</t>
+    <t>7ba26e807a4cb398bb150a7885740e96</t>
   </si>
   <si>
     <t>915-150009A</t>
   </si>
   <si>
-    <t>27162f060b503dd3b03739e69f99cdf5</t>
+    <t>c385735a4c483d51f2ae13a1c253cf21</t>
   </si>
   <si>
     <t>05-050201TM</t>
@@ -1865,19 +1865,19 @@
     <t>05-0709-070906ATC</t>
   </si>
   <si>
-    <t>1d538b85277d28472a82b08c1972ef36</t>
+    <t>d272e12677169965add2053d711e3d48</t>
   </si>
   <si>
     <t>915-150013TP</t>
   </si>
   <si>
-    <t>0bc8bdf73950f50bb65c5e87bf7c5d77</t>
+    <t>7b84711152414e4c246f740725ddb603</t>
   </si>
   <si>
     <t>03-030006TC</t>
   </si>
   <si>
-    <t>67e89ce88d11a78c862620a61b3f2f70</t>
+    <t>0f44e0ea975115699e243e0508f30d3a</t>
   </si>
   <si>
     <t>03-030006TM</t>
@@ -1889,7 +1889,7 @@
     <t>02-020001TC</t>
   </si>
   <si>
-    <t>16e8cb4dbf50ec4e86c7fa64fe380541</t>
+    <t>9591a6121b5000e5a91a52ea1e8530c1</t>
   </si>
   <si>
     <t>01-010016TP</t>
@@ -1919,7 +1919,7 @@
     <t>05-0709-070906ATM</t>
   </si>
   <si>
-    <t>c28618037e25e3704c441d1b6fd012db</t>
+    <t>3dd7fdf4f82e75464d8723fdbaa9d6a8</t>
   </si>
   <si>
     <t>03-030070TC</t>
@@ -1931,19 +1931,19 @@
     <t>05-0709-070906ATP</t>
   </si>
   <si>
-    <t>d2366e3876160ff8d83a9104aaef04fe</t>
+    <t>7342a9f55328567957fa51a1215fe113</t>
   </si>
   <si>
     <t>915-150013TC</t>
   </si>
   <si>
-    <t>06d4b0df2e3daa2e6f3952151324d3c2</t>
+    <t>306a82df144581f68cff1eb662f27375</t>
   </si>
   <si>
     <t>915-150013TM</t>
   </si>
   <si>
-    <t>9e2b479681aec8331992d5e2e269b068</t>
+    <t>291a632eed38372a2118a845060580f8</t>
   </si>
   <si>
     <t>03-030045A</t>
@@ -1955,7 +1955,7 @@
     <t>05-0709-070910A</t>
   </si>
   <si>
-    <t>ca3bc93378cdc336fb1d23bfd0287161</t>
+    <t>4829f40c44dcec27a667170ba36b3818</t>
   </si>
   <si>
     <t>01-010074A</t>
@@ -2009,13 +2009,13 @@
     <t>01-010050A</t>
   </si>
   <si>
-    <t>172db03539e2184365cf33be7505021b</t>
+    <t>8911b65ff0adc6263b52dd7272d2332f</t>
   </si>
   <si>
     <t>02-020001TM</t>
   </si>
   <si>
-    <t>10cb88bbcdcba6564f4634c1c3e628ef</t>
+    <t>10ef3d705ebb46abf3fa5a21b5e047d7</t>
   </si>
   <si>
     <t>01-080101-010084TP</t>
@@ -2039,7 +2039,7 @@
     <t>02-020001TP</t>
   </si>
   <si>
-    <t>1d2a0fad47aed368e039d0d34410fcec</t>
+    <t>b201805672b67168e40e217b6a6ebb82</t>
   </si>
   <si>
     <t>03-02010301-030091TC</t>
@@ -2105,13 +2105,13 @@
     <t>915-150015TP</t>
   </si>
   <si>
-    <t>ca9a0ce7200f67ff0f489c634cd576bf</t>
+    <t>ad1f80c8a38b25554200cea4225df193</t>
   </si>
   <si>
     <t>03-030004TC</t>
   </si>
   <si>
-    <t>ab039e8b28b07cb439eb3fe7f2a6baee</t>
+    <t>0dd543a2b7142033c57bf093f5631b3a</t>
   </si>
   <si>
     <t>01-010018TC</t>
@@ -2129,7 +2129,7 @@
     <t>915-150015TM</t>
   </si>
   <si>
-    <t>aec11b26aac47ff6bdcac8864b6f5cbf</t>
+    <t>72124e51ca8fbad9a299073b8ccbe1a6</t>
   </si>
   <si>
     <t>901-010202-9010102022TC</t>
@@ -2144,7 +2144,7 @@
     <t>03-030004TP</t>
   </si>
   <si>
-    <t>84a1a9aff333a40f7b93ff13f396825b</t>
+    <t>83f377bdb33260c4ca151c226f670d2e</t>
   </si>
   <si>
     <t>03-030004TM</t>
@@ -2153,7 +2153,7 @@
     <t>915-150015TC</t>
   </si>
   <si>
-    <t>363b8da5a43db16b69f56ba299c69d4a</t>
+    <t>1e80b3d0df570694e83ec8c84bcc78ca</t>
   </si>
   <si>
     <t>04-040009TC</t>
@@ -2204,7 +2204,7 @@
     <t>915-150004TP</t>
   </si>
   <si>
-    <t>19796459bde6467c01113b81816d466f</t>
+    <t>ffed5a323c47487b53ac2cadb90868ab</t>
   </si>
   <si>
     <t>01-010060TP</t>
@@ -2225,7 +2225,7 @@
     <t>915-150004TM</t>
   </si>
   <si>
-    <t>2fe5f54c0a0d39a3106d13918c7f78a7</t>
+    <t>b046fedaf21e139c91af0947c19d4c24</t>
   </si>
   <si>
     <t>01-010060TM</t>
@@ -2234,7 +2234,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>4d90c661e98736dfc9bc7228ed2a11e5</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2261,7 +2261,7 @@
     <t>915-150004TC</t>
   </si>
   <si>
-    <t>c3d15ba386f49a4a89cff768392ffa95</t>
+    <t>0fa37d4e516c6457cb1d73aacb9154b7</t>
   </si>
   <si>
     <t>03-030040A</t>
@@ -2282,7 +2282,7 @@
     <t>05-0709-070905BTP</t>
   </si>
   <si>
-    <t>c3a6bebf959923ce3ad21b967d0b2062</t>
+    <t>0ace74bd4d5e14e304eb72587aa1e207</t>
   </si>
   <si>
     <t>01-010007TP</t>
@@ -2405,13 +2405,13 @@
     <t>915-150017TP</t>
   </si>
   <si>
-    <t>2882a2cb40dba8d87f6ef93f3dc9b3b3</t>
+    <t>0bf208eae38e5873692b84a66f8fb2ca</t>
   </si>
   <si>
     <t>915-150017TM</t>
   </si>
   <si>
-    <t>ec21d5055c8849c0238a64995935b9ac</t>
+    <t>49281bf4f40ead942888b810674ffdb9</t>
   </si>
   <si>
     <t>01-010023A</t>
@@ -2438,7 +2438,7 @@
     <t>05-0709-070909TC</t>
   </si>
   <si>
-    <t>4e57d31c81b8f0b4e80c3d80a51d4c70</t>
+    <t>b8d747b6a2f4360f473ec24392463b45</t>
   </si>
   <si>
     <t>05-050204A</t>
@@ -2474,7 +2474,7 @@
     <t>915-150017TC</t>
   </si>
   <si>
-    <t>466d1df6ad4f7853fa33b6bca722803d</t>
+    <t>4370bf2a6c612a26ee49dfc30ab5e233</t>
   </si>
   <si>
     <t>01-010009TC</t>
@@ -2549,7 +2549,7 @@
     <t>04-040011TM</t>
   </si>
   <si>
-    <t>9c97e798b02676a3ca40e0f0ef22b628</t>
+    <t>c9509a175aee0e574dc1a10d5352122b</t>
   </si>
   <si>
     <t>05-050314A</t>
@@ -2564,7 +2564,7 @@
     <t>05-0709-070909TM</t>
   </si>
   <si>
-    <t>3dcb045817c3098469dbe3b3069eb83d</t>
+    <t>9f49a98543ca027eb508621e1fb91e3b</t>
   </si>
   <si>
     <t>01-010009TP</t>
@@ -2576,7 +2576,7 @@
     <t>03-030001TC</t>
   </si>
   <si>
-    <t>ac5faa7b24db5e3a4281517c9b86466e</t>
+    <t>b160c7ec0a78a8efefbead291473c70e</t>
   </si>
   <si>
     <t>03-030047TC</t>
@@ -2588,7 +2588,7 @@
     <t>05-0709-070909TP</t>
   </si>
   <si>
-    <t>1651e0a559aaee0fdaf68eecd726d95c</t>
+    <t>f32062aa5e28d6309651fc09b2df374b</t>
   </si>
   <si>
     <t>04-040011TP</t>
@@ -2606,7 +2606,7 @@
     <t>905-9050607-905060701TM</t>
   </si>
   <si>
-    <t>e0e5a8781dbac31946c52f46dcd95db7</t>
+    <t>1c8a64a363632393752b560f5a6a2f10</t>
   </si>
   <si>
     <t>01-010051TP</t>
@@ -2618,7 +2618,7 @@
     <t>905-9050607-905060701TP</t>
   </si>
   <si>
-    <t>1f4766a2be0c799e3c5310f4e0f5c983</t>
+    <t>6c00b36e0eaa8e4dcd941f8ed587f786</t>
   </si>
   <si>
     <t>01-010045A</t>
@@ -2723,7 +2723,7 @@
     <t>905-9050607-905060701TC</t>
   </si>
   <si>
-    <t>caf0902acd5e4ab007abd4dbb31c1a66</t>
+    <t>b6968f3f8506bbe85976337f02c79a14</t>
   </si>
   <si>
     <t>01-010062TC</t>
@@ -2807,7 +2807,7 @@
     <t>05-0709-070903A</t>
   </si>
   <si>
-    <t>935ef81b9fb805a4be34a828255ed1c9</t>
+    <t>4aaa92afb0abaea7fcdadb713098ba12</t>
   </si>
   <si>
     <t>05-050317TP</t>
@@ -2879,7 +2879,7 @@
     <t>05-0709-070902A</t>
   </si>
   <si>
-    <t>b28a09c762509387e269714acae243b2</t>
+    <t>ee108dfa4ade719dfc394066af30f874</t>
   </si>
   <si>
     <t>03-030013A</t>
@@ -2891,7 +2891,7 @@
     <t>01-010064TP</t>
   </si>
   <si>
-    <t>d152e0b7e58e4c0a3b12fbe91d962f80</t>
+    <t>61af9898f6bd8e9b0b8cc5ef77622c3a</t>
   </si>
   <si>
     <t>03-90205-0205_007A</t>
@@ -2906,7 +2906,7 @@
     <t>915-150008TM</t>
   </si>
   <si>
-    <t>32137b737f73b05333e215fb77c16587</t>
+    <t>f85e80bd8c13c6c66f07235d826f385f</t>
   </si>
   <si>
     <t>01-010064TM</t>
@@ -2954,7 +2954,7 @@
     <t>915-150008TP</t>
   </si>
   <si>
-    <t>4c36003fcffd031a25a22fbbe3a1ca63</t>
+    <t>ac8cf6c32ece5e43ac3f79ebad48ed51</t>
   </si>
   <si>
     <t>01-010075TC</t>
@@ -2966,7 +2966,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>a5bbea05ff12d3a39e488a47ddf51a4b</t>
+    <t>579451a92beef97da558af495ebe8606</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -2978,7 +2978,7 @@
     <t>05-0709-070901A</t>
   </si>
   <si>
-    <t>e6ece49d19fe9fdfa605f0790e42ec84</t>
+    <t>b46da07bb323bdbffc5d0cfa704f77e6</t>
   </si>
   <si>
     <t>03-030012A</t>
@@ -2996,7 +2996,7 @@
     <t>915-150008TC</t>
   </si>
   <si>
-    <t>6e672982fa194296a2efa95bac027c65</t>
+    <t>9518f3d56e3f5e0f6059671e877e498d</t>
   </si>
   <si>
     <t>03-02010301-030100TC</t>
@@ -3017,7 +3017,7 @@
     <t>03-030001TM</t>
   </si>
   <si>
-    <t>2f7eb22ff6ad0ca3d69e86974d03036b</t>
+    <t>ead04ed2740ceb084a3f0ce234470464</t>
   </si>
   <si>
     <t>05-050308TC</t>
@@ -3029,7 +3029,7 @@
     <t>02-020002TC</t>
   </si>
   <si>
-    <t>a3ee29141986a4326417d8abaf0d6c3b</t>
+    <t>417016e5a0ec9e73fd288ff16d22d782</t>
   </si>
   <si>
     <t>03-030047TP</t>
@@ -3047,7 +3047,7 @@
     <t>03-030001TP</t>
   </si>
   <si>
-    <t>ce67bdb572db24e4f6a2a30199fbe017</t>
+    <t>c30b13a5f0820e4e3c43214a99090270</t>
   </si>
   <si>
     <t>03-030047TM</t>
@@ -3101,7 +3101,7 @@
     <t>01-010042TM</t>
   </si>
   <si>
-    <t>ed9f4b5680ebb02261d1eb6cc016f9a4</t>
+    <t>842636dc1e868b133495f4c2822e30a8</t>
   </si>
   <si>
     <t>03-030012TM</t>
@@ -3155,7 +3155,7 @@
     <t>01-080101-010089TM</t>
   </si>
   <si>
-    <t>c557d1831e9be763f4fc83df83adf496</t>
+    <t>f6bfb4fdedde97622b8a9058dcdeb57a</t>
   </si>
   <si>
     <t>03-030058A</t>
@@ -3173,7 +3173,7 @@
     <t>02-020002TM</t>
   </si>
   <si>
-    <t>918d0f6d00993ac69e708551f5e7e685</t>
+    <t>93d7e9998659a16749e560d868f6e77a</t>
   </si>
   <si>
     <t>01-010053TC</t>
@@ -3185,7 +3185,7 @@
     <t>02-020002TP</t>
   </si>
   <si>
-    <t>64b83428c51981a8982ff0dc2928eeb6</t>
+    <t>a306edc42f7ab2f4a339be49a216ffcb</t>
   </si>
   <si>
     <t>01-010031TP</t>
@@ -3224,7 +3224,7 @@
     <t>915-150008A</t>
   </si>
   <si>
-    <t>372abfffb38b2dc96240a099ef34c8d4</t>
+    <t>df19891eae88e9c353acb3c0f9238ac6</t>
   </si>
   <si>
     <t>05-0709-070955TP</t>
@@ -3248,7 +3248,7 @@
     <t>01-010042TC</t>
   </si>
   <si>
-    <t>922fbfeb06bc04374c9b8582e84c655d</t>
+    <t>d678389545d7e835d100ebc2f8ed9cca</t>
   </si>
   <si>
     <t>03-030032TC</t>
@@ -3260,7 +3260,7 @@
     <t>03-030032TM</t>
   </si>
   <si>
-    <t>0bab210f526a9fc6401ce27133db8695</t>
+    <t>e921ee20a692464fa072920c7b478c40</t>
   </si>
   <si>
     <t>03-030078TM</t>
@@ -3314,7 +3314,7 @@
     <t>915-150007A</t>
   </si>
   <si>
-    <t>8bf4d4b70def7c3e1618c64e37847534</t>
+    <t>cafd5b65cc2ec420f27ccaa633e56e54</t>
   </si>
   <si>
     <t>05-050204TM</t>
@@ -3578,7 +3578,7 @@
     <t>01-010022TM</t>
   </si>
   <si>
-    <t>656a006cbcf7ec2b05e7d214903ff9f2</t>
+    <t>d906ce77b292c21e5f235b858758d7a8</t>
   </si>
   <si>
     <t>03-030030TP</t>
@@ -3590,7 +3590,7 @@
     <t>01-010002A</t>
   </si>
   <si>
-    <t>35629bd494fb012622aba1a361a71f50</t>
+    <t>169b297b7fff24b881c52844b61284f0</t>
   </si>
   <si>
     <t>01-010026A</t>
@@ -3632,7 +3632,7 @@
     <t>05-0709-070909A</t>
   </si>
   <si>
-    <t>31cfbe580fe6dfa303d681e53f909b80</t>
+    <t>dfc6091f934fc5044cfda2da5a67bfe3</t>
   </si>
   <si>
     <t>05-050206TM</t>
@@ -3647,7 +3647,7 @@
     <t>04-040013TM</t>
   </si>
   <si>
-    <t>d90a7dff71d15179e07e07d8d49cfe8e</t>
+    <t>2fe9e38eb071602504cde8eff31fe52e</t>
   </si>
   <si>
     <t>03-030041TC</t>
@@ -3659,7 +3659,7 @@
     <t>04-040013TP</t>
   </si>
   <si>
-    <t>901335dcb975050b3a06ba2bb478fb2d</t>
+    <t>2677e6917f5f9c5aa9daaa462655b2df</t>
   </si>
   <si>
     <t>01-010011TM</t>
@@ -3710,7 +3710,7 @@
     <t>04-040013TC</t>
   </si>
   <si>
-    <t>5d36b099269766af24b39475fff3e8e3</t>
+    <t>3591178de414aee03e8df5bbfe0638dd</t>
   </si>
   <si>
     <t>01-010011TP</t>
@@ -3755,25 +3755,25 @@
     <t>05-0709-070908A</t>
   </si>
   <si>
-    <t>7392593711ab7bb3250d7e56e6dece16</t>
+    <t>a570bf9870c8beb68d7d03210d5b6f2c</t>
   </si>
   <si>
     <t>01-010022TC</t>
   </si>
   <si>
-    <t>e9d235c08e4c1c94c33f933f84de5cef</t>
+    <t>18fa7188d999ad4ba17761497e898d64</t>
   </si>
   <si>
     <t>01-010049A</t>
   </si>
   <si>
-    <t>cc393fd4da76289572f103c2edfb820d</t>
+    <t>1b165eb937c09f4de7e61b497d3863c7</t>
   </si>
   <si>
     <t>05-0709-070905AA</t>
   </si>
   <si>
-    <t>b63bbf7509084a2b7b03ebc9663565f9</t>
+    <t>6b00962aa51e03e90db15ec9f0d86e8f</t>
   </si>
   <si>
     <t>01-080101-010110TP</t>
@@ -3788,7 +3788,7 @@
     <t>915-150002A</t>
   </si>
   <si>
-    <t>74bc5bcce3784988c2080f7367ac96d1</t>
+    <t>ae9e80c0c022799a39445a2399c8fe6e</t>
   </si>
   <si>
     <t>03-030054TC</t>
@@ -3824,7 +3824,7 @@
     <t>05-0709-070921ATP</t>
   </si>
   <si>
-    <t>ea3f030a8a490b970f7da01d292fecd4</t>
+    <t>74476aad8ebce81639d2b214aaafd947</t>
   </si>
   <si>
     <t>01-010024A</t>
@@ -3881,13 +3881,13 @@
     <t>02-020006TC</t>
   </si>
   <si>
-    <t>2802ab1063279d54146223f696f20eb3</t>
+    <t>863e39fef68f7fa45e955c21edad39b0</t>
   </si>
   <si>
     <t>05-0709-070921ATC</t>
   </si>
   <si>
-    <t>f0e5c24140c9cb41727b2a54e3a260c8</t>
+    <t>deab5c160b3856a617105a2bec99a5e9</t>
   </si>
   <si>
     <t>05-050207A</t>
@@ -3899,7 +3899,7 @@
     <t>02-020006TM</t>
   </si>
   <si>
-    <t>fb6579275369feca2249f6a62946d497</t>
+    <t>6a9b8ebe912b307b25cda9cc6184e098</t>
   </si>
   <si>
     <t>902-0204-02040101BTM</t>
@@ -3920,19 +3920,19 @@
     <t>05-0709-070905BA</t>
   </si>
   <si>
-    <t>6fcb607af1cb60af2252a39f7d1745de</t>
+    <t>265b93a97a6e7762073090ed8bd68ce6</t>
   </si>
   <si>
     <t>02-020006TP</t>
   </si>
   <si>
-    <t>45cce2fdc22e2cfd7fa5302a2e549dab</t>
+    <t>0cbd0f8fba9b7654d2c9e52df7e20192</t>
   </si>
   <si>
     <t>915-150001A</t>
   </si>
   <si>
-    <t>bbb159c371c7188bcb1da38b8b6d591f</t>
+    <t>81d184e5ea89069a9746708c27ba9b3a</t>
   </si>
   <si>
     <t>03-030065TC</t>
@@ -3962,7 +3962,7 @@
     <t>05-0709-070901TC</t>
   </si>
   <si>
-    <t>ed8d0f2e534d224e43bcd71563f0f88b</t>
+    <t>01b6ff12abce8f078560254cddfc1627</t>
   </si>
   <si>
     <t>03-02010301-030096TC</t>
@@ -3971,19 +3971,19 @@
     <t>05-0709-070901TM</t>
   </si>
   <si>
-    <t>a7c1dadd7ec65360b7f5725a4cbe5b52</t>
+    <t>fee68621940ff3e17fd834505ea2331f</t>
   </si>
   <si>
     <t>01-010035TP</t>
   </si>
   <si>
-    <t>edf354052625762b4b29e5510944d1cf</t>
+    <t>6490fabded0eb05a792536ed212a3e3e</t>
   </si>
   <si>
     <t>01-010035TM</t>
   </si>
   <si>
-    <t>e5555af19ade7cb69b3de639b53efbe2</t>
+    <t>9d4902c0a081edff9aa839214ab773dc</t>
   </si>
   <si>
     <t>03-030073A</t>
@@ -4052,13 +4052,13 @@
     <t>05-0709-070901TP</t>
   </si>
   <si>
-    <t>ba34bad9b6e7c800a1ade4e878ae97ca</t>
+    <t>397ba27f653d891ebe59029a6f0dab43</t>
   </si>
   <si>
     <t>01-010035TC</t>
   </si>
   <si>
-    <t>535b9101700329efe947e9ed77b67f67</t>
+    <t>50f3d5dd6de63f6f2ef93eb78f2564ba</t>
   </si>
   <si>
     <t>03-02010301-030097A</t>
@@ -4073,7 +4073,7 @@
     <t>05-050102TP</t>
   </si>
   <si>
-    <t>44bb8b5c0ae4d1268d9bac033e211aee</t>
+    <t>4c26779b04aeb6357d6d674c0a29a362</t>
   </si>
   <si>
     <t>03-030062TC</t>
@@ -4160,7 +4160,7 @@
     <t>03-030075TC</t>
   </si>
   <si>
-    <t>1dd2ae8d880542e886ef8a0209785ad8</t>
+    <t>108dc20ead86ac9393e968a56ddbf757</t>
   </si>
   <si>
     <t>05-050002TC</t>
@@ -4172,13 +4172,13 @@
     <t>03-030075TP</t>
   </si>
   <si>
-    <t>4275c97ed1a790378ff8d6467314d457</t>
+    <t>6eeff8e5ccfdab36c3b0a066b9bdbb66</t>
   </si>
   <si>
     <t>03-030075TM</t>
   </si>
   <si>
-    <t>8faee9629b60f43f0634f2f8efb568d4</t>
+    <t>c8670ec4e105f8c3246ecc1e391e16c4</t>
   </si>
   <si>
     <t>01-010048TC</t>
@@ -4199,13 +4199,13 @@
     <t>01-010002TM</t>
   </si>
   <si>
-    <t>b1b88d90fa7d6865d68888cf1e30c1b8</t>
+    <t>002835f1d5546c3b330e10097ccbdc55</t>
   </si>
   <si>
     <t>01-010002TP</t>
   </si>
   <si>
-    <t>1b26a4858ebe756a23b4d8e5281c487e</t>
+    <t>0cca9b1731114d9a37c688f6079a9756</t>
   </si>
   <si>
     <t>03-030070A</t>
@@ -4238,7 +4238,7 @@
     <t>05-0709-070903TC</t>
   </si>
   <si>
-    <t>dfb41bc87eb854e2b99e152486144459</t>
+    <t>655ea82c1cd5f1a39de0c488797ceb33</t>
   </si>
   <si>
     <t>01-010037TC</t>
@@ -4277,7 +4277,7 @@
     <t>01-010002TC</t>
   </si>
   <si>
-    <t>2367230e0e9179c07dffed373205d81b</t>
+    <t>a7baf553fd3303b88d87616b23993853</t>
   </si>
   <si>
     <t>03-02010301-030094A</t>
@@ -4310,6 +4310,9 @@
     <t>05-050006TM</t>
   </si>
   <si>
+    <t>f902c0c65af0ce991e7c7e13b50b8236</t>
+  </si>
+  <si>
     <t>05-050104TC</t>
   </si>
   <si>
@@ -4331,7 +4334,7 @@
     <t>05-0709-070903TM</t>
   </si>
   <si>
-    <t>b4e3ba5466c57f698549f42028666b21</t>
+    <t>60bc3633d16921f4896c881995a4e52e</t>
   </si>
   <si>
     <t>03-02010301-030093A</t>
@@ -4349,7 +4352,7 @@
     <t>05-0709-070903TP</t>
   </si>
   <si>
-    <t>d8ef158d83f87a66c3dcaa3efb83d98e</t>
+    <t>e9530b989030d7acff041a50998e3855</t>
   </si>
   <si>
     <t>04-040017TM</t>
@@ -4397,7 +4400,7 @@
     <t>04-040014A</t>
   </si>
   <si>
-    <t>3bbeda48cc454f005a899945f7dbc5cd</t>
+    <t>1b6ed3b3a92747c4d0e386b2f9f87036</t>
   </si>
   <si>
     <t>03-02010301-030092A</t>
@@ -4442,7 +4445,7 @@
     <t>915-150001TP</t>
   </si>
   <si>
-    <t>fb8bdd52c88c645604e93c2f67b8f429</t>
+    <t>0c127b5f0172ed781a509349e6c28409</t>
   </si>
   <si>
     <t>01-010004TP</t>
@@ -4472,7 +4475,7 @@
     <t>04-040013A</t>
   </si>
   <si>
-    <t>97220f71e67f3b425088a394f3a84b22</t>
+    <t>e441fe22d2b6b1f8e98bd23734f91e23</t>
   </si>
   <si>
     <t>03-02010301-030085TM</t>
@@ -4481,7 +4484,7 @@
     <t>915-150001TC</t>
   </si>
   <si>
-    <t>3c8fe25a6d9290e0a1321791ef223075</t>
+    <t>0ee05b216d187cd84b1366bfd9caf193</t>
   </si>
   <si>
     <t>03-02010301-030091A</t>
@@ -4490,7 +4493,7 @@
     <t>915-150001TM</t>
   </si>
   <si>
-    <t>767187267aeb43374fa487d09b04d827</t>
+    <t>d3e31586fc0f238413a108d7c84e733b</t>
   </si>
   <si>
     <t>03-02010301-030092TC</t>
@@ -4508,7 +4511,7 @@
     <t>01-010039TC</t>
   </si>
   <si>
-    <t>7a5683a1bed4ff3e2674c0c7d869e083</t>
+    <t>1f91ba663c5d24d29a8a88b3b45b8af5</t>
   </si>
   <si>
     <t>03-030029TC</t>
@@ -4529,7 +4532,7 @@
     <t>01-010039TM</t>
   </si>
   <si>
-    <t>ef898df150aa366cade8df3324848dbf</t>
+    <t>7cfd5035d1ebc32c5b2e72d83c64bb55</t>
   </si>
   <si>
     <t>01-080101-010084A</t>
@@ -4562,7 +4565,7 @@
     <t>03-030033A</t>
   </si>
   <si>
-    <t>5651ddd7888be309a021eb04eadb21e4</t>
+    <t>15e040aac52534eb1e5fdf489255be7c</t>
   </si>
   <si>
     <t>03-02010301-030102TC</t>
@@ -4616,13 +4619,13 @@
     <t>915-150014TP</t>
   </si>
   <si>
-    <t>ebdec01a6b309e3748d9754a298a2ebb</t>
+    <t>e095021e161529e65617f068d8eacd08</t>
   </si>
   <si>
     <t>05-0709-070906BTC</t>
   </si>
   <si>
-    <t>ff0372bf9239fb61a080e87ed3195bd4</t>
+    <t>948d665e3651e517e7ba26c501a65a10</t>
   </si>
   <si>
     <t>01-010017TC</t>
@@ -4646,7 +4649,7 @@
     <t>915-150014TM</t>
   </si>
   <si>
-    <t>57e6a5c84dd98419a196f687ba7da1cf</t>
+    <t>1ca3c1484e483fc4f4a9f3f57da3afba</t>
   </si>
   <si>
     <t>901-010202-9010102023TC</t>
@@ -4682,7 +4685,7 @@
     <t>05-0709-070906BTM</t>
   </si>
   <si>
-    <t>dab242bab5bc7656d6a1f3e354d7d51e</t>
+    <t>dbee2729cb23d5bd7600ef69e57d464b</t>
   </si>
   <si>
     <t>03-030071TC</t>
@@ -4694,7 +4697,7 @@
     <t>915-150014TC</t>
   </si>
   <si>
-    <t>ec565bb99879f865a731ab258df28300</t>
+    <t>aca0e08bd02ff79f804a3d1d3f23c4ec</t>
   </si>
   <si>
     <t>01-010115TC</t>
@@ -4706,7 +4709,7 @@
     <t>05-0709-070906BTP</t>
   </si>
   <si>
-    <t>602b4fb729c08f06791474bf1a154eb1</t>
+    <t>3ed0674e3f47802436055ef0aee8cd25</t>
   </si>
   <si>
     <t>03-030007TP</t>
@@ -4742,7 +4745,7 @@
     <t>915-150003TP</t>
   </si>
   <si>
-    <t>6c8a48c4793f647ae22e6415d1918f72</t>
+    <t>fce84300477d16728114d72d4f7f8c5f</t>
   </si>
   <si>
     <t>01-080101-010083TC</t>
@@ -4754,7 +4757,7 @@
     <t>05-0709-070905ATC</t>
   </si>
   <si>
-    <t>b2f44d3255fdd42d13a8b4353660a499</t>
+    <t>059a421cbf7df830f6ac6bf08b052994</t>
   </si>
   <si>
     <t>01-010006TC</t>
@@ -4772,7 +4775,7 @@
     <t>915-150003TM</t>
   </si>
   <si>
-    <t>b98caff4d64e24b295aa661bef3da148</t>
+    <t>b7a6d29a9cba82cd87d582fa13a4bd8b</t>
   </si>
   <si>
     <t>01-080101-010083TM</t>
@@ -4823,13 +4826,13 @@
     <t>915-150003TC</t>
   </si>
   <si>
-    <t>cba30d7950a13a0c0967661dd8f1ded3</t>
+    <t>35058e423177b5c2a1d9a3311e909735</t>
   </si>
   <si>
     <t>05-0709-070905ATP</t>
   </si>
   <si>
-    <t>b213c4e2488ad106b7235cb5839dce7a</t>
+    <t>9d0ae80615e37b264f45d02edcddf360</t>
   </si>
   <si>
     <t>03-030018TP</t>
@@ -4880,7 +4883,7 @@
     <t>05-0709-070921AA</t>
   </si>
   <si>
-    <t>95060d6e31bc91f2529e80a514b7f8a5</t>
+    <t>48ceb0bb5e2337ee5eb66697c3577418</t>
   </si>
   <si>
     <t>03-02010301-030094TP</t>
@@ -4898,7 +4901,7 @@
     <t>03-02010301-030094TM</t>
   </si>
   <si>
-    <t>5d277c98d807f951754f80bb69f75730</t>
+    <t>e803f7f4aa3331ae0d7c50f00e3f9fd8</t>
   </si>
   <si>
     <t>03-030077A</t>
@@ -4907,7 +4910,7 @@
     <t>02-020006A</t>
   </si>
   <si>
-    <t>0739e4252751d56b83824b70b671b54d</t>
+    <t>2369ec9edb1081bafb40644aa89da109</t>
   </si>
   <si>
     <t>03-030053A</t>
@@ -4937,7 +4940,7 @@
     <t>05-0709-070921BA</t>
   </si>
   <si>
-    <t>74ae33be2fdccb45346e846d82e80256</t>
+    <t>388219a416373a3bd84b66165eec03cb</t>
   </si>
   <si>
     <t>03-030076A</t>
@@ -4961,7 +4964,7 @@
     <t>915-150016TP</t>
   </si>
   <si>
-    <t>252258ccc0477f771cfa7f7fff6e2847</t>
+    <t>ce1b21339d84c5b978949d033b30414d</t>
   </si>
   <si>
     <t>03-030005TC</t>
@@ -4973,7 +4976,7 @@
     <t>915-150016TM</t>
   </si>
   <si>
-    <t>cddf31685c87ea1f10494c5af2604c98</t>
+    <t>22e4bccc3e21839772d7f2ed46a745fe</t>
   </si>
   <si>
     <t>901-010202-9010102021TC</t>
@@ -5012,7 +5015,7 @@
     <t>915-150016TC</t>
   </si>
   <si>
-    <t>164564ca6182282ff0c3c6b63f6c25c6</t>
+    <t>2a91eeed6df5af4e3324f09910f32329</t>
   </si>
   <si>
     <t>01-080101-010085TC</t>
@@ -11869,12 +11872,12 @@
         <v>1431</v>
       </c>
       <c r="B842" t="s">
-        <v>1</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B843" t="s">
         <v>1</v>
@@ -11882,15 +11885,15 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B844" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B845" t="s">
         <v>1</v>
@@ -11898,23 +11901,23 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B846" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B847" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B848" t="s">
         <v>1</v>
@@ -11922,7 +11925,7 @@
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B849" t="s">
         <v>1</v>
@@ -11930,31 +11933,31 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B850" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B851" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B852" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B853" t="s">
         <v>1</v>
@@ -11962,15 +11965,15 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B854" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B855" t="s">
         <v>1</v>
@@ -11978,47 +11981,47 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B856" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B857" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B858" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B859" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B860" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B861" t="s">
         <v>1</v>
@@ -12026,103 +12029,103 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B862" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B863" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B864" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B865" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B866" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B867" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B868" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B869" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B870" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B871" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B872" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B873" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B874" t="s">
         <v>1</v>
@@ -12130,15 +12133,15 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B875" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B876" t="s">
         <v>1</v>
@@ -12146,15 +12149,15 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B877" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B878" t="s">
         <v>1</v>
@@ -12162,15 +12165,15 @@
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B879" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B880" t="s">
         <v>75</v>
@@ -12178,15 +12181,15 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B881" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B882" t="s">
         <v>1</v>
@@ -12194,39 +12197,39 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B883" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B884" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B885" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B886" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B887" t="s">
         <v>1</v>
@@ -12234,7 +12237,7 @@
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B888" t="s">
         <v>1</v>
@@ -12242,7 +12245,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B889" t="s">
         <v>1</v>
@@ -12250,7 +12253,7 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B890" t="s">
         <v>1</v>
@@ -12258,15 +12261,15 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B891" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B892" t="s">
         <v>1</v>
@@ -12274,15 +12277,15 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B893" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B894" t="s">
         <v>1</v>
@@ -12290,7 +12293,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B895" t="s">
         <v>1</v>
@@ -12298,7 +12301,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B896" t="s">
         <v>1</v>
@@ -12306,7 +12309,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B897" t="s">
         <v>1</v>
@@ -12314,23 +12317,23 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B898" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B899" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B900" t="s">
         <v>1</v>
@@ -12338,7 +12341,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B901" t="s">
         <v>1</v>
@@ -12346,79 +12349,79 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B902" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B903" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B904" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B905" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B906" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B907" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B908" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B909" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B910" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B911" t="s">
         <v>75</v>
@@ -12426,23 +12429,23 @@
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B912" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B913" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B914" t="s">
         <v>1</v>
@@ -12450,199 +12453,199 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B915" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B916" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B917" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B918" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B919" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B920" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B921" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B922" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B923" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B924" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B925" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B926" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B927" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B928" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B929" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B930" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B931" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B932" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B933" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B934" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B935" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B936" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B937" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B938" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B939" t="s">
         <v>1</v>
@@ -12650,47 +12653,47 @@
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B940" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B941" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B942" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B943" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B944" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B945" t="s">
         <v>1</v>
@@ -12698,79 +12701,79 @@
     </row>
     <row r="946">
       <c r="A946" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B946" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B947" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B948" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B949" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B950" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B951" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B952" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B953" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B954" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B955" t="s">
         <v>1</v>
@@ -12778,31 +12781,31 @@
     </row>
     <row r="956">
       <c r="A956" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B956" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B957" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B958" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B959" t="s">
         <v>1</v>
@@ -12810,7 +12813,7 @@
     </row>
     <row r="960">
       <c r="A960" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B960" t="s">
         <v>1</v>
@@ -12818,7 +12821,7 @@
     </row>
     <row r="961">
       <c r="A961" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B961" t="s">
         <v>75</v>
@@ -12826,7 +12829,7 @@
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B962" t="s">
         <v>75</v>
@@ -12834,15 +12837,15 @@
     </row>
     <row r="963">
       <c r="A963" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B963" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B964" t="s">
         <v>1</v>
@@ -12850,15 +12853,15 @@
     </row>
     <row r="965">
       <c r="A965" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B965" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B966" t="s">
         <v>1</v>
@@ -12866,7 +12869,7 @@
     </row>
     <row r="967">
       <c r="A967" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B967" t="s">
         <v>1</v>
@@ -12874,7 +12877,7 @@
     </row>
     <row r="968">
       <c r="A968" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B968" t="s">
         <v>1</v>
@@ -12882,31 +12885,31 @@
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B969" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B970" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B971" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B972" t="s">
         <v>75</v>
@@ -12914,15 +12917,15 @@
     </row>
     <row r="973">
       <c r="A973" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B973" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B974" t="s">
         <v>1</v>
@@ -12930,23 +12933,23 @@
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B975" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B976" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B977" t="s">
         <v>1</v>
@@ -12954,7 +12957,7 @@
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B978" t="s">
         <v>1</v>
@@ -12962,7 +12965,7 @@
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B979" t="s">
         <v>1386</v>
@@ -12970,23 +12973,23 @@
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B980" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B981" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B982" t="s">
         <v>1</v>
@@ -12994,79 +12997,79 @@
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B983" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B984" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B985" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B986" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B987" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B988" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B989" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B990" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B991" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B992" t="s">
         <v>1</v>
@@ -13074,15 +13077,15 @@
     </row>
     <row r="993">
       <c r="A993" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B993" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B994" t="s">
         <v>1</v>
@@ -13090,7 +13093,7 @@
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B995" t="s">
         <v>1</v>
@@ -13098,10 +13101,10 @@
     </row>
     <row r="996">
       <c r="A996" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B996" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
   </sheetData>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -29,13 +29,13 @@
     <t>01-010050TP</t>
   </si>
   <si>
-    <t>821d617ccb748bee004129e886366b23</t>
+    <t>af91f3692b5c2a074c3f4fbe008ebd6f</t>
   </si>
   <si>
     <t>01-010035A</t>
   </si>
   <si>
-    <t>41719c71caba7b1e33163ba72bfe84aa</t>
+    <t>4a97e7dfbcdd2b1a8476f0dd150a01ef</t>
   </si>
   <si>
     <t>03-030029A</t>
@@ -59,7 +59,7 @@
     <t>03-030005A</t>
   </si>
   <si>
-    <t>2af0cb07e0e1f294f110e85e40af40be</t>
+    <t>b9894e60fbfa01ea11b5198f1b3e6816</t>
   </si>
   <si>
     <t>05-050305TC</t>
@@ -77,7 +77,7 @@
     <t>05-050301A</t>
   </si>
   <si>
-    <t>2ae1f19395183ed5b2388788b0763313</t>
+    <t>59de551a125521c3444790c0661399ae</t>
   </si>
   <si>
     <t>03-030002TP</t>
@@ -107,7 +107,7 @@
     <t>915-150012A</t>
   </si>
   <si>
-    <t>4b44cb446163485ebb0b311da4abdcc6</t>
+    <t>09d75f98149a07c4a0583ae9ca10de4d</t>
   </si>
   <si>
     <t>05-050305TP</t>
@@ -119,7 +119,7 @@
     <t>05-0709-070921BTP</t>
   </si>
   <si>
-    <t>05b9491f51ef494cb7e34dadbef1270e</t>
+    <t>4c6f84b27dcccd77f694c10531a70268</t>
   </si>
   <si>
     <t>01-010010A</t>
@@ -176,7 +176,7 @@
     <t>01-010050TC</t>
   </si>
   <si>
-    <t>0b806737ac696a894d996b6499d5d1a8</t>
+    <t>f701fc6735e33393ae9dfc09dc1f862b</t>
   </si>
   <si>
     <t>05-050302A</t>
@@ -191,19 +191,19 @@
     <t>05-0709-070921BTC</t>
   </si>
   <si>
-    <t>5852ad166ec6983e1f7c2f03b75d3bd2</t>
+    <t>5fd184f870d2af27239c7755601859fa</t>
   </si>
   <si>
     <t>03-030004A</t>
   </si>
   <si>
-    <t>4f28fb248e974767ac37a0dceefd7331</t>
+    <t>6d62a0557ea936e302361742a90bbf2d</t>
   </si>
   <si>
     <t>915-150011A</t>
   </si>
   <si>
-    <t>53fe8e276ff06c3fd44492c69d21f244</t>
+    <t>378ab1f948c4e84c7e2344d013d62a55</t>
   </si>
   <si>
     <t>05-050316TP</t>
@@ -215,7 +215,7 @@
     <t>915-150018TP</t>
   </si>
   <si>
-    <t>0993f7a58024c6a48ac3ce721114a5c8</t>
+    <t>62e8009b0bb43fe17664e9f2373a6c8c</t>
   </si>
   <si>
     <t>03-02010301-030102A</t>
@@ -224,7 +224,7 @@
     <t>915-150018TM</t>
   </si>
   <si>
-    <t>3f22b180f8c5118737028e2efba3aa45</t>
+    <t>39b20a4d3a33d1313cc52833ba6c0bca</t>
   </si>
   <si>
     <t>01-010057A</t>
@@ -251,7 +251,7 @@
     <t>05-0709-070908TC</t>
   </si>
   <si>
-    <t>5400dab8b05a98ab638b37351beb6afa</t>
+    <t>9908c29b7fab4cef9c80ff46dcf03af6</t>
   </si>
   <si>
     <t>05-050105A</t>
@@ -281,19 +281,19 @@
     <t>915-150018TC</t>
   </si>
   <si>
-    <t>a56d0a49802668923272ffd81f20ec30</t>
+    <t>6a8ff615cdb00a46b4e5c0f541ed124b</t>
   </si>
   <si>
     <t>915-150007TP</t>
   </si>
   <si>
-    <t>61fbcac4a0e40b79503dbfe09a088dbc</t>
+    <t>7d576524d3c4fc8fef7b58eb5f8f284d</t>
   </si>
   <si>
     <t>01-010063TP</t>
   </si>
   <si>
-    <t>e7f908c55a61b9f4c5f7a987985fd925</t>
+    <t>b3f7614824357fe5c8b54b6288c09e92</t>
   </si>
   <si>
     <t>01-010032A</t>
@@ -305,7 +305,7 @@
     <t>915-150007TM</t>
   </si>
   <si>
-    <t>6c894387e4343caaa722bdb22cc24fb6</t>
+    <t>b367758740bae7360eac1bc8e5e38bc2</t>
   </si>
   <si>
     <t>01-010063TM</t>
@@ -341,7 +341,7 @@
     <t>05-0709-070908TM</t>
   </si>
   <si>
-    <t>0f2b5a283bbd0fa2e6f4d204e75a45fb</t>
+    <t>67b7c9f494638cfa165a2cb3d182fc27</t>
   </si>
   <si>
     <t>03-030026A</t>
@@ -356,7 +356,7 @@
     <t>05-0709-070908TP</t>
   </si>
   <si>
-    <t>c66752fff0d24cd595df16cead8321f4</t>
+    <t>4e05305223e360a8e38718a184190ecd</t>
   </si>
   <si>
     <t>03-030002A</t>
@@ -371,7 +371,7 @@
     <t>915-150007TC</t>
   </si>
   <si>
-    <t>49747575b2941f2d7b203570ce685586</t>
+    <t>0159658a61ec1e54769b3e111cd5e338</t>
   </si>
   <si>
     <t>04-040012TP</t>
@@ -395,7 +395,7 @@
     <t>905-9050607-905060702TM</t>
   </si>
   <si>
-    <t>de587608272e7642fea45dc6a4eec7b4</t>
+    <t>b0bfef82cb938c7b37b82ac03dd92e02</t>
   </si>
   <si>
     <t>01-010055A</t>
@@ -422,7 +422,7 @@
     <t>905-9050607-905060702TP</t>
   </si>
   <si>
-    <t>3ff638c668f8683b3239757c18b1bd75</t>
+    <t>9d1d568df4a0a88312f112aaa595d6c1</t>
   </si>
   <si>
     <t>03-030025A</t>
@@ -434,7 +434,7 @@
     <t>03-030001A</t>
   </si>
   <si>
-    <t>508c4b7f803246bcf6e5c5169d743a75</t>
+    <t>e9080851709b95373d75ab3d52b1eed3</t>
   </si>
   <si>
     <t>05-050307TP</t>
@@ -449,7 +449,7 @@
     <t>905-9050607-905060702TC</t>
   </si>
   <si>
-    <t>3e37fab3289964e163748ae1ae0dc5eb</t>
+    <t>bc13665eac829680b6a0efac910209a9</t>
   </si>
   <si>
     <t>01-010030A</t>
@@ -536,7 +536,7 @@
     <t>05-050101A</t>
   </si>
   <si>
-    <t>a6a4ad04bd595317b0079bb650a01d78</t>
+    <t>dd075c32b83f804ad858b81f767d7141</t>
   </si>
   <si>
     <t>04-040021TM</t>
@@ -578,7 +578,7 @@
     <t>915-150009TM</t>
   </si>
   <si>
-    <t>1a44f6d0f05186195bc181a560434d4d</t>
+    <t>c90124b7b564c8fd04454539d0804182</t>
   </si>
   <si>
     <t>01-010065TM</t>
@@ -593,7 +593,7 @@
     <t>05-050102A</t>
   </si>
   <si>
-    <t>0fec58aacd6a62d325a1710fbf7dc0cf</t>
+    <t>c4164dd3c88981d8c135bbe7faeaf0cf</t>
   </si>
   <si>
     <t>03-030035TP</t>
@@ -605,7 +605,7 @@
     <t>915-150009TP</t>
   </si>
   <si>
-    <t>d2e7587229c3885463b891d3614cc054</t>
+    <t>8c9538fa6d11f86766a4e3d63d121b0e</t>
   </si>
   <si>
     <t>04-040021TC</t>
@@ -635,7 +635,7 @@
     <t>915-150009TC</t>
   </si>
   <si>
-    <t>99142123935409b93c41af5ec368f9b2</t>
+    <t>c44933a8687ca715bd1e53da6d63de28</t>
   </si>
   <si>
     <t>04-040010TP</t>
@@ -668,7 +668,7 @@
     <t>04-040014TC</t>
   </si>
   <si>
-    <t>87a5e69893d7f7e018944f9895caf1d9</t>
+    <t>a412ce738c555f504b3c2fc2563a4afe</t>
   </si>
   <si>
     <t>05-050301TC</t>
@@ -698,7 +698,7 @@
     <t>04-040003TP</t>
   </si>
   <si>
-    <t>65691ef982935fd3b44ba3dd108cd83f</t>
+    <t>9e948857ded2a8589cde9e2d0d74f7f7</t>
   </si>
   <si>
     <t>01-010019A</t>
@@ -713,7 +713,7 @@
     <t>04-040003TM</t>
   </si>
   <si>
-    <t>8faa25e5191430c9e9919d991f82646a</t>
+    <t>cd96b58e7ba840c9698dfaad67319aad</t>
   </si>
   <si>
     <t>01-110304-11030403A</t>
@@ -722,7 +722,7 @@
     <t>01-010043TM</t>
   </si>
   <si>
-    <t>7880cb33e90d0f0bb0dad5532b72c6d6</t>
+    <t>b0a11a3971ce3c114ec540c1c518bf4f</t>
   </si>
   <si>
     <t>05-050312TP</t>
@@ -737,7 +737,7 @@
     <t>04-040003TC</t>
   </si>
   <si>
-    <t>73ad8a2aeacf9e3eeff989980e0e8450</t>
+    <t>11cbe408a34939d2f06c53505a4dfbb8</t>
   </si>
   <si>
     <t>05-050312TC</t>
@@ -833,13 +833,13 @@
     <t>01-010043TC</t>
   </si>
   <si>
-    <t>4eabe142441c98a110c9ee12d712cfe6</t>
+    <t>e7b56bcf0d89e5e16dceb6f97a42f1f9</t>
   </si>
   <si>
     <t>05-050007TC</t>
   </si>
   <si>
-    <t>b65a056e377dd16eedcda4f04a751251</t>
+    <t>501ff54fe1ec0eb156cb3055e62653e8</t>
   </si>
   <si>
     <t>01-110304-11030402TC</t>
@@ -869,7 +869,7 @@
     <t>05-050007TP</t>
   </si>
   <si>
-    <t>26775f8fb4f7818f49d5dc49b38a3129</t>
+    <t>8f027885c173037131b7c503d2368195</t>
   </si>
   <si>
     <t>05-050105TC</t>
@@ -1010,7 +1010,7 @@
     <t>05-0709-070906AA</t>
   </si>
   <si>
-    <t>1d10f1f6af396db708ccf4ee098150ca</t>
+    <t>ec1698ab8e6353b5c9c7fcc6b4c8e660</t>
   </si>
   <si>
     <t>01-010067TC</t>
@@ -1064,13 +1064,13 @@
     <t>05-0709-070910TC</t>
   </si>
   <si>
-    <t>8ef4cd605a3cf46667f8182712494327</t>
+    <t>b7d2fb4e6114387d8b68a8ec6efef78b</t>
   </si>
   <si>
     <t>05-0709-070910TM</t>
   </si>
   <si>
-    <t>8d7e340b825b66d5861497c1e780ddc2</t>
+    <t>c7b13c896d79f110af279a23b4fc0266</t>
   </si>
   <si>
     <t>01-010045TP</t>
@@ -1103,7 +1103,7 @@
     <t>05-0709-070906BA</t>
   </si>
   <si>
-    <t>90d8ac6682832f94ac5098dfcf75478f</t>
+    <t>8eb157a8fa1bbe10c34f8a5bf203d4b3</t>
   </si>
   <si>
     <t>01-010056TC</t>
@@ -1166,7 +1166,7 @@
     <t>05-0709-070910TP</t>
   </si>
   <si>
-    <t>3e431fb07fb0f6c9694ec63ca9dc0768</t>
+    <t>bb9ffa8ad25621f081e6aa7a6eb95859</t>
   </si>
   <si>
     <t>01-010045TC</t>
@@ -1217,7 +1217,7 @@
     <t>03-030006A</t>
   </si>
   <si>
-    <t>2449228716b6538cd66d5bc8c14cf808</t>
+    <t>8db38e28a1f46406c8d92bc388bb0885</t>
   </si>
   <si>
     <t>05-050009TM</t>
@@ -1256,7 +1256,7 @@
     <t>04-040014TP</t>
   </si>
   <si>
-    <t>0defa52e30cb2325fa7a2ac126c3721d</t>
+    <t>a6aa62789d57a04a889943c1037ac8a7</t>
   </si>
   <si>
     <t>03-030042TC</t>
@@ -1271,7 +1271,7 @@
     <t>04-040014TM</t>
   </si>
   <si>
-    <t>fca3f688af13cc97c5e08c9d3cdb5ec4</t>
+    <t>492d3a39d5a70a93cd6c37e584ad93d6</t>
   </si>
   <si>
     <t>03-02010301-030089TM</t>
@@ -1301,7 +1301,7 @@
     <t>01-080101-010091TM</t>
   </si>
   <si>
-    <t>3485dcb96c4cad67ffca40b22f7a021a</t>
+    <t>19fc0070b6cb6aaf7ebcf6b8d1e992db</t>
   </si>
   <si>
     <t>01-010058TM</t>
@@ -1403,7 +1403,7 @@
     <t>01-080101-010091TC</t>
   </si>
   <si>
-    <t>6954b707057466638bc105dedcc0ae2b</t>
+    <t>4eb30eab2e23b782208c6a5b2be44559</t>
   </si>
   <si>
     <t>03-030041TP</t>
@@ -1475,7 +1475,7 @@
     <t>01-080101-010112TM</t>
   </si>
   <si>
-    <t>0e4158b3be5756e9866cace2776c8db4</t>
+    <t>8c6e2b75376b8490b816902250befb49</t>
   </si>
   <si>
     <t>01-010025TP</t>
@@ -1505,7 +1505,7 @@
     <t>05-050101TP</t>
   </si>
   <si>
-    <t>70a8a24919664930809e813e115083b9</t>
+    <t>eaa9458a605631a1d065a462c5e5c008</t>
   </si>
   <si>
     <t>03-030063TC</t>
@@ -1547,7 +1547,7 @@
     <t>915-150011TP</t>
   </si>
   <si>
-    <t>e854ca8a23b47c0d6e9010f4816e8974</t>
+    <t>0c26fd91b9125946602969e60614ecb8</t>
   </si>
   <si>
     <t>01-010014TP</t>
@@ -1574,7 +1574,7 @@
     <t>905-9050607-905060701A</t>
   </si>
   <si>
-    <t>7e910355cac59aae9cdb5abe67f245c8</t>
+    <t>b2a61c1c546004cbbd4486f2e85dab05</t>
   </si>
   <si>
     <t>01-080101-010093TM</t>
@@ -1607,7 +1607,7 @@
     <t>915-150011TC</t>
   </si>
   <si>
-    <t>08fee30ea443d574b66bedbbb56d1561</t>
+    <t>856b6031b20a0979bfaf8d26d1b23bbe</t>
   </si>
   <si>
     <t>03-030008TP</t>
@@ -1622,7 +1622,7 @@
     <t>915-150011TM</t>
   </si>
   <si>
-    <t>6f20c78dbc6676815780eb9ecb83d509</t>
+    <t>903bb20630a8ace4e47ca2fd1a725f41</t>
   </si>
   <si>
     <t>03-030072TP</t>
@@ -1655,7 +1655,7 @@
     <t>01-010049TP</t>
   </si>
   <si>
-    <t>bfb7a011b20a35d6c9a0d8ffa3efe1ac</t>
+    <t>bd28a05aac77a0bd798d2871eedfbe58</t>
   </si>
   <si>
     <t>01-010003TP</t>
@@ -1676,7 +1676,7 @@
     <t>01-010049TM</t>
   </si>
   <si>
-    <t>e956c7a7df01a3d09562f57bb09129a4</t>
+    <t>8154777e2c8ce05773d7088ed02de109</t>
   </si>
   <si>
     <t>01-080101-010082TM</t>
@@ -1688,7 +1688,7 @@
     <t>04-040003A</t>
   </si>
   <si>
-    <t>7741b7ed09595472064d877c3a04e492</t>
+    <t>d743159f8dd21ff896b707521e0082c6</t>
   </si>
   <si>
     <t>03-02010301-030081A</t>
@@ -1715,7 +1715,7 @@
     <t>05-0709-070902TC</t>
   </si>
   <si>
-    <t>78141aa3ad407c25ee10a705a2793344</t>
+    <t>b40b1af66372a7b4200f93a3b9a705ab</t>
   </si>
   <si>
     <t>03-02010301-030097TC</t>
@@ -1730,7 +1730,7 @@
     <t>03-02010301-030097TM</t>
   </si>
   <si>
-    <t>2634a1798d1a3c6dfbcfd59bb211ad92</t>
+    <t>5311dc722c4fc5a1ee66cca5a4ad5f46</t>
   </si>
   <si>
     <t>03-030050TC</t>
@@ -1802,7 +1802,7 @@
     <t>905-9050607-905060702A</t>
   </si>
   <si>
-    <t>2b7ace009c184cf0272a47b51bbb0c02</t>
+    <t>e1021bea513ab0537bc4df13105d9737</t>
   </si>
   <si>
     <t>03-030061TC</t>
@@ -1814,7 +1814,7 @@
     <t>05-0709-070902TP</t>
   </si>
   <si>
-    <t>a321218770d54c1ead7b42d941944f6d</t>
+    <t>852dd907a8027478a4daf60cf9088c2c</t>
   </si>
   <si>
     <t>05-050201TP</t>
@@ -1826,13 +1826,13 @@
     <t>05-0709-070902TM</t>
   </si>
   <si>
-    <t>7ba26e807a4cb398bb150a7885740e96</t>
+    <t>2db18754cfde08b840d87e01bd99babb</t>
   </si>
   <si>
     <t>915-150009A</t>
   </si>
   <si>
-    <t>c385735a4c483d51f2ae13a1c253cf21</t>
+    <t>27162f060b503dd3b03739e69f99cdf5</t>
   </si>
   <si>
     <t>05-050201TM</t>
@@ -1868,19 +1868,19 @@
     <t>05-0709-070906ATC</t>
   </si>
   <si>
-    <t>d272e12677169965add2053d711e3d48</t>
+    <t>1d538b85277d28472a82b08c1972ef36</t>
   </si>
   <si>
     <t>915-150013TP</t>
   </si>
   <si>
-    <t>7b84711152414e4c246f740725ddb603</t>
+    <t>0bc8bdf73950f50bb65c5e87bf7c5d77</t>
   </si>
   <si>
     <t>03-030006TC</t>
   </si>
   <si>
-    <t>0f44e0ea975115699e243e0508f30d3a</t>
+    <t>67e89ce88d11a78c862620a61b3f2f70</t>
   </si>
   <si>
     <t>03-030006TM</t>
@@ -1892,7 +1892,7 @@
     <t>02-020001TC</t>
   </si>
   <si>
-    <t>9591a6121b5000e5a91a52ea1e8530c1</t>
+    <t>16e8cb4dbf50ec4e86c7fa64fe380541</t>
   </si>
   <si>
     <t>01-010016TP</t>
@@ -1922,7 +1922,7 @@
     <t>05-0709-070906ATM</t>
   </si>
   <si>
-    <t>3dd7fdf4f82e75464d8723fdbaa9d6a8</t>
+    <t>c28618037e25e3704c441d1b6fd012db</t>
   </si>
   <si>
     <t>03-030070TC</t>
@@ -1934,19 +1934,19 @@
     <t>05-0709-070906ATP</t>
   </si>
   <si>
-    <t>7342a9f55328567957fa51a1215fe113</t>
+    <t>d2366e3876160ff8d83a9104aaef04fe</t>
   </si>
   <si>
     <t>915-150013TC</t>
   </si>
   <si>
-    <t>306a82df144581f68cff1eb662f27375</t>
+    <t>06d4b0df2e3daa2e6f3952151324d3c2</t>
   </si>
   <si>
     <t>915-150013TM</t>
   </si>
   <si>
-    <t>291a632eed38372a2118a845060580f8</t>
+    <t>9e2b479681aec8331992d5e2e269b068</t>
   </si>
   <si>
     <t>03-030045A</t>
@@ -1958,7 +1958,7 @@
     <t>05-0709-070910A</t>
   </si>
   <si>
-    <t>4829f40c44dcec27a667170ba36b3818</t>
+    <t>ca3bc93378cdc336fb1d23bfd0287161</t>
   </si>
   <si>
     <t>01-010074A</t>
@@ -2012,13 +2012,13 @@
     <t>01-010050A</t>
   </si>
   <si>
-    <t>8911b65ff0adc6263b52dd7272d2332f</t>
+    <t>172db03539e2184365cf33be7505021b</t>
   </si>
   <si>
     <t>02-020001TM</t>
   </si>
   <si>
-    <t>10ef3d705ebb46abf3fa5a21b5e047d7</t>
+    <t>10cb88bbcdcba6564f4634c1c3e628ef</t>
   </si>
   <si>
     <t>01-080101-010084TP</t>
@@ -2042,7 +2042,7 @@
     <t>02-020001TP</t>
   </si>
   <si>
-    <t>b201805672b67168e40e217b6a6ebb82</t>
+    <t>1d2a0fad47aed368e039d0d34410fcec</t>
   </si>
   <si>
     <t>03-02010301-030091TC</t>
@@ -2108,13 +2108,13 @@
     <t>915-150015TP</t>
   </si>
   <si>
-    <t>ad1f80c8a38b25554200cea4225df193</t>
+    <t>ca9a0ce7200f67ff0f489c634cd576bf</t>
   </si>
   <si>
     <t>03-030004TC</t>
   </si>
   <si>
-    <t>0dd543a2b7142033c57bf093f5631b3a</t>
+    <t>ab039e8b28b07cb439eb3fe7f2a6baee</t>
   </si>
   <si>
     <t>01-010018TC</t>
@@ -2132,7 +2132,7 @@
     <t>915-150015TM</t>
   </si>
   <si>
-    <t>72124e51ca8fbad9a299073b8ccbe1a6</t>
+    <t>aec11b26aac47ff6bdcac8864b6f5cbf</t>
   </si>
   <si>
     <t>901-010202-9010102022TC</t>
@@ -2147,7 +2147,7 @@
     <t>03-030004TP</t>
   </si>
   <si>
-    <t>83f377bdb33260c4ca151c226f670d2e</t>
+    <t>84a1a9aff333a40f7b93ff13f396825b</t>
   </si>
   <si>
     <t>03-030004TM</t>
@@ -2156,7 +2156,7 @@
     <t>915-150015TC</t>
   </si>
   <si>
-    <t>1e80b3d0df570694e83ec8c84bcc78ca</t>
+    <t>363b8da5a43db16b69f56ba299c69d4a</t>
   </si>
   <si>
     <t>04-040009TC</t>
@@ -2207,7 +2207,7 @@
     <t>915-150004TP</t>
   </si>
   <si>
-    <t>ffed5a323c47487b53ac2cadb90868ab</t>
+    <t>19796459bde6467c01113b81816d466f</t>
   </si>
   <si>
     <t>01-010060TP</t>
@@ -2228,7 +2228,7 @@
     <t>915-150004TM</t>
   </si>
   <si>
-    <t>b046fedaf21e139c91af0947c19d4c24</t>
+    <t>2fe5f54c0a0d39a3106d13918c7f78a7</t>
   </si>
   <si>
     <t>01-010060TM</t>
@@ -2237,7 +2237,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>4d90c661e98736dfc9bc7228ed2a11e5</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2264,7 +2264,7 @@
     <t>915-150004TC</t>
   </si>
   <si>
-    <t>0fa37d4e516c6457cb1d73aacb9154b7</t>
+    <t>c3d15ba386f49a4a89cff768392ffa95</t>
   </si>
   <si>
     <t>03-030040A</t>
@@ -2285,7 +2285,7 @@
     <t>05-0709-070905BTP</t>
   </si>
   <si>
-    <t>0ace74bd4d5e14e304eb72587aa1e207</t>
+    <t>c3a6bebf959923ce3ad21b967d0b2062</t>
   </si>
   <si>
     <t>01-010007TP</t>
@@ -2408,13 +2408,13 @@
     <t>915-150017TP</t>
   </si>
   <si>
-    <t>0bf208eae38e5873692b84a66f8fb2ca</t>
+    <t>2882a2cb40dba8d87f6ef93f3dc9b3b3</t>
   </si>
   <si>
     <t>915-150017TM</t>
   </si>
   <si>
-    <t>49281bf4f40ead942888b810674ffdb9</t>
+    <t>ec21d5055c8849c0238a64995935b9ac</t>
   </si>
   <si>
     <t>01-010023A</t>
@@ -2441,7 +2441,7 @@
     <t>05-0709-070909TC</t>
   </si>
   <si>
-    <t>b8d747b6a2f4360f473ec24392463b45</t>
+    <t>4e57d31c81b8f0b4e80c3d80a51d4c70</t>
   </si>
   <si>
     <t>05-050204A</t>
@@ -2453,7 +2453,7 @@
     <t>05-050313A</t>
   </si>
   <si>
-    <t>ed22506af71d0901f2e012d947ce109b</t>
+    <t>5854519ef399046ca625a71dce515635</t>
   </si>
   <si>
     <t>902-0204-02040102ATC</t>
@@ -2477,7 +2477,7 @@
     <t>915-150017TC</t>
   </si>
   <si>
-    <t>4370bf2a6c612a26ee49dfc30ab5e233</t>
+    <t>466d1df6ad4f7853fa33b6bca722803d</t>
   </si>
   <si>
     <t>01-010009TC</t>
@@ -2516,7 +2516,7 @@
     <t>03-030016A</t>
   </si>
   <si>
-    <t>a9763d2a082f1a96fc711b79aaf5c6e8</t>
+    <t>2e1cb344bc4c52acae679a96ac27c388</t>
   </si>
   <si>
     <t>03-030036TP</t>
@@ -2552,7 +2552,7 @@
     <t>04-040011TM</t>
   </si>
   <si>
-    <t>c9509a175aee0e574dc1a10d5352122b</t>
+    <t>9c97e798b02676a3ca40e0f0ef22b628</t>
   </si>
   <si>
     <t>05-050314A</t>
@@ -2567,7 +2567,7 @@
     <t>05-0709-070909TM</t>
   </si>
   <si>
-    <t>9f49a98543ca027eb508621e1fb91e3b</t>
+    <t>3dcb045817c3098469dbe3b3069eb83d</t>
   </si>
   <si>
     <t>01-010009TP</t>
@@ -2579,7 +2579,7 @@
     <t>03-030001TC</t>
   </si>
   <si>
-    <t>b160c7ec0a78a8efefbead291473c70e</t>
+    <t>ac5faa7b24db5e3a4281517c9b86466e</t>
   </si>
   <si>
     <t>03-030047TC</t>
@@ -2591,7 +2591,7 @@
     <t>05-0709-070909TP</t>
   </si>
   <si>
-    <t>f32062aa5e28d6309651fc09b2df374b</t>
+    <t>1651e0a559aaee0fdaf68eecd726d95c</t>
   </si>
   <si>
     <t>04-040011TP</t>
@@ -2609,7 +2609,7 @@
     <t>905-9050607-905060701TM</t>
   </si>
   <si>
-    <t>1c8a64a363632393752b560f5a6a2f10</t>
+    <t>e0e5a8781dbac31946c52f46dcd95db7</t>
   </si>
   <si>
     <t>01-010051TP</t>
@@ -2621,7 +2621,7 @@
     <t>905-9050607-905060701TP</t>
   </si>
   <si>
-    <t>6c00b36e0eaa8e4dcd941f8ed587f786</t>
+    <t>1f4766a2be0c799e3c5310f4e0f5c983</t>
   </si>
   <si>
     <t>01-010045A</t>
@@ -2726,7 +2726,7 @@
     <t>905-9050607-905060701TC</t>
   </si>
   <si>
-    <t>b6968f3f8506bbe85976337f02c79a14</t>
+    <t>caf0902acd5e4ab007abd4dbb31c1a66</t>
   </si>
   <si>
     <t>01-010062TC</t>
@@ -2747,7 +2747,7 @@
     <t>01-010068A</t>
   </si>
   <si>
-    <t>381d76a139cbb5b90408aa873647f71b</t>
+    <t>121b6022ca6b23d18bfb7fb505803db0</t>
   </si>
   <si>
     <t>03-030014TP</t>
@@ -2810,7 +2810,7 @@
     <t>05-0709-070903A</t>
   </si>
   <si>
-    <t>4aaa92afb0abaea7fcdadb713098ba12</t>
+    <t>935ef81b9fb805a4be34a828255ed1c9</t>
   </si>
   <si>
     <t>05-050317TP</t>
@@ -2864,7 +2864,7 @@
     <t>05-050006A</t>
   </si>
   <si>
-    <t>2f155268974893256ff764d9a39e9335</t>
+    <t>524aacb4580b4166773e582cb0808dbc</t>
   </si>
   <si>
     <t>01-080101-010078TM</t>
@@ -2882,7 +2882,7 @@
     <t>05-0709-070902A</t>
   </si>
   <si>
-    <t>ee108dfa4ade719dfc394066af30f874</t>
+    <t>b28a09c762509387e269714acae243b2</t>
   </si>
   <si>
     <t>03-030013A</t>
@@ -2894,7 +2894,7 @@
     <t>01-010064TP</t>
   </si>
   <si>
-    <t>61af9898f6bd8e9b0b8cc5ef77622c3a</t>
+    <t>d152e0b7e58e4c0a3b12fbe91d962f80</t>
   </si>
   <si>
     <t>03-90205-0205_007A</t>
@@ -2909,7 +2909,7 @@
     <t>915-150008TM</t>
   </si>
   <si>
-    <t>f85e80bd8c13c6c66f07235d826f385f</t>
+    <t>32137b737f73b05333e215fb77c16587</t>
   </si>
   <si>
     <t>01-010064TM</t>
@@ -2957,7 +2957,7 @@
     <t>915-150008TP</t>
   </si>
   <si>
-    <t>ac8cf6c32ece5e43ac3f79ebad48ed51</t>
+    <t>4c36003fcffd031a25a22fbbe3a1ca63</t>
   </si>
   <si>
     <t>01-010075TC</t>
@@ -2969,7 +2969,7 @@
     <t>05-050007A</t>
   </si>
   <si>
-    <t>579451a92beef97da558af495ebe8606</t>
+    <t>9908ed097b4574baad512db74f20ff68</t>
   </si>
   <si>
     <t>03-030036A</t>
@@ -2981,7 +2981,7 @@
     <t>05-0709-070901A</t>
   </si>
   <si>
-    <t>b46da07bb323bdbffc5d0cfa704f77e6</t>
+    <t>e6ece49d19fe9fdfa605f0790e42ec84</t>
   </si>
   <si>
     <t>03-030012A</t>
@@ -2999,7 +2999,7 @@
     <t>915-150008TC</t>
   </si>
   <si>
-    <t>9518f3d56e3f5e0f6059671e877e498d</t>
+    <t>6e672982fa194296a2efa95bac027c65</t>
   </si>
   <si>
     <t>03-02010301-030100TC</t>
@@ -3020,7 +3020,7 @@
     <t>03-030001TM</t>
   </si>
   <si>
-    <t>ead04ed2740ceb084a3f0ce234470464</t>
+    <t>2f7eb22ff6ad0ca3d69e86974d03036b</t>
   </si>
   <si>
     <t>05-050308TC</t>
@@ -3032,7 +3032,7 @@
     <t>02-020002TC</t>
   </si>
   <si>
-    <t>417016e5a0ec9e73fd288ff16d22d782</t>
+    <t>a3ee29141986a4326417d8abaf0d6c3b</t>
   </si>
   <si>
     <t>03-030047TP</t>
@@ -3050,7 +3050,7 @@
     <t>03-030001TP</t>
   </si>
   <si>
-    <t>c30b13a5f0820e4e3c43214a99090270</t>
+    <t>ce67bdb572db24e4f6a2a30199fbe017</t>
   </si>
   <si>
     <t>03-030047TM</t>
@@ -3104,7 +3104,7 @@
     <t>01-010042TM</t>
   </si>
   <si>
-    <t>842636dc1e868b133495f4c2822e30a8</t>
+    <t>ed9f4b5680ebb02261d1eb6cc016f9a4</t>
   </si>
   <si>
     <t>03-030012TM</t>
@@ -3158,7 +3158,7 @@
     <t>01-080101-010089TM</t>
   </si>
   <si>
-    <t>f6bfb4fdedde97622b8a9058dcdeb57a</t>
+    <t>c557d1831e9be763f4fc83df83adf496</t>
   </si>
   <si>
     <t>03-030058A</t>
@@ -3176,7 +3176,7 @@
     <t>02-020002TM</t>
   </si>
   <si>
-    <t>93d7e9998659a16749e560d868f6e77a</t>
+    <t>918d0f6d00993ac69e708551f5e7e685</t>
   </si>
   <si>
     <t>01-010053TC</t>
@@ -3188,7 +3188,7 @@
     <t>02-020002TP</t>
   </si>
   <si>
-    <t>a306edc42f7ab2f4a339be49a216ffcb</t>
+    <t>64b83428c51981a8982ff0dc2928eeb6</t>
   </si>
   <si>
     <t>01-010031TP</t>
@@ -3227,7 +3227,7 @@
     <t>915-150008A</t>
   </si>
   <si>
-    <t>df19891eae88e9c353acb3c0f9238ac6</t>
+    <t>372abfffb38b2dc96240a099ef34c8d4</t>
   </si>
   <si>
     <t>05-0709-070955TP</t>
@@ -3251,7 +3251,7 @@
     <t>01-010042TC</t>
   </si>
   <si>
-    <t>d678389545d7e835d100ebc2f8ed9cca</t>
+    <t>922fbfeb06bc04374c9b8582e84c655d</t>
   </si>
   <si>
     <t>03-030032TC</t>
@@ -3317,7 +3317,7 @@
     <t>915-150007A</t>
   </si>
   <si>
-    <t>cafd5b65cc2ec420f27ccaa633e56e54</t>
+    <t>8bf4d4b70def7c3e1618c64e37847534</t>
   </si>
   <si>
     <t>05-050204TM</t>
@@ -3476,7 +3476,7 @@
     <t>05-050313TP</t>
   </si>
   <si>
-    <t>3509aa1997c3bcfb51b1a748dbd724ac</t>
+    <t>5b29ef0d3bf73f26c0132e79d57393cb</t>
   </si>
   <si>
     <t>01-010004A</t>
@@ -3503,7 +3503,7 @@
     <t>05-050313TC</t>
   </si>
   <si>
-    <t>e7360a55096f740ab6e9aa80791956d2</t>
+    <t>0dc6f178beadd0b262ab340291e84963</t>
   </si>
   <si>
     <t>01-010028A</t>
@@ -3581,7 +3581,7 @@
     <t>01-010022TM</t>
   </si>
   <si>
-    <t>d906ce77b292c21e5f235b858758d7a8</t>
+    <t>656a006cbcf7ec2b05e7d214903ff9f2</t>
   </si>
   <si>
     <t>03-030030TP</t>
@@ -3593,7 +3593,7 @@
     <t>01-010002A</t>
   </si>
   <si>
-    <t>169b297b7fff24b881c52844b61284f0</t>
+    <t>35629bd494fb012622aba1a361a71f50</t>
   </si>
   <si>
     <t>01-010026A</t>
@@ -3614,7 +3614,7 @@
     <t>01-010068TP</t>
   </si>
   <si>
-    <t>6d5a025eee1b238ca18d69b146d7ed69</t>
+    <t>79222eb8a64864ef0957ba4fb2640dfd</t>
   </si>
   <si>
     <t>05-050206TP</t>
@@ -3626,7 +3626,7 @@
     <t>01-010068TM</t>
   </si>
   <si>
-    <t>efb93854e64d76a0082712ec93245e76</t>
+    <t>e1fa09aa78f53496969d261f9f5e7b69</t>
   </si>
   <si>
     <t>03-030076TP</t>
@@ -3635,7 +3635,7 @@
     <t>05-0709-070909A</t>
   </si>
   <si>
-    <t>dfc6091f934fc5044cfda2da5a67bfe3</t>
+    <t>31cfbe580fe6dfa303d681e53f909b80</t>
   </si>
   <si>
     <t>05-050206TM</t>
@@ -3650,7 +3650,7 @@
     <t>04-040013TM</t>
   </si>
   <si>
-    <t>2fe9e38eb071602504cde8eff31fe52e</t>
+    <t>d90a7dff71d15179e07e07d8d49cfe8e</t>
   </si>
   <si>
     <t>03-030041TC</t>
@@ -3662,7 +3662,7 @@
     <t>04-040013TP</t>
   </si>
   <si>
-    <t>2677e6917f5f9c5aa9daaa462655b2df</t>
+    <t>901335dcb975050b3a06ba2bb478fb2d</t>
   </si>
   <si>
     <t>01-010011TM</t>
@@ -3713,7 +3713,7 @@
     <t>04-040013TC</t>
   </si>
   <si>
-    <t>3591178de414aee03e8df5bbfe0638dd</t>
+    <t>5d36b099269766af24b39475fff3e8e3</t>
   </si>
   <si>
     <t>01-010011TP</t>
@@ -3758,25 +3758,25 @@
     <t>05-0709-070908A</t>
   </si>
   <si>
-    <t>a570bf9870c8beb68d7d03210d5b6f2c</t>
+    <t>7392593711ab7bb3250d7e56e6dece16</t>
   </si>
   <si>
     <t>01-010022TC</t>
   </si>
   <si>
-    <t>18fa7188d999ad4ba17761497e898d64</t>
+    <t>e9d235c08e4c1c94c33f933f84de5cef</t>
   </si>
   <si>
     <t>01-010049A</t>
   </si>
   <si>
-    <t>1b165eb937c09f4de7e61b497d3863c7</t>
+    <t>cc393fd4da76289572f103c2edfb820d</t>
   </si>
   <si>
     <t>05-0709-070905AA</t>
   </si>
   <si>
-    <t>6b00962aa51e03e90db15ec9f0d86e8f</t>
+    <t>b63bbf7509084a2b7b03ebc9663565f9</t>
   </si>
   <si>
     <t>01-080101-010110TP</t>
@@ -3791,7 +3791,7 @@
     <t>915-150002A</t>
   </si>
   <si>
-    <t>ae9e80c0c022799a39445a2399c8fe6e</t>
+    <t>74bc5bcce3784988c2080f7367ac96d1</t>
   </si>
   <si>
     <t>03-030054TC</t>
@@ -3827,7 +3827,7 @@
     <t>05-0709-070921ATP</t>
   </si>
   <si>
-    <t>74476aad8ebce81639d2b214aaafd947</t>
+    <t>ea3f030a8a490b970f7da01d292fecd4</t>
   </si>
   <si>
     <t>01-010024A</t>
@@ -3884,13 +3884,13 @@
     <t>02-020006TC</t>
   </si>
   <si>
-    <t>863e39fef68f7fa45e955c21edad39b0</t>
+    <t>2802ab1063279d54146223f696f20eb3</t>
   </si>
   <si>
     <t>05-0709-070921ATC</t>
   </si>
   <si>
-    <t>deab5c160b3856a617105a2bec99a5e9</t>
+    <t>f0e5c24140c9cb41727b2a54e3a260c8</t>
   </si>
   <si>
     <t>05-050207A</t>
@@ -3902,7 +3902,7 @@
     <t>02-020006TM</t>
   </si>
   <si>
-    <t>6a9b8ebe912b307b25cda9cc6184e098</t>
+    <t>fb6579275369feca2249f6a62946d497</t>
   </si>
   <si>
     <t>902-0204-02040101BTM</t>
@@ -3923,19 +3923,19 @@
     <t>05-0709-070905BA</t>
   </si>
   <si>
-    <t>265b93a97a6e7762073090ed8bd68ce6</t>
+    <t>6fcb607af1cb60af2252a39f7d1745de</t>
   </si>
   <si>
     <t>02-020006TP</t>
   </si>
   <si>
-    <t>0cbd0f8fba9b7654d2c9e52df7e20192</t>
+    <t>45cce2fdc22e2cfd7fa5302a2e549dab</t>
   </si>
   <si>
     <t>915-150001A</t>
   </si>
   <si>
-    <t>81d184e5ea89069a9746708c27ba9b3a</t>
+    <t>bbb159c371c7188bcb1da38b8b6d591f</t>
   </si>
   <si>
     <t>03-030065TC</t>
@@ -3965,7 +3965,7 @@
     <t>05-0709-070901TC</t>
   </si>
   <si>
-    <t>01b6ff12abce8f078560254cddfc1627</t>
+    <t>ed8d0f2e534d224e43bcd71563f0f88b</t>
   </si>
   <si>
     <t>03-02010301-030096TC</t>
@@ -3974,19 +3974,19 @@
     <t>05-0709-070901TM</t>
   </si>
   <si>
-    <t>fee68621940ff3e17fd834505ea2331f</t>
+    <t>a7c1dadd7ec65360b7f5725a4cbe5b52</t>
   </si>
   <si>
     <t>01-010035TP</t>
   </si>
   <si>
-    <t>6490fabded0eb05a792536ed212a3e3e</t>
+    <t>edf354052625762b4b29e5510944d1cf</t>
   </si>
   <si>
     <t>01-010035TM</t>
   </si>
   <si>
-    <t>9d4902c0a081edff9aa839214ab773dc</t>
+    <t>e5555af19ade7cb69b3de639b53efbe2</t>
   </si>
   <si>
     <t>03-030073A</t>
@@ -4055,13 +4055,13 @@
     <t>05-0709-070901TP</t>
   </si>
   <si>
-    <t>397ba27f653d891ebe59029a6f0dab43</t>
+    <t>ba34bad9b6e7c800a1ade4e878ae97ca</t>
   </si>
   <si>
     <t>01-010035TC</t>
   </si>
   <si>
-    <t>50f3d5dd6de63f6f2ef93eb78f2564ba</t>
+    <t>535b9101700329efe947e9ed77b67f67</t>
   </si>
   <si>
     <t>03-02010301-030097A</t>
@@ -4076,7 +4076,7 @@
     <t>05-050102TP</t>
   </si>
   <si>
-    <t>4c26779b04aeb6357d6d674c0a29a362</t>
+    <t>84cab191ff25374b88bc173f93d60944</t>
   </si>
   <si>
     <t>03-030062TC</t>
@@ -4163,7 +4163,7 @@
     <t>03-030075TC</t>
   </si>
   <si>
-    <t>108dc20ead86ac9393e968a56ddbf757</t>
+    <t>1dd2ae8d880542e886ef8a0209785ad8</t>
   </si>
   <si>
     <t>05-050002TC</t>
@@ -4175,13 +4175,13 @@
     <t>03-030075TP</t>
   </si>
   <si>
-    <t>6eeff8e5ccfdab36c3b0a066b9bdbb66</t>
+    <t>4275c97ed1a790378ff8d6467314d457</t>
   </si>
   <si>
     <t>03-030075TM</t>
   </si>
   <si>
-    <t>c8670ec4e105f8c3246ecc1e391e16c4</t>
+    <t>8faee9629b60f43f0634f2f8efb568d4</t>
   </si>
   <si>
     <t>01-010048TC</t>
@@ -4202,13 +4202,13 @@
     <t>01-010002TM</t>
   </si>
   <si>
-    <t>002835f1d5546c3b330e10097ccbdc55</t>
+    <t>b1b88d90fa7d6865d68888cf1e30c1b8</t>
   </si>
   <si>
     <t>01-010002TP</t>
   </si>
   <si>
-    <t>0cca9b1731114d9a37c688f6079a9756</t>
+    <t>1b26a4858ebe756a23b4d8e5281c487e</t>
   </si>
   <si>
     <t>03-030070A</t>
@@ -4241,7 +4241,7 @@
     <t>05-0709-070903TC</t>
   </si>
   <si>
-    <t>655ea82c1cd5f1a39de0c488797ceb33</t>
+    <t>dfb41bc87eb854e2b99e152486144459</t>
   </si>
   <si>
     <t>01-010037TC</t>
@@ -4280,7 +4280,7 @@
     <t>01-010002TC</t>
   </si>
   <si>
-    <t>a7baf553fd3303b88d87616b23993853</t>
+    <t>2367230e0e9179c07dffed373205d81b</t>
   </si>
   <si>
     <t>03-02010301-030094A</t>
@@ -4292,7 +4292,7 @@
     <t>05-050006TC</t>
   </si>
   <si>
-    <t>235ab4bbe3eaa87649557f3c8ee3781b</t>
+    <t>ee1c195c1c2e0f45c3609111d1ac2f34</t>
   </si>
   <si>
     <t>01-010026TC</t>
@@ -4307,7 +4307,7 @@
     <t>05-050006TP</t>
   </si>
   <si>
-    <t>54dff1e3570afa76227c826ad2050f2d</t>
+    <t>1e2f02d90578b126e9ea63ac2cfcf96b</t>
   </si>
   <si>
     <t>05-050006TM</t>
@@ -4337,7 +4337,7 @@
     <t>05-0709-070903TM</t>
   </si>
   <si>
-    <t>60bc3633d16921f4896c881995a4e52e</t>
+    <t>b4e3ba5466c57f698549f42028666b21</t>
   </si>
   <si>
     <t>03-02010301-030093A</t>
@@ -4355,7 +4355,7 @@
     <t>05-0709-070903TP</t>
   </si>
   <si>
-    <t>e9530b989030d7acff041a50998e3855</t>
+    <t>d8ef158d83f87a66c3dcaa3efb83d98e</t>
   </si>
   <si>
     <t>04-040017TM</t>
@@ -4403,7 +4403,7 @@
     <t>04-040014A</t>
   </si>
   <si>
-    <t>1b6ed3b3a92747c4d0e386b2f9f87036</t>
+    <t>3bbeda48cc454f005a899945f7dbc5cd</t>
   </si>
   <si>
     <t>03-02010301-030092A</t>
@@ -4448,7 +4448,7 @@
     <t>915-150001TP</t>
   </si>
   <si>
-    <t>0c127b5f0172ed781a509349e6c28409</t>
+    <t>fb8bdd52c88c645604e93c2f67b8f429</t>
   </si>
   <si>
     <t>01-010004TP</t>
@@ -4478,7 +4478,7 @@
     <t>04-040013A</t>
   </si>
   <si>
-    <t>e441fe22d2b6b1f8e98bd23734f91e23</t>
+    <t>97220f71e67f3b425088a394f3a84b22</t>
   </si>
   <si>
     <t>03-02010301-030085TM</t>
@@ -4487,7 +4487,7 @@
     <t>915-150001TC</t>
   </si>
   <si>
-    <t>0ee05b216d187cd84b1366bfd9caf193</t>
+    <t>3c8fe25a6d9290e0a1321791ef223075</t>
   </si>
   <si>
     <t>03-02010301-030091A</t>
@@ -4496,7 +4496,7 @@
     <t>915-150001TM</t>
   </si>
   <si>
-    <t>d3e31586fc0f238413a108d7c84e733b</t>
+    <t>767187267aeb43374fa487d09b04d827</t>
   </si>
   <si>
     <t>03-02010301-030092TC</t>
@@ -4514,7 +4514,7 @@
     <t>01-010039TC</t>
   </si>
   <si>
-    <t>1f91ba663c5d24d29a8a88b3b45b8af5</t>
+    <t>7a5683a1bed4ff3e2674c0c7d869e083</t>
   </si>
   <si>
     <t>03-030029TC</t>
@@ -4535,7 +4535,7 @@
     <t>01-010039TM</t>
   </si>
   <si>
-    <t>7cfd5035d1ebc32c5b2e72d83c64bb55</t>
+    <t>ef898df150aa366cade8df3324848dbf</t>
   </si>
   <si>
     <t>01-080101-010084A</t>
@@ -4568,7 +4568,7 @@
     <t>03-030033A</t>
   </si>
   <si>
-    <t>17762dfdee88730f2873000080b186a2</t>
+    <t>5651ddd7888be309a021eb04eadb21e4</t>
   </si>
   <si>
     <t>03-02010301-030102TC</t>
@@ -4622,13 +4622,13 @@
     <t>915-150014TP</t>
   </si>
   <si>
-    <t>e095021e161529e65617f068d8eacd08</t>
+    <t>ebdec01a6b309e3748d9754a298a2ebb</t>
   </si>
   <si>
     <t>05-0709-070906BTC</t>
   </si>
   <si>
-    <t>948d665e3651e517e7ba26c501a65a10</t>
+    <t>ff0372bf9239fb61a080e87ed3195bd4</t>
   </si>
   <si>
     <t>01-010017TC</t>
@@ -4652,7 +4652,7 @@
     <t>915-150014TM</t>
   </si>
   <si>
-    <t>1ca3c1484e483fc4f4a9f3f57da3afba</t>
+    <t>57e6a5c84dd98419a196f687ba7da1cf</t>
   </si>
   <si>
     <t>901-010202-9010102023TC</t>
@@ -4688,7 +4688,7 @@
     <t>05-0709-070906BTM</t>
   </si>
   <si>
-    <t>dbee2729cb23d5bd7600ef69e57d464b</t>
+    <t>dab242bab5bc7656d6a1f3e354d7d51e</t>
   </si>
   <si>
     <t>03-030071TC</t>
@@ -4700,7 +4700,7 @@
     <t>915-150014TC</t>
   </si>
   <si>
-    <t>aca0e08bd02ff79f804a3d1d3f23c4ec</t>
+    <t>ec565bb99879f865a731ab258df28300</t>
   </si>
   <si>
     <t>01-010115TC</t>
@@ -4712,7 +4712,7 @@
     <t>05-0709-070906BTP</t>
   </si>
   <si>
-    <t>3ed0674e3f47802436055ef0aee8cd25</t>
+    <t>602b4fb729c08f06791474bf1a154eb1</t>
   </si>
   <si>
     <t>03-030007TP</t>
@@ -4748,7 +4748,7 @@
     <t>915-150003TP</t>
   </si>
   <si>
-    <t>fce84300477d16728114d72d4f7f8c5f</t>
+    <t>6c8a48c4793f647ae22e6415d1918f72</t>
   </si>
   <si>
     <t>01-080101-010083TC</t>
@@ -4760,7 +4760,7 @@
     <t>05-0709-070905ATC</t>
   </si>
   <si>
-    <t>059a421cbf7df830f6ac6bf08b052994</t>
+    <t>b2f44d3255fdd42d13a8b4353660a499</t>
   </si>
   <si>
     <t>01-010006TC</t>
@@ -4778,7 +4778,7 @@
     <t>915-150003TM</t>
   </si>
   <si>
-    <t>b7a6d29a9cba82cd87d582fa13a4bd8b</t>
+    <t>b98caff4d64e24b295aa661bef3da148</t>
   </si>
   <si>
     <t>01-080101-010083TM</t>
@@ -4829,13 +4829,13 @@
     <t>915-150003TC</t>
   </si>
   <si>
-    <t>35058e423177b5c2a1d9a3311e909735</t>
+    <t>cba30d7950a13a0c0967661dd8f1ded3</t>
   </si>
   <si>
     <t>05-0709-070905ATP</t>
   </si>
   <si>
-    <t>9d0ae80615e37b264f45d02edcddf360</t>
+    <t>b213c4e2488ad106b7235cb5839dce7a</t>
   </si>
   <si>
     <t>03-030018TP</t>
@@ -4886,7 +4886,7 @@
     <t>05-0709-070921AA</t>
   </si>
   <si>
-    <t>48ceb0bb5e2337ee5eb66697c3577418</t>
+    <t>95060d6e31bc91f2529e80a514b7f8a5</t>
   </si>
   <si>
     <t>03-02010301-030094TP</t>
@@ -4904,7 +4904,7 @@
     <t>03-02010301-030094TM</t>
   </si>
   <si>
-    <t>e803f7f4aa3331ae0d7c50f00e3f9fd8</t>
+    <t>5d277c98d807f951754f80bb69f75730</t>
   </si>
   <si>
     <t>03-030077A</t>
@@ -4913,7 +4913,7 @@
     <t>02-020006A</t>
   </si>
   <si>
-    <t>2369ec9edb1081bafb40644aa89da109</t>
+    <t>0739e4252751d56b83824b70b671b54d</t>
   </si>
   <si>
     <t>03-030053A</t>
@@ -4943,7 +4943,7 @@
     <t>05-0709-070921BA</t>
   </si>
   <si>
-    <t>388219a416373a3bd84b66165eec03cb</t>
+    <t>74ae33be2fdccb45346e846d82e80256</t>
   </si>
   <si>
     <t>03-030076A</t>
@@ -4967,7 +4967,7 @@
     <t>915-150016TP</t>
   </si>
   <si>
-    <t>ce1b21339d84c5b978949d033b30414d</t>
+    <t>252258ccc0477f771cfa7f7fff6e2847</t>
   </si>
   <si>
     <t>03-030005TC</t>
@@ -4979,7 +4979,7 @@
     <t>915-150016TM</t>
   </si>
   <si>
-    <t>22e4bccc3e21839772d7f2ed46a745fe</t>
+    <t>cddf31685c87ea1f10494c5af2604c98</t>
   </si>
   <si>
     <t>901-010202-9010102021TC</t>
@@ -5018,7 +5018,7 @@
     <t>915-150016TC</t>
   </si>
   <si>
-    <t>2a91eeed6df5af4e3324f09910f32329</t>
+    <t>164564ca6182282ff0c3c6b63f6c25c6</t>
   </si>
   <si>
     <t>01-080101-010085TC</t>
@@ -5045,7 +5045,7 @@
     <t>03-030016TC</t>
   </si>
   <si>
-    <t>135b2f3d16f10aadcd7a1e64c383a5b4</t>
+    <t>f74152985e919acc18d24beda95e9ea2</t>
   </si>
   <si>
     <t>915-150005TM</t>
@@ -5069,7 +5069,7 @@
     <t>03-030016TP</t>
   </si>
   <si>
-    <t>e23f0036d392bc5288233b226bb4056b</t>
+    <t>2775c1aca94ef3be5e1cb93e632b9c32</t>
   </si>
   <si>
     <t>03-030050A</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -311,7 +311,7 @@
     <t>01-010063TM</t>
   </si>
   <si>
-    <t>1a6e4967b8ad4e3060d15835ec792907</t>
+    <t>ad89823b30623527e3baef2253bbb1b1</t>
   </si>
   <si>
     <t>01-010056A</t>
@@ -443,7 +443,7 @@
     <t>01-010063TC</t>
   </si>
   <si>
-    <t>8ddcd036d580247e0b740246cf2a0105</t>
+    <t>c4ba01d46b527d0a4e04edce448dd616</t>
   </si>
   <si>
     <t>905-9050607-905060702TC</t>
@@ -1775,7 +1775,7 @@
     <t>05-050005TC</t>
   </si>
   <si>
-    <t>c90fc8532d13b2b346d3f832d1eadf70</t>
+    <t>07e7ff1786a3adbf9c279a7e4fbc6815</t>
   </si>
   <si>
     <t>04-040018TP</t>
@@ -2237,7 +2237,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2915,7 +2915,7 @@
     <t>01-010064TM</t>
   </si>
   <si>
-    <t>3b38a9b4f52efd161cab11b028c91cdb</t>
+    <t>282e369444428aa780db634d3867d417</t>
   </si>
   <si>
     <t>01-080101-010087A</t>
@@ -3092,13 +3092,13 @@
     <t>01-010064TC</t>
   </si>
   <si>
-    <t>34d02d95e73aec059411612203a54ca3</t>
+    <t>b7ae7df38ad9ddc0f435e255584d2b1b</t>
   </si>
   <si>
     <t>01-010064A</t>
   </si>
   <si>
-    <t>b50b38e198c71bcf98c0c43aaa9ed33b</t>
+    <t>819a318a42b307090b15e32fe333138c</t>
   </si>
   <si>
     <t>01-010042TM</t>
@@ -4505,7 +4505,7 @@
     <t>01-010063A</t>
   </si>
   <si>
-    <t>ada3adcd7fdb09e539595719cabad321</t>
+    <t>43057fba58fa2f6a9cc65bd8ce502873</t>
   </si>
   <si>
     <t>902-0204-02040101AA</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -65,7 +65,7 @@
     <t>05-050305TC</t>
   </si>
   <si>
-    <t>13630f8ea748eb39213fb6ef801fd380</t>
+    <t>c53aca77dd2eb05472af945ce1fab4a0</t>
   </si>
   <si>
     <t>03-030002TM</t>
@@ -101,7 +101,7 @@
     <t>05-050207TP</t>
   </si>
   <si>
-    <t>6823801810e55ff4c050f38a91e4ee75</t>
+    <t>be277a350cb68cb239874586d866832c</t>
   </si>
   <si>
     <t>915-150012A</t>
@@ -113,7 +113,7 @@
     <t>05-050305TP</t>
   </si>
   <si>
-    <t>055fecd33eb5761f774217967e6b2550</t>
+    <t>3016d42d9958a4430e511833cbad6fdb</t>
   </si>
   <si>
     <t>05-0709-070921BTP</t>
@@ -209,7 +209,7 @@
     <t>05-050316TP</t>
   </si>
   <si>
-    <t>e5cfcd4b711511c2aa6cacf2c915a266</t>
+    <t>cfaa5bf0423f64320f9a9d42bd4cf449</t>
   </si>
   <si>
     <t>915-150018TP</t>
@@ -659,7 +659,7 @@
     <t>05-050301TP</t>
   </si>
   <si>
-    <t>d7dc2244dcc7fecc58c0c3f61dbc3c9c</t>
+    <t>8d829c4616cf4b96cdcf731bac392921</t>
   </si>
   <si>
     <t>05-050301TM</t>
@@ -674,7 +674,7 @@
     <t>05-050301TC</t>
   </si>
   <si>
-    <t>ffc1acb4f56a9e3a2b0a163ba14a7197</t>
+    <t>cd850b29b88b6ee555efda7d2e1ed0d8</t>
   </si>
   <si>
     <t>01-010054TP</t>
@@ -692,7 +692,7 @@
     <t>05-050309A</t>
   </si>
   <si>
-    <t>736157ad34d20b9c81f8fff54f9a9631</t>
+    <t>e9e3a3273eaea7f1621c414b75cd8e62</t>
   </si>
   <si>
     <t>04-040003TP</t>
@@ -728,7 +728,7 @@
     <t>05-050312TP</t>
   </si>
   <si>
-    <t>506c015a866fcfd78105d0dad33e5604</t>
+    <t>0b699f43ea4ee38a8ef5af2190d978db</t>
   </si>
   <si>
     <t>05-0709-070954TC</t>
@@ -743,7 +743,7 @@
     <t>05-050312TC</t>
   </si>
   <si>
-    <t>5d72b43503f22b39630f179807bb9baa</t>
+    <t>7cda573046364bdfef778b607b1de319</t>
   </si>
   <si>
     <t>03-030055TP</t>
@@ -863,7 +863,7 @@
     <t>05-050203TP</t>
   </si>
   <si>
-    <t>a8fdbc611b2e9f7c4c152c9ba817869a</t>
+    <t>ec793cf2baa9c1e8e7a640296dc50ce5</t>
   </si>
   <si>
     <t>05-050007TP</t>
@@ -878,7 +878,7 @@
     <t>05-050308A</t>
   </si>
   <si>
-    <t>ec4833957306512adf3cd6b652995fbb</t>
+    <t>5296f8a14708031cbb4605357cefad3c</t>
   </si>
   <si>
     <t>05-050203TM</t>
@@ -920,7 +920,7 @@
     <t>05-050203TC</t>
   </si>
   <si>
-    <t>3ae605d2b3b9c02b245e347ef8d76cca</t>
+    <t>1c233742bac1e1822da8175ed997895e</t>
   </si>
   <si>
     <t>01-110304-11030404A</t>
@@ -950,7 +950,7 @@
     <t>05-050303TP</t>
   </si>
   <si>
-    <t>3baf8294f342ef57a23dda7f24b84723</t>
+    <t>dab12adcd4ed49832c26769dfc184eee</t>
   </si>
   <si>
     <t>03-030042TM</t>
@@ -977,7 +977,7 @@
     <t>05-050303TC</t>
   </si>
   <si>
-    <t>df06acf56eb967b330d5b4c870ed029f</t>
+    <t>c8c118d80a2faed223eb06df3af69849</t>
   </si>
   <si>
     <t>01-010010TP</t>
@@ -995,7 +995,7 @@
     <t>05-050305A</t>
   </si>
   <si>
-    <t>f8821589ef5fdd9120fbd2aff304eec0</t>
+    <t>bbf014442ec7342f24a53f458de5ad7e</t>
   </si>
   <si>
     <t>04-040001TM</t>
@@ -1040,7 +1040,7 @@
     <t>05-050314TP</t>
   </si>
   <si>
-    <t>451d116ee64b5aa6bf3d70e50dc98460</t>
+    <t>2da1fe0de84631b48d3a06e374457a98</t>
   </si>
   <si>
     <t>902-0204-02040102STC</t>
@@ -1082,7 +1082,7 @@
     <t>05-050314TC</t>
   </si>
   <si>
-    <t>7c81ed8327f94681ddb71d7a034dd2ae</t>
+    <t>41f45a9006ca64465dcc261596a96597</t>
   </si>
   <si>
     <t>902-0204-02040101ATC</t>
@@ -1091,7 +1091,7 @@
     <t>05-050306A</t>
   </si>
   <si>
-    <t>781bbd8f0bd4f4011ad0c5aa657b3dfd</t>
+    <t>99e3a3c99b1a18803949cf311cddee9b</t>
   </si>
   <si>
     <t>902-0204-02040102STP</t>
@@ -1160,7 +1160,7 @@
     <t>05-050303A</t>
   </si>
   <si>
-    <t>f148727e7d1763d473f4e7d50a0d0537</t>
+    <t>3d71c1a01703991aa2e798cd69cc83fd</t>
   </si>
   <si>
     <t>05-0709-070910TP</t>
@@ -1205,7 +1205,7 @@
     <t>05-050009TC</t>
   </si>
   <si>
-    <t>fef84f93db9651d6600d6c8a708afce2</t>
+    <t>9b9c5ad6d08999ce87b5a3fb29e233e1</t>
   </si>
   <si>
     <t>01-010036A</t>
@@ -1223,7 +1223,7 @@
     <t>05-050009TM</t>
   </si>
   <si>
-    <t>0f005e63dde286f8e3058b771f9337b8</t>
+    <t>a8a5934b9fbb7f8a3af7943abe7151a7</t>
   </si>
   <si>
     <t>03-030077TP</t>
@@ -1235,19 +1235,19 @@
     <t>05-050205TP</t>
   </si>
   <si>
-    <t>c980546ac28c1898ef8532c6ac4dd9ad</t>
+    <t>47a95099f630a3c583fbf39b74203835</t>
   </si>
   <si>
     <t>05-050304A</t>
   </si>
   <si>
-    <t>e876d5ecab2c294d26cd82e36841d4e1</t>
+    <t>298f515debba9a5401523ba659a476b7</t>
   </si>
   <si>
     <t>05-050009TP</t>
   </si>
   <si>
-    <t>d10fec61808a7040d47b8ca917d63023</t>
+    <t>b49f57b75c313ea891009b54356d4dc7</t>
   </si>
   <si>
     <t>05-050205TM</t>
@@ -1265,7 +1265,7 @@
     <t>05-050205TC</t>
   </si>
   <si>
-    <t>136010479b81bec4839cd44ca875e0da</t>
+    <t>6ddc9e616f4e07a473378ab68070f8b6</t>
   </si>
   <si>
     <t>04-040014TM</t>
@@ -1334,7 +1334,7 @@
     <t>05-050003TC</t>
   </si>
   <si>
-    <t>59e2c60c299b11bf1878b7c12928704b</t>
+    <t>ea63104c284ba92d83bc28f5d4b4d0fa</t>
   </si>
   <si>
     <t>03-030074TC</t>
@@ -1493,7 +1493,7 @@
     <t>05-050003TP</t>
   </si>
   <si>
-    <t>24268ba88e2f55a73e6dcfc6688432f6</t>
+    <t>dec5f47ae10b79faf1426a61aa8f8f71</t>
   </si>
   <si>
     <t>01-010036TC</t>
@@ -1523,7 +1523,7 @@
     <t>05-050201TC</t>
   </si>
   <si>
-    <t>a35b6184d00322ac983d6e46c8d3b739</t>
+    <t>1ff49cc2cabbac71112c2dd8e1e07df9</t>
   </si>
   <si>
     <t>03-030061TP</t>
@@ -1592,7 +1592,7 @@
     <t>05-050310TC</t>
   </si>
   <si>
-    <t>1adcf6dd01531097255d81652cf0e496</t>
+    <t>c805972242716513bfadad06ca579d42</t>
   </si>
   <si>
     <t>04-040004A</t>
@@ -1628,7 +1628,7 @@
     <t>03-030072TP</t>
   </si>
   <si>
-    <t>4183ab0db7a08c682ce11ed5151a5865</t>
+    <t>350988c015adaef798f9ca27e0db87e2</t>
   </si>
   <si>
     <t>01-080101-010082TC</t>
@@ -1640,7 +1640,7 @@
     <t>05-050310TP</t>
   </si>
   <si>
-    <t>f38ff71b4069d32deb4b7efc6c9a494b</t>
+    <t>e8a4f4a4c128ff1c4f80285ebd76cd83</t>
   </si>
   <si>
     <t>03-030072TM</t>
@@ -1796,7 +1796,7 @@
     <t>05-050005TP</t>
   </si>
   <si>
-    <t>a76262f09e2bababef10048b7cf6b52e</t>
+    <t>88c2c435c6884dbc5cd8eee399a772bd</t>
   </si>
   <si>
     <t>905-9050607-905060702A</t>
@@ -1820,7 +1820,7 @@
     <t>05-050201TP</t>
   </si>
   <si>
-    <t>521a1ea2b471158f05007f3d14e8a0ec</t>
+    <t>ba89fa237d3c1de83be112506073ffef</t>
   </si>
   <si>
     <t>05-0709-070902TM</t>
@@ -2192,7 +2192,7 @@
     <t>05-050001TC</t>
   </si>
   <si>
-    <t>f32ef20998e148a5e83300b518f8b8aa</t>
+    <t>71eb7d279df1c426c1fd315939e79c4c</t>
   </si>
   <si>
     <t>05-0709-070954A</t>
@@ -2237,7 +2237,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>
@@ -2375,7 +2375,7 @@
     <t>05-050001TP</t>
   </si>
   <si>
-    <t>5f3bede9bc5494fbe250853461b17ef7</t>
+    <t>6b59dffa6a9d25921f97bf229d443f9f</t>
   </si>
   <si>
     <t>03-030039TP</t>
@@ -2447,7 +2447,7 @@
     <t>05-050204A</t>
   </si>
   <si>
-    <t>8457a07139e24db019e8d6df63ad2827</t>
+    <t>a59190224bf106fc2b4489a4cecd3308</t>
   </si>
   <si>
     <t>05-050313A</t>
@@ -2546,7 +2546,7 @@
     <t>05-050205A</t>
   </si>
   <si>
-    <t>d1f78befcbb5ec95525e4a7383c40a3d</t>
+    <t>1fae6ea99358972b39c639786ee95090</t>
   </si>
   <si>
     <t>04-040011TM</t>
@@ -2558,7 +2558,7 @@
     <t>05-050314A</t>
   </si>
   <si>
-    <t>875fe72072dbc895784a534a5d3e2e28</t>
+    <t>268ccf6c135c07df6ef7a32de07d76ac</t>
   </si>
   <si>
     <t>901-010202-9010102021TP</t>
@@ -2639,7 +2639,7 @@
     <t>05-050208TC</t>
   </si>
   <si>
-    <t>e4d54b20b5600dd1d55880b751fe0a3b</t>
+    <t>40dbccc2a205d1183f72c8ebda232d7f</t>
   </si>
   <si>
     <t>03-030039A</t>
@@ -2690,7 +2690,7 @@
     <t>05-050311A</t>
   </si>
   <si>
-    <t>78f5ced1ce911714c84b05d6a2f92c45</t>
+    <t>8167a2ba8c125857267cd07e5e751176</t>
   </si>
   <si>
     <t>05-050208TP</t>
@@ -2720,7 +2720,7 @@
     <t>05-050306TP</t>
   </si>
   <si>
-    <t>d187e98f94589cff4479a0c30e4cbae3</t>
+    <t>3fb67e4334b5f14ec0e6abda6406aea5</t>
   </si>
   <si>
     <t>905-9050607-905060701TC</t>
@@ -2759,25 +2759,25 @@
     <t>05-050317TC</t>
   </si>
   <si>
-    <t>de3989494a8d80f0e897ec548840e892</t>
+    <t>247d2893ef57beb94920af4c3a13268b</t>
   </si>
   <si>
     <t>05-050312A</t>
   </si>
   <si>
-    <t>85b414f65cb310bc02d3b5a8d2e6aafa</t>
+    <t>6838da6c280e0c020cdff659201a38a8</t>
   </si>
   <si>
     <t>05-050009A</t>
   </si>
   <si>
-    <t>19ecefd17ffd2ecb988508254d964af1</t>
+    <t>23d15f1cb493200890169d571862b78c</t>
   </si>
   <si>
     <t>05-050203A</t>
   </si>
   <si>
-    <t>6bafa4222fcfa731ffc89cbcf0a38cdd</t>
+    <t>d0635cb66a53dc8f3f496b0b48204ebb</t>
   </si>
   <si>
     <t>01-080101-010087TM</t>
@@ -2816,7 +2816,7 @@
     <t>05-050317TP</t>
   </si>
   <si>
-    <t>db8b3e160875855515bd36f32b37d052</t>
+    <t>6db229385d7a332619d838a619ce1f0e</t>
   </si>
   <si>
     <t>01-010051TC</t>
@@ -2933,7 +2933,7 @@
     <t>05-050201A</t>
   </si>
   <si>
-    <t>ce7ffbd88adb00583fb4e8593eff66d7</t>
+    <t>d68016c2360cfba9cc7bb1fa05b2fcc8</t>
   </si>
   <si>
     <t>04-040020TC</t>
@@ -2951,7 +2951,7 @@
     <t>05-050310A</t>
   </si>
   <si>
-    <t>6fcb97b4a576ce03922c3902ff5a16f1</t>
+    <t>6951d41d22924c7ab8b3bf00c598385c</t>
   </si>
   <si>
     <t>915-150008TP</t>
@@ -3026,7 +3026,7 @@
     <t>05-050308TC</t>
   </si>
   <si>
-    <t>bcf4be1647d201974f4b0c9ee489295f</t>
+    <t>dcfb9e42e10397fd09d545a4970f1e03</t>
   </si>
   <si>
     <t>02-020002TC</t>
@@ -3044,7 +3044,7 @@
     <t>05-050004A</t>
   </si>
   <si>
-    <t>dfc4f7a6e509488ca6dd55ea25e4f67d</t>
+    <t>39034531c7e1e066474fb27a4e884d31</t>
   </si>
   <si>
     <t>03-030001TP</t>
@@ -3080,7 +3080,7 @@
     <t>05-050308TP</t>
   </si>
   <si>
-    <t>0fd199be6f4b0c11ad5b1d17d6cf4ee2</t>
+    <t>b7ba5a35fae68f25ce43ece6d5c66757</t>
   </si>
   <si>
     <t>03-030035A</t>
@@ -3152,7 +3152,7 @@
     <t>05-050005A</t>
   </si>
   <si>
-    <t>566462fd282551480d244a97e19df41f</t>
+    <t>c6e78183b43f39189efec6685703a997</t>
   </si>
   <si>
     <t>01-080101-010089TM</t>
@@ -3311,7 +3311,7 @@
     <t>05-050204TP</t>
   </si>
   <si>
-    <t>04d4a4dde888ace96511377acc86d18e</t>
+    <t>273130e8155c20a2a805533d4dc27d6c</t>
   </si>
   <si>
     <t>915-150007A</t>
@@ -3365,7 +3365,7 @@
     <t>05-050204TC</t>
   </si>
   <si>
-    <t>339e16d77d46a0c02df06e6b09cd300e</t>
+    <t>4b37fefbeb61c67215325e4cb59935e5</t>
   </si>
   <si>
     <t>04-040015TM</t>
@@ -3401,7 +3401,7 @@
     <t>05-050302TC</t>
   </si>
   <si>
-    <t>8221a623c2222a4c1107cf2575720ec5</t>
+    <t>d7b63d0c5ead8ea370338c4af7bf8d19</t>
   </si>
   <si>
     <t>01-110304-11030403TP</t>
@@ -3554,7 +3554,7 @@
     <t>05-050317A</t>
   </si>
   <si>
-    <t>1120433771da77469c9c1baa4818b120</t>
+    <t>60ada143f9042a8d096218e39f0248a2</t>
   </si>
   <si>
     <t>01-010027A</t>
@@ -3620,7 +3620,7 @@
     <t>05-050206TP</t>
   </si>
   <si>
-    <t>5cbdd52c76a3a7656bd66c1706434ebc</t>
+    <t>5c55b7bf12ff4456e1b8aedb2f4c8985</t>
   </si>
   <si>
     <t>01-010068TM</t>
@@ -3644,7 +3644,7 @@
     <t>05-050206TC</t>
   </si>
   <si>
-    <t>2182b10777082951959b97d7584fdc12</t>
+    <t>fe3f06501ddafceab9b092665cc20436</t>
   </si>
   <si>
     <t>04-040013TM</t>
@@ -3728,7 +3728,7 @@
     <t>05-050304TC</t>
   </si>
   <si>
-    <t>1244be0c3cb0fd8401423484ea23db4e</t>
+    <t>22c2b281c13284cc6f284ed199446070</t>
   </si>
   <si>
     <t>03-030043TP</t>
@@ -3740,13 +3740,13 @@
     <t>05-050206A</t>
   </si>
   <si>
-    <t>9b2c0f7d69eb2c153cbc54c17dd014d4</t>
+    <t>46ec2f9ea6517760035a3563ebcad0a2</t>
   </si>
   <si>
     <t>05-050315A</t>
   </si>
   <si>
-    <t>9f197d1576d87a37f72bad3a0091e36e</t>
+    <t>dd9e1c5e0bd7764c6d92dab6d071c342</t>
   </si>
   <si>
     <t>902-0204-02040101STP</t>
@@ -3809,7 +3809,7 @@
     <t>05-050304TP</t>
   </si>
   <si>
-    <t>e325ac58d2c018c05398370c6aa8b454</t>
+    <t>7646562564e2afd2dc47e0c7fdbb92f2</t>
   </si>
   <si>
     <t>04-040002TP</t>
@@ -3857,7 +3857,7 @@
     <t>05-050315TC</t>
   </si>
   <si>
-    <t>18b5b6b7843e3a0c6b5e24f7bb284379</t>
+    <t>5be32278080156c5a60a9623e20d69bc</t>
   </si>
   <si>
     <t>01-010046TM</t>
@@ -3872,7 +3872,7 @@
     <t>05-050316A</t>
   </si>
   <si>
-    <t>04737aab45fd06f3fd0b30259466fa71</t>
+    <t>cd44ce05963049fb11b16ca8c418e68f</t>
   </si>
   <si>
     <t>902-0204-02040101BTC</t>
@@ -3896,7 +3896,7 @@
     <t>05-050207A</t>
   </si>
   <si>
-    <t>e9fb843323e7e79fdc96daf231e22da8</t>
+    <t>8e89956ea9346583179bddb29fe7a67c</t>
   </si>
   <si>
     <t>02-020006TM</t>
@@ -3947,7 +3947,7 @@
     <t>05-050315TP</t>
   </si>
   <si>
-    <t>2000fef9b593309d512616c5c0518c00</t>
+    <t>d47eca90d0b1c581bd5adaebabed648f</t>
   </si>
   <si>
     <t>03-030040TP</t>
@@ -4019,7 +4019,7 @@
     <t>05-050004TC</t>
   </si>
   <si>
-    <t>d7f617917143389b639634a39c04c3ce</t>
+    <t>dccb20dfef28d5ed895d63f8f7e04400</t>
   </si>
   <si>
     <t>04-040019TP</t>
@@ -4040,13 +4040,13 @@
     <t>05-050004TP</t>
   </si>
   <si>
-    <t>f210143051871837bfc6627dd7c56325</t>
+    <t>f18f536e3de80068df632cfe33f3bb03</t>
   </si>
   <si>
     <t>03-030072A</t>
   </si>
   <si>
-    <t>847ed2a86541d7dff12a22c185cc5e4f</t>
+    <t>fdcf1341c4940500bc3314e7d423c93f</t>
   </si>
   <si>
     <t>04-040019TC</t>
@@ -4169,7 +4169,7 @@
     <t>05-050002TC</t>
   </si>
   <si>
-    <t>c8542c3fc14549a882ce5868fc05d872</t>
+    <t>8a04a9aa62ef3df9bf6a9a7eb767d24e</t>
   </si>
   <si>
     <t>03-030075TP</t>
@@ -4379,7 +4379,7 @@
     <t>05-050202TC</t>
   </si>
   <si>
-    <t>770fdb1cec3a9e3293ed5272c64ca9f1</t>
+    <t>f9c83da9342f98d4e01c32045e4cd7a5</t>
   </si>
   <si>
     <t>03-030062TP</t>
@@ -4397,7 +4397,7 @@
     <t>05-050311TC</t>
   </si>
   <si>
-    <t>6d6b70f832a931acc0f79c7ea4fa0815</t>
+    <t>95934d6fd05c3c25aef4d88585311d0c</t>
   </si>
   <si>
     <t>04-040014A</t>
@@ -4424,7 +4424,7 @@
     <t>05-050311TP</t>
   </si>
   <si>
-    <t>1da3972a2a795ae38fdc7cf064ae3495</t>
+    <t>94f8b627ca292ce8f5f6a87cdbae9a88</t>
   </si>
   <si>
     <t>01-080101-010081TC</t>
@@ -4523,13 +4523,13 @@
     <t>05-050309TC</t>
   </si>
   <si>
-    <t>3bbb92af73a72d21d7d114abb9b296f8</t>
+    <t>33d9ff0211090157d1fe1c44163c8c81</t>
   </si>
   <si>
     <t>05-050002A</t>
   </si>
   <si>
-    <t>37bc8746756aee4c57f645530b894c71</t>
+    <t>97a4b71c619267fbc7a432e40b572498</t>
   </si>
   <si>
     <t>01-010039TM</t>
@@ -4559,7 +4559,7 @@
     <t>05-050309TP</t>
   </si>
   <si>
-    <t>471f5dcc4254d33acd91db30453b5cd5</t>
+    <t>dc081dbe79b68938b1d983e668aeb2a0</t>
   </si>
   <si>
     <t>05-050309TM</t>
@@ -4586,7 +4586,7 @@
     <t>05-050003A</t>
   </si>
   <si>
-    <t>35f46cc2fe6a73572aca4c48470db552</t>
+    <t>ca5323dc83c80c367335e59fb001f277</t>
   </si>
   <si>
     <t>01-080101-010083A</t>
@@ -4790,7 +4790,7 @@
     <t>05-050001A</t>
   </si>
   <si>
-    <t>48240156f8a81f6de60a53a6f7fafed1</t>
+    <t>41db3c4839784cf4d3b168511e209381</t>
   </si>
   <si>
     <t>01-010006TM</t>
@@ -4925,7 +4925,7 @@
     <t>05-050002TP</t>
   </si>
   <si>
-    <t>202098ad51d2c394cf99d44d4e81b2b5</t>
+    <t>3e9e213a9d032a3e59a0992b563250a8</t>
   </si>
   <si>
     <t>05-050002TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -152,7 +152,7 @@
     <t>05-050316TC</t>
   </si>
   <si>
-    <t>3962fd7b709886f150bd31bb3b07ca9e</t>
+    <t>7174e6b3cf9fa37bacae7ad6c81246c8</t>
   </si>
   <si>
     <t>03-030059TP</t>
@@ -182,7 +182,7 @@
     <t>05-050302A</t>
   </si>
   <si>
-    <t>3ab600f8362b7bcfde638b88e63a8edf</t>
+    <t>9768a0c89cf9a4d0e4eb049cf1e10e50</t>
   </si>
   <si>
     <t>02-020005TC</t>
@@ -2684,7 +2684,7 @@
     <t>05-050202A</t>
   </si>
   <si>
-    <t>0469b64bb08b560959c1a4b120224755</t>
+    <t>1f1fee98b33e14a4c767eea7088d4d1a</t>
   </si>
   <si>
     <t>05-050311A</t>
@@ -2696,7 +2696,7 @@
     <t>05-050208TP</t>
   </si>
   <si>
-    <t>4eedab6b746da735ee74177a709f6dbe</t>
+    <t>efbd23f4219cad75c5dcd48237a79503</t>
   </si>
   <si>
     <t>901-010202-9010102022A</t>
@@ -3374,7 +3374,7 @@
     <t>05-050302TP</t>
   </si>
   <si>
-    <t>83753fff470acdb2d7675839e5d94a25</t>
+    <t>f91da0bd70bc4b36583b401d3391f1a5</t>
   </si>
   <si>
     <t>01-010055TM</t>
@@ -3548,7 +3548,7 @@
     <t>05-050208A</t>
   </si>
   <si>
-    <t>32af589514444a64350b4c5fbc8493d6</t>
+    <t>03b7accc98cca16374adda1ddc340b24</t>
   </si>
   <si>
     <t>05-050317A</t>
@@ -4331,7 +4331,7 @@
     <t>05-050202TP</t>
   </si>
   <si>
-    <t>a32272aa3859c328aa744788c8f65243</t>
+    <t>8ca78fda18656c861cebf50c49ec0829</t>
   </si>
   <si>
     <t>05-0709-070903TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2237,7 +2237,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
+    <t>bf3569543f5afe0bd329968445d710df</t>
   </si>
   <si>
     <t>01-010007TM</t>

--- a/data/metadata/hashcode.xlsx
+++ b/data/metadata/hashcode.xlsx
@@ -2237,7 +2237,7 @@
     <t>05-0709-070905BTC</t>
   </si>
   <si>
-    <t>bf3569543f5afe0bd329968445d710df</t>
+    <t>930e9bd628ccd09c643cd2b4a4b8cfad</t>
   </si>
   <si>
     <t>01-010007TM</t>
